--- a/downloads/doctors.xlsx
+++ b/downloads/doctors.xlsx
@@ -458,7 +458,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Chiropractor websites</t>
+          <t>Chiropractor directory: websites and saved pages</t>
         </is>
       </c>
     </row>

--- a/downloads/doctors.xlsx
+++ b/downloads/doctors.xlsx
@@ -458,7 +458,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Chiropractor directory: websites and saved pages</t>
+          <t>Directory of chiropractors: websites and archived pages</t>
         </is>
       </c>
     </row>

--- a/downloads/doctors.xlsx
+++ b/downloads/doctors.xlsx
@@ -492,11 +492,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Websites that post a CV (12)</t>
+          <t>Websites that post a CV (11)</t>
         </is>
       </c>
     </row>
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -562,13 +562,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
-    <col width="64" customWidth="1" min="4" max="4"/>
+    <col width="49" customWidth="1" min="1" max="1"/>
+    <col width="51" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="72" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -579,15 +581,25 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>About page</t>
+          <t>Practice</t>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
+          <t>About or team page</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
           <t>CV</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Other pages</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>How the site shows it</t>
         </is>
@@ -596,292 +608,338 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Whalen, Wayne, DC</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>drwhalen.com</t>
+          <t>Betz, Joseph W, DC</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Modern Chiropractic Center</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
+          <t>modernchiropracticcenter.com</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
           <t>open the CV</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>'Curriculum Vitae' tab under Meet the Doctors</t>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Bio page with a "Link to Curriculum Vitae" button that opens the full CV (PDF, September 2026). The set-up to copy.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Junnila, Rick, DC</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>oakleychiropractor.com</t>
+          <t>Moreau, William (Bill), DC, DACBSP</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>NeuroSport Spine and Concussion</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>neurosportspineandconcussion.com</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>open the CV</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>'Dr. Junnila's Curriculum Vitae' link (PDF, 2026)</t>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>CV (PDF) · CV (PDF) · dconline.org · ncmic.com</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Team page with a CV summary and drop-downs; a Curriculum Vitae page with highlights and a "Download Full Curriculum Vitae (PDF)" button; instructor and speaker bios elsewhere.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Austrager, Howard, DC</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>metrowestspineclinic.com</t>
+          <t>Fish, Gene, DC</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Genesis Chiropractic</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>genesischiroclinic.com</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>open the CV</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>'click HERE' for CV on About Us (PDF)</t>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>About page with a "See Dr. Fish's CV" button (PDF).</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Frisch, Todd, DC</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>shapereclaimed.com</t>
+          <t>Injury and Spinecare Chiropractic, La Crescenta</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Injury and Spinecare Chiropractic</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>injuryandspinecare.com</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
           <t>open the CV</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>CV PDF linked from About</t>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>About page with "Click to view CV"; the CV is a page on US Chiro Directory.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Reinboldt, Daniel, DC</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>greenvillespineandjoint.com</t>
+          <t>Casazza, Lance, DC</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Sacramento Chiropractic</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>open the CV</t>
+          <t>sacramentochiropractic.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>'CLICK HERE' for CV (PDF)</t>
+          <t>no separate CV</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>sacramentochiropractic.com</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Team page with a full bio for each doctor (education, experience, certifications, books); no separate CV.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Poller, Wayne, DC</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>drpoller.com</t>
+          <t>Cool Chiropractic (Sacramento)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Cool Chiropractic</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>open the CV</t>
+          <t>coolchiropracticsac.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>'Curriculum Vitae - CLICK HERE' (PDF on letterhead)</t>
+          <t>no separate CV</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Team page with a full bio for each doctor; no separate CV.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>McDowell, Gary, DC</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>mcdowellfamilychiropractic.com</t>
+          <t>P2 Sports Care</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>P2 Sports Care</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>open the CV</t>
+          <t>p2sportscare.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CV and accolades PDF on About Us</t>
+          <t>no separate CV</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Team page with a full bio for each doctor; no separate CV.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bienenfeld, Joel, DC</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>drjoelchiropractic.com</t>
+          <t>Sorrentino, Anne, DC</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dr. Anne Sorrentino</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>open the CV</t>
+          <t>drannesorrentino.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>'Dr. Joel's CV' page plus a downloadable PDF</t>
+          <t>no separate CV</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Short bio with credentials after the name; no CV.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Jaime, Joe, DC</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>onthegosportschiro.com</t>
+          <t>Young, Tom, DC</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Countryside Chiropractic</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>open the CV</t>
+          <t>countryside-chiropractic.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Curriculum Vitae page in the site menu</t>
+          <t>no separate CV</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Short bio with credentials after the name; no CV.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Thomas, William, DC</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>drtchiro.com</t>
+          <t>Horrigan, Joseph, DC</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Southern California University of Health Sciences</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>open the CV</t>
+          <t>scuhs.edu</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>'CV (Curriculum Vitae)' link on homepage</t>
+          <t>no separate CV</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Faculty bio page; no CV.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Davis, Timothy, MD</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>sourcehealthcare.com</t>
+          <t>Bisaccia, John and Marna, DC (NMR certified)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Williston Chiropractic &amp; Sportsmedicine</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>open the CV</t>
+          <t>willistonchiropractic.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>'See Dr. Davis' Curriculum Vitae' button (MD, sports medicine)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Griffith, Alexis, DC</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>impowersportsperformance.com</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>written into the About page</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>CV section written into the About page</t>
+          <t>no separate CV</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>About page with each doctor's bio and NMR certification; no CV.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -893,7 +951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E744"/>
+  <dimension ref="A1:E747"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
@@ -6493,7 +6551,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Moreau, William</t>
+          <t>Moreau, Williamalso in: Other chiropractors (CV and website review)</t>
         </is>
       </c>
       <c r="B306" s="3" t="inlineStr">
@@ -6673,7 +6731,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Sorrentino, Anne</t>
+          <t>Sorrentino, Annealso in: Other chiropractors (CV and website review)</t>
         </is>
       </c>
       <c r="B314" s="3" t="inlineStr">
@@ -9611,7 +9669,7 @@
       </c>
       <c r="C446" s="3" t="inlineStr">
         <is>
-          <t>mcdowellfamilychiropractic.com/about-us · my.onlinechiro.com/0004124/storage/app/media/gary-mcdowell-c</t>
+          <t>mcdowellfamilychiropractic.com/about-us</t>
         </is>
       </c>
       <c r="D446" t="inlineStr"/>
@@ -12825,7 +12883,7 @@
       </c>
       <c r="C600" s="3" t="inlineStr">
         <is>
-          <t>metrowestspineclinic.com/about-us/ · metrowestspineclinic.com/wp-content/uploads/2024/01/Dr.-Howa</t>
+          <t>metrowestspineclinic.com/about-us/</t>
         </is>
       </c>
       <c r="D600" t="inlineStr"/>
@@ -13014,32 +13072,32 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>CFMP, Michael Putman</t>
+          <t>Casazza, Lance</t>
         </is>
       </c>
       <c r="B609" t="inlineStr"/>
       <c r="C609" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com/directory/ca/twin-creeks-health-rosevil</t>
+          <t>sacramentochiropractic.com/team/</t>
         </is>
       </c>
       <c r="D609" t="inlineStr"/>
       <c r="E609" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com</t>
+          <t>sacramentochiropractic.com</t>
         </is>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>Charrette, Dale</t>
+          <t>CFMP, Michael Putman</t>
         </is>
       </c>
       <c r="B610" t="inlineStr"/>
       <c r="C610" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com/directory/ca/charrette-chiropractic-hea</t>
+          <t>uschirodirectory.com/directory/ca/twin-creeks-health-rosevil</t>
         </is>
       </c>
       <c r="D610" t="inlineStr"/>
@@ -13052,135 +13110,135 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>Cherik, Ara</t>
-        </is>
-      </c>
-      <c r="B611" s="3" t="inlineStr">
-        <is>
-          <t>calspinecare.com</t>
-        </is>
-      </c>
+          <t>Charrette, Dale</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr"/>
       <c r="C611" s="3" t="inlineStr">
         <is>
-          <t>calspinecare.com/about-us</t>
+          <t>uschirodirectory.com/directory/ca/charrette-chiropractic-hea</t>
         </is>
       </c>
       <c r="D611" t="inlineStr"/>
       <c r="E611" s="3" t="inlineStr">
         <is>
-          <t>calspinecare.com</t>
+          <t>uschirodirectory.com</t>
         </is>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>Conrad, Shane</t>
+          <t>Cherik, Ara</t>
         </is>
       </c>
       <c r="B612" s="3" t="inlineStr">
         <is>
-          <t>spineandsportcenter.janeapp.com</t>
-        </is>
-      </c>
-      <c r="C612" t="inlineStr"/>
+          <t>calspinecare.com</t>
+        </is>
+      </c>
+      <c r="C612" s="3" t="inlineStr">
+        <is>
+          <t>calspinecare.com/about-us</t>
+        </is>
+      </c>
       <c r="D612" t="inlineStr"/>
       <c r="E612" s="3" t="inlineStr">
         <is>
-          <t>spineandsportcenter.janeapp.com</t>
+          <t>calspinecare.com</t>
         </is>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>Coyle, Jeff</t>
+          <t>Conrad, Shane</t>
         </is>
       </c>
       <c r="B613" s="3" t="inlineStr">
         <is>
-          <t>advancedhealthcenter.com</t>
+          <t>spineandsportcenter.janeapp.com</t>
         </is>
       </c>
       <c r="C613" t="inlineStr"/>
       <c r="D613" t="inlineStr"/>
       <c r="E613" s="3" t="inlineStr">
         <is>
-          <t>advancedhealthcenter.com</t>
+          <t>spineandsportcenter.janeapp.com</t>
         </is>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>CPAK, Bradley Mouroux</t>
-        </is>
-      </c>
-      <c r="B614" t="inlineStr"/>
-      <c r="C614" s="3" t="inlineStr">
-        <is>
-          <t>uschirodirectory.com/directory/ca/mouroux-chiropractic-san-j</t>
-        </is>
-      </c>
+          <t>Coyle, Jeff</t>
+        </is>
+      </c>
+      <c r="B614" s="3" t="inlineStr">
+        <is>
+          <t>advancedhealthcenter.com</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr"/>
       <c r="D614" t="inlineStr"/>
       <c r="E614" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com</t>
+          <t>advancedhealthcenter.com</t>
         </is>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>Cremata, Edward</t>
-        </is>
-      </c>
-      <c r="B615" s="3" t="inlineStr">
-        <is>
-          <t>reliefmedicalgroup.com</t>
-        </is>
-      </c>
+          <t>CPAK, Bradley Mouroux</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr"/>
       <c r="C615" s="3" t="inlineStr">
         <is>
-          <t>reliefmedicalgroup.com/author/cremata/</t>
+          <t>uschirodirectory.com/directory/ca/mouroux-chiropractic-san-j</t>
         </is>
       </c>
       <c r="D615" t="inlineStr"/>
       <c r="E615" s="3" t="inlineStr">
         <is>
-          <t>reliefmedicalgroup.com</t>
+          <t>uschirodirectory.com</t>
         </is>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>DAAML, Marc Weiss</t>
-        </is>
-      </c>
-      <c r="B616" t="inlineStr"/>
+          <t>Cremata, Edward</t>
+        </is>
+      </c>
+      <c r="B616" s="3" t="inlineStr">
+        <is>
+          <t>reliefmedicalgroup.com</t>
+        </is>
+      </c>
       <c r="C616" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com/directory/ca/weiss-chiropractic-inc-tor</t>
+          <t>reliefmedicalgroup.com/author/cremata/</t>
         </is>
       </c>
       <c r="D616" t="inlineStr"/>
       <c r="E616" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com</t>
+          <t>reliefmedicalgroup.com</t>
         </is>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>DAAML, Rod Melvin</t>
+          <t>DAAML, Marc Weiss</t>
         </is>
       </c>
       <c r="B617" t="inlineStr"/>
       <c r="C617" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com/directory/ca/south-ontario-chiropractic</t>
+          <t>uschirodirectory.com/directory/ca/weiss-chiropractic-inc-tor</t>
         </is>
       </c>
       <c r="D617" t="inlineStr"/>
@@ -13193,13 +13251,13 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>DAAML, WON YOO</t>
+          <t>DAAML, Rod Melvin</t>
         </is>
       </c>
       <c r="B618" t="inlineStr"/>
       <c r="C618" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com/directory/ca/dr-won-s-yoo-d-c-oakland-c</t>
+          <t>uschirodirectory.com/directory/ca/south-ontario-chiropractic</t>
         </is>
       </c>
       <c r="D618" t="inlineStr"/>
@@ -13212,13 +13270,13 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>DAAPM, Rick Junnila</t>
+          <t>DAAML, WON YOO</t>
         </is>
       </c>
       <c r="B619" t="inlineStr"/>
       <c r="C619" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com/directory/ca/spine-sportcare-associates</t>
+          <t>uschirodirectory.com/directory/ca/dr-won-s-yoo-d-c-oakland-c</t>
         </is>
       </c>
       <c r="D619" t="inlineStr"/>
@@ -13231,242 +13289,242 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>Davis, Timothy</t>
-        </is>
-      </c>
-      <c r="B620" s="3" t="inlineStr">
-        <is>
-          <t>sourcehealthcare.com</t>
-        </is>
-      </c>
+          <t>DAAPM, Rick Junnila</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr"/>
       <c r="C620" s="3" t="inlineStr">
         <is>
-          <t>sourcehealthcare.com/about/dr-timothy-davis/ · sourcehealthcare.com/dr-timothy-t-davis-cv/</t>
+          <t>uschirodirectory.com/directory/ca/spine-sportcare-associates</t>
         </is>
       </c>
       <c r="D620" t="inlineStr"/>
       <c r="E620" s="3" t="inlineStr">
         <is>
-          <t>sourcehealthcare.com</t>
+          <t>uschirodirectory.com</t>
         </is>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>Davison, Robert</t>
+          <t>Davis, Timothy</t>
         </is>
       </c>
       <c r="B621" s="3" t="inlineStr">
         <is>
-          <t>backnaction.com</t>
+          <t>sourcehealthcare.com</t>
         </is>
       </c>
       <c r="C621" s="3" t="inlineStr">
         <is>
-          <t>backnaction.com/about-us · uschirodirectory.com/directory/ca/back-in-action-chiropracti</t>
+          <t>sourcehealthcare.com/about/dr-timothy-davis/</t>
         </is>
       </c>
       <c r="D621" t="inlineStr"/>
       <c r="E621" s="3" t="inlineStr">
         <is>
-          <t>backnaction.com</t>
+          <t>sourcehealthcare.com</t>
         </is>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>DeSalvo, Douglas</t>
+          <t>Davison, Robert</t>
         </is>
       </c>
       <c r="B622" s="3" t="inlineStr">
         <is>
-          <t>desalvochiropractic.com</t>
+          <t>backnaction.com</t>
         </is>
       </c>
       <c r="C622" s="3" t="inlineStr">
         <is>
-          <t>desalvochiropractic.com/about/douglas-desalvo/</t>
+          <t>backnaction.com/about-us · uschirodirectory.com/directory/ca/back-in-action-chiropracti</t>
         </is>
       </c>
       <c r="D622" t="inlineStr"/>
       <c r="E622" s="3" t="inlineStr">
         <is>
-          <t>desalvochiropractic.com</t>
+          <t>backnaction.com</t>
         </is>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>Dickman, Robert</t>
-        </is>
-      </c>
-      <c r="B623" t="inlineStr"/>
+          <t>DeSalvo, Douglas</t>
+        </is>
+      </c>
+      <c r="B623" s="3" t="inlineStr">
+        <is>
+          <t>desalvochiropractic.com</t>
+        </is>
+      </c>
       <c r="C623" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com/directory/ca/dickman-chiropractic-corpo</t>
+          <t>desalvochiropractic.com/about/douglas-desalvo/</t>
         </is>
       </c>
       <c r="D623" t="inlineStr"/>
       <c r="E623" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com</t>
+          <t>desalvochiropractic.com</t>
         </is>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>DiSiena, Douglas</t>
-        </is>
-      </c>
-      <c r="B624" s="3" t="inlineStr">
-        <is>
-          <t>irvinechiropracticoffices.com</t>
-        </is>
-      </c>
+          <t>Dickman, Robert</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr"/>
       <c r="C624" s="3" t="inlineStr">
         <is>
-          <t>irvinechiropracticoffices.com/about/douglas-a-disiena.php</t>
+          <t>uschirodirectory.com/directory/ca/dickman-chiropractic-corpo</t>
         </is>
       </c>
       <c r="D624" t="inlineStr"/>
       <c r="E624" s="3" t="inlineStr">
         <is>
-          <t>irvinechiropracticoffices.com</t>
+          <t>uschirodirectory.com</t>
         </is>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>Do, Binh Huu</t>
-        </is>
-      </c>
-      <c r="B625" t="inlineStr"/>
+          <t>DiSiena, Douglas</t>
+        </is>
+      </c>
+      <c r="B625" s="3" t="inlineStr">
+        <is>
+          <t>irvinechiropracticoffices.com</t>
+        </is>
+      </c>
       <c r="C625" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com/directory/ca/binh-huu-do-d-c-san-jose-c</t>
+          <t>irvinechiropracticoffices.com/about/douglas-a-disiena.php</t>
         </is>
       </c>
       <c r="D625" t="inlineStr"/>
       <c r="E625" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com</t>
+          <t>irvinechiropracticoffices.com</t>
         </is>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>Fakhoury, Sayel</t>
-        </is>
-      </c>
-      <c r="B626" s="3" t="inlineStr">
-        <is>
-          <t>drsayelfakhouryonline.com</t>
-        </is>
-      </c>
-      <c r="C626" t="inlineStr"/>
+          <t>Do, Binh Huu</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr"/>
+      <c r="C626" s="3" t="inlineStr">
+        <is>
+          <t>uschirodirectory.com/directory/ca/binh-huu-do-d-c-san-jose-c</t>
+        </is>
+      </c>
       <c r="D626" t="inlineStr"/>
       <c r="E626" s="3" t="inlineStr">
         <is>
-          <t>drsayelfakhouryonline.com</t>
+          <t>uschirodirectory.com</t>
         </is>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>FASBE, Jeff Coyle</t>
-        </is>
-      </c>
-      <c r="B627" t="inlineStr"/>
-      <c r="C627" s="3" t="inlineStr">
-        <is>
-          <t>uschirodirectory.com/directory/ca/jeff-coyle-and-advanced-he</t>
-        </is>
-      </c>
+          <t>Fakhoury, Sayel</t>
+        </is>
+      </c>
+      <c r="B627" s="3" t="inlineStr">
+        <is>
+          <t>drsayelfakhouryonline.com</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr"/>
       <c r="D627" t="inlineStr"/>
       <c r="E627" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com</t>
+          <t>drsayelfakhouryonline.com</t>
         </is>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>Faye, Leonard</t>
-        </is>
-      </c>
-      <c r="B628" s="3" t="inlineStr">
-        <is>
-          <t>fayechiropractic.com</t>
-        </is>
-      </c>
-      <c r="C628" t="inlineStr"/>
+          <t>FASBE, Jeff Coyle</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr"/>
+      <c r="C628" s="3" t="inlineStr">
+        <is>
+          <t>uschirodirectory.com/directory/ca/jeff-coyle-and-advanced-he</t>
+        </is>
+      </c>
       <c r="D628" t="inlineStr"/>
       <c r="E628" s="3" t="inlineStr">
         <is>
-          <t>fayechiropractic.com</t>
+          <t>uschirodirectory.com</t>
         </is>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>Fey, Pierre</t>
+          <t>Faye, Leonard</t>
         </is>
       </c>
       <c r="B629" s="3" t="inlineStr">
         <is>
-          <t>feychiropractic.com</t>
-        </is>
-      </c>
-      <c r="C629" s="3" t="inlineStr">
-        <is>
-          <t>uschirodirectory.com/directory/ca/fey-chiropractic-westlake-</t>
-        </is>
-      </c>
+          <t>fayechiropractic.com</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr"/>
       <c r="D629" t="inlineStr"/>
       <c r="E629" s="3" t="inlineStr">
         <is>
-          <t>feychiropractic.com</t>
+          <t>fayechiropractic.com</t>
         </is>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>FPSC, Daniel Steffins</t>
-        </is>
-      </c>
-      <c r="B630" t="inlineStr"/>
+          <t>Fey, Pierre</t>
+        </is>
+      </c>
+      <c r="B630" s="3" t="inlineStr">
+        <is>
+          <t>feychiropractic.com</t>
+        </is>
+      </c>
       <c r="C630" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com/directory/ca/spinal-health-center-of-we</t>
+          <t>uschirodirectory.com/directory/ca/fey-chiropractic-westlake-</t>
         </is>
       </c>
       <c r="D630" t="inlineStr"/>
       <c r="E630" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com</t>
+          <t>feychiropractic.com</t>
         </is>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>FPSC, Rick Junnila</t>
+          <t>FPSC, Daniel Steffins</t>
         </is>
       </c>
       <c r="B631" t="inlineStr"/>
       <c r="C631" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com/directory/ca/lifestyle-health-fitness-o</t>
+          <t>uschirodirectory.com/directory/ca/spinal-health-center-of-we</t>
         </is>
       </c>
       <c r="D631" t="inlineStr"/>
@@ -13479,13 +13537,13 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>FRCCS, Leonard Faye</t>
+          <t>FPSC, Rick Junnila</t>
         </is>
       </c>
       <c r="B632" t="inlineStr"/>
       <c r="C632" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com/directory/ca/faye-faye-chiropractic-los</t>
+          <t>uschirodirectory.com/directory/ca/lifestyle-health-fitness-o</t>
         </is>
       </c>
       <c r="D632" t="inlineStr"/>
@@ -13498,13 +13556,13 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>Friedman, Howard</t>
+          <t>FRCCS, Leonard Faye</t>
         </is>
       </c>
       <c r="B633" t="inlineStr"/>
       <c r="C633" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com/directory/ca/friedman-family-chiropract</t>
+          <t>uschirodirectory.com/directory/ca/faye-faye-chiropractic-los</t>
         </is>
       </c>
       <c r="D633" t="inlineStr"/>
@@ -13517,166 +13575,166 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>Frisch, Todd</t>
-        </is>
-      </c>
-      <c r="B634" s="3" t="inlineStr">
-        <is>
-          <t>shapereclaimed.com</t>
-        </is>
-      </c>
+          <t>Friedman, Howard</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr"/>
       <c r="C634" s="3" t="inlineStr">
         <is>
-          <t>shapereclaimed.com/about · shapereclaimed.com/wp-content/uploads/2024/09/Dr.-Todd-Frisc</t>
+          <t>uschirodirectory.com/directory/ca/friedman-family-chiropract</t>
         </is>
       </c>
       <c r="D634" t="inlineStr"/>
       <c r="E634" s="3" t="inlineStr">
         <is>
-          <t>shapereclaimed.com</t>
+          <t>uschirodirectory.com</t>
         </is>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>Funk, Steve</t>
+          <t>Frisch, Todd</t>
         </is>
       </c>
       <c r="B635" s="3" t="inlineStr">
         <is>
-          <t>drfunkchiropractic.com</t>
+          <t>shapereclaimed.com</t>
         </is>
       </c>
       <c r="C635" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com/directory/ca/dr-funk-chiropractic-rosev</t>
+          <t>shapereclaimed.com/about</t>
         </is>
       </c>
       <c r="D635" t="inlineStr"/>
       <c r="E635" s="3" t="inlineStr">
         <is>
-          <t>drfunkchiropractic.com</t>
+          <t>shapereclaimed.com</t>
         </is>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>Galla, Eric</t>
+          <t>Funk, Steve</t>
         </is>
       </c>
       <c r="B636" s="3" t="inlineStr">
         <is>
-          <t>gallachiropractic.com</t>
-        </is>
-      </c>
-      <c r="C636" t="inlineStr"/>
+          <t>drfunkchiropractic.com</t>
+        </is>
+      </c>
+      <c r="C636" s="3" t="inlineStr">
+        <is>
+          <t>uschirodirectory.com/directory/ca/dr-funk-chiropractic-rosev</t>
+        </is>
+      </c>
       <c r="D636" t="inlineStr"/>
       <c r="E636" s="3" t="inlineStr">
         <is>
-          <t>gallachiropractic.com</t>
+          <t>drfunkchiropractic.com</t>
         </is>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>Garcia, Daniel</t>
+          <t>Galla, Eric</t>
         </is>
       </c>
       <c r="B637" s="3" t="inlineStr">
         <is>
-          <t>dannygarciadc.com</t>
-        </is>
-      </c>
-      <c r="C637" s="3" t="inlineStr">
-        <is>
-          <t>uschirodirectory.com/directory/ca/garcia-chiropractic-costa-</t>
-        </is>
-      </c>
+          <t>gallachiropractic.com</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr"/>
       <c r="D637" t="inlineStr"/>
       <c r="E637" s="3" t="inlineStr">
         <is>
-          <t>dannygarciadc.com</t>
+          <t>gallachiropractic.com</t>
         </is>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>Geary, David</t>
+          <t>Garcia, Daniel</t>
         </is>
       </c>
       <c r="B638" s="3" t="inlineStr">
         <is>
-          <t>valleychiroassoc.com</t>
+          <t>dannygarciadc.com</t>
         </is>
       </c>
       <c r="C638" s="3" t="inlineStr">
         <is>
-          <t>valleychiroassoc.com/who-we-are/</t>
+          <t>uschirodirectory.com/directory/ca/garcia-chiropractic-costa-</t>
         </is>
       </c>
       <c r="D638" t="inlineStr"/>
       <c r="E638" s="3" t="inlineStr">
         <is>
-          <t>valleychiroassoc.com</t>
+          <t>dannygarciadc.com</t>
         </is>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>Ghods, Arman</t>
+          <t>Geary, David</t>
         </is>
       </c>
       <c r="B639" s="3" t="inlineStr">
         <is>
-          <t>drarmanghods.com</t>
+          <t>valleychiroassoc.com</t>
         </is>
       </c>
       <c r="C639" s="3" t="inlineStr">
         <is>
-          <t>drarmanghods.com/about-reliable-physical-exams/</t>
+          <t>valleychiroassoc.com/who-we-are/</t>
         </is>
       </c>
       <c r="D639" t="inlineStr"/>
       <c r="E639" s="3" t="inlineStr">
         <is>
-          <t>drarmanghods.com</t>
+          <t>valleychiroassoc.com</t>
         </is>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>Gibson, Tom</t>
-        </is>
-      </c>
-      <c r="B640" t="inlineStr"/>
+          <t>Ghods, Arman</t>
+        </is>
+      </c>
+      <c r="B640" s="3" t="inlineStr">
+        <is>
+          <t>drarmanghods.com</t>
+        </is>
+      </c>
       <c r="C640" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com/directory/ca/dr-tom-gibson-d-c-cameron-</t>
+          <t>drarmanghods.com/about-reliable-physical-exams/</t>
         </is>
       </c>
       <c r="D640" t="inlineStr"/>
       <c r="E640" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com</t>
+          <t>drarmanghods.com</t>
         </is>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>HARMO, KIRK WRIGHT RN</t>
+          <t>Gibson, Tom</t>
         </is>
       </c>
       <c r="B641" t="inlineStr"/>
       <c r="C641" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com/directory/ca/harmonic-life-chiropractic</t>
+          <t>uschirodirectory.com/directory/ca/dr-tom-gibson-d-c-cameron-</t>
         </is>
       </c>
       <c r="D641" t="inlineStr"/>
@@ -13689,13 +13747,13 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>Hecht, Robert</t>
+          <t>HARMO, KIRK WRIGHT RN</t>
         </is>
       </c>
       <c r="B642" t="inlineStr"/>
       <c r="C642" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com/directory/ca/advanced-health-solutions-</t>
+          <t>uschirodirectory.com/directory/ca/harmonic-life-chiropractic</t>
         </is>
       </c>
       <c r="D642" t="inlineStr"/>
@@ -13708,13 +13766,13 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>Hernandez, Jose</t>
+          <t>Hecht, Robert</t>
         </is>
       </c>
       <c r="B643" t="inlineStr"/>
       <c r="C643" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com/directory/ca/hernandez-chiropractic-san</t>
+          <t>uschirodirectory.com/directory/ca/advanced-health-solutions-</t>
         </is>
       </c>
       <c r="D643" t="inlineStr"/>
@@ -13727,13 +13785,13 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>IDE, Albert Mansour</t>
+          <t>Hernandez, Jose</t>
         </is>
       </c>
       <c r="B644" t="inlineStr"/>
       <c r="C644" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com/directory/ca/mansour-chiropractic-inc-c</t>
+          <t>uschirodirectory.com/directory/ca/hernandez-chiropractic-san</t>
         </is>
       </c>
       <c r="D644" t="inlineStr"/>
@@ -13746,665 +13804,665 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>Ingram, Patrick</t>
-        </is>
-      </c>
-      <c r="B645" s="3" t="inlineStr">
-        <is>
-          <t>marylandspinecare.com</t>
-        </is>
-      </c>
-      <c r="C645" t="inlineStr"/>
+          <t>IDE, Albert Mansour</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr"/>
+      <c r="C645" s="3" t="inlineStr">
+        <is>
+          <t>uschirodirectory.com/directory/ca/mansour-chiropractic-inc-c</t>
+        </is>
+      </c>
       <c r="D645" t="inlineStr"/>
       <c r="E645" s="3" t="inlineStr">
         <is>
-          <t>marylandspinecare.com</t>
+          <t>uschirodirectory.com</t>
         </is>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>Joe, Tobias D</t>
-        </is>
-      </c>
-      <c r="B646" t="inlineStr"/>
-      <c r="C646" s="3" t="inlineStr">
-        <is>
-          <t>uschirodirectory.com/directory/ca/d-joe-tobias-d-c-laguna-hi · uschirodirectory.com/directory/ca/placentia-linda-chiropract</t>
-        </is>
-      </c>
+          <t>Ingram, Patrick</t>
+        </is>
+      </c>
+      <c r="B646" s="3" t="inlineStr">
+        <is>
+          <t>marylandspinecare.com</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr"/>
       <c r="D646" t="inlineStr"/>
       <c r="E646" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com</t>
+          <t>marylandspinecare.com</t>
         </is>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>Jones, Greg</t>
-        </is>
-      </c>
-      <c r="B647" s="3" t="inlineStr">
-        <is>
-          <t>turlockchiro.com</t>
-        </is>
-      </c>
+          <t>Joe, Tobias D</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr"/>
       <c r="C647" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com/directory/ca/turlock-family-chiropracti</t>
+          <t>uschirodirectory.com/directory/ca/d-joe-tobias-d-c-laguna-hi · uschirodirectory.com/directory/ca/placentia-linda-chiropract</t>
         </is>
       </c>
       <c r="D647" t="inlineStr"/>
       <c r="E647" s="3" t="inlineStr">
         <is>
-          <t>turlockchiro.com</t>
+          <t>uschirodirectory.com</t>
         </is>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>Junnila, Rick</t>
+          <t>Jones, Greg</t>
         </is>
       </c>
       <c r="B648" s="3" t="inlineStr">
         <is>
-          <t>oakleychiropractor.com</t>
+          <t>turlockchiro.com</t>
         </is>
       </c>
       <c r="C648" s="3" t="inlineStr">
         <is>
-          <t>oakleychiropractor.com/meet-the-staff/ · doc.vortala.com/childsites/uploads/1252/files/dr-rick-cv-202</t>
+          <t>uschirodirectory.com/directory/ca/turlock-family-chiropracti</t>
         </is>
       </c>
       <c r="D648" t="inlineStr"/>
       <c r="E648" s="3" t="inlineStr">
         <is>
-          <t>oakleychiropractor.com</t>
+          <t>turlockchiro.com</t>
         </is>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>Khodabakhsh, Ashkan</t>
+          <t>Junnila, Rick</t>
         </is>
       </c>
       <c r="B649" s="3" t="inlineStr">
         <is>
-          <t>thechiroguy.com</t>
+          <t>oakleychiropractor.com</t>
         </is>
       </c>
       <c r="C649" s="3" t="inlineStr">
         <is>
-          <t>thechiroguy.com/meet-dr-brian-noor/</t>
+          <t>oakleychiropractor.com/meet-the-staff/</t>
         </is>
       </c>
       <c r="D649" t="inlineStr"/>
       <c r="E649" s="3" t="inlineStr">
         <is>
-          <t>thechiroguy.com</t>
+          <t>oakleychiropractor.com</t>
         </is>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>LA, T Jimmy Kazandjian</t>
-        </is>
-      </c>
-      <c r="B650" t="inlineStr"/>
+          <t>Khodabakhsh, Ashkan</t>
+        </is>
+      </c>
+      <c r="B650" s="3" t="inlineStr">
+        <is>
+          <t>thechiroguy.com</t>
+        </is>
+      </c>
       <c r="C650" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com/directory/ca/sol-wellness-center-burban</t>
+          <t>thechiroguy.com/meet-dr-brian-noor/</t>
         </is>
       </c>
       <c r="D650" t="inlineStr"/>
       <c r="E650" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com</t>
+          <t>thechiroguy.com</t>
         </is>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>Lane, Marc</t>
-        </is>
-      </c>
-      <c r="B651" s="3" t="inlineStr">
-        <is>
-          <t>marcjlane.com</t>
-        </is>
-      </c>
+          <t>LA, T Jimmy Kazandjian</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr"/>
       <c r="C651" s="3" t="inlineStr">
         <is>
-          <t>marcjlane.com/newsfeed/rss/marcjlane-newsletters-articles/</t>
+          <t>uschirodirectory.com/directory/ca/sol-wellness-center-burban</t>
         </is>
       </c>
       <c r="D651" t="inlineStr"/>
       <c r="E651" s="3" t="inlineStr">
         <is>
-          <t>marcjlane.com</t>
+          <t>uschirodirectory.com</t>
         </is>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>Langmaid, Jeff</t>
+          <t>Lane, Marc</t>
         </is>
       </c>
       <c r="B652" s="3" t="inlineStr">
         <is>
-          <t>theevidencebasedchiropractor.com</t>
-        </is>
-      </c>
-      <c r="C652" t="inlineStr"/>
+          <t>marcjlane.com</t>
+        </is>
+      </c>
+      <c r="C652" s="3" t="inlineStr">
+        <is>
+          <t>marcjlane.com/newsfeed/rss/marcjlane-newsletters-articles/</t>
+        </is>
+      </c>
       <c r="D652" t="inlineStr"/>
       <c r="E652" s="3" t="inlineStr">
         <is>
-          <t>theevidencebasedchiropractor.com</t>
+          <t>marcjlane.com</t>
         </is>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>Lesko, Mark</t>
+          <t>Langmaid, Jeff</t>
         </is>
       </c>
       <c r="B653" s="3" t="inlineStr">
         <is>
-          <t>chrcaustin.com</t>
-        </is>
-      </c>
-      <c r="C653" s="3" t="inlineStr">
-        <is>
-          <t>chrcaustin.com/about-us/</t>
-        </is>
-      </c>
+          <t>theevidencebasedchiropractor.com</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr"/>
       <c r="D653" t="inlineStr"/>
       <c r="E653" s="3" t="inlineStr">
         <is>
-          <t>chrcaustin.com</t>
+          <t>theevidencebasedchiropractor.com</t>
         </is>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>Lewis, Marc</t>
-        </is>
-      </c>
-      <c r="B654" t="inlineStr"/>
+          <t>Lesko, Mark</t>
+        </is>
+      </c>
+      <c r="B654" s="3" t="inlineStr">
+        <is>
+          <t>chrcaustin.com</t>
+        </is>
+      </c>
       <c r="C654" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com/directory/ca/gabriel-hannawi-san-diego-</t>
+          <t>chrcaustin.com/about-us/</t>
         </is>
       </c>
       <c r="D654" t="inlineStr"/>
       <c r="E654" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com</t>
+          <t>chrcaustin.com</t>
         </is>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>Libs, Jay</t>
-        </is>
-      </c>
-      <c r="B655" s="3" t="inlineStr">
-        <is>
-          <t>libschiropractic.com</t>
-        </is>
-      </c>
-      <c r="C655" t="inlineStr"/>
+          <t>Lewis, Marc</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr"/>
+      <c r="C655" s="3" t="inlineStr">
+        <is>
+          <t>uschirodirectory.com/directory/ca/gabriel-hannawi-san-diego-</t>
+        </is>
+      </c>
       <c r="D655" t="inlineStr"/>
       <c r="E655" s="3" t="inlineStr">
         <is>
-          <t>libschiropractic.com</t>
+          <t>uschirodirectory.com</t>
         </is>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>Lincoln, David</t>
-        </is>
-      </c>
-      <c r="B656" t="inlineStr"/>
-      <c r="C656" s="3" t="inlineStr">
-        <is>
-          <t>uschirodirectory.com/directory/ca/healthy-families-chiroprac</t>
-        </is>
-      </c>
+          <t>Libs, Jay</t>
+        </is>
+      </c>
+      <c r="B656" s="3" t="inlineStr">
+        <is>
+          <t>libschiropractic.com</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr"/>
       <c r="D656" t="inlineStr"/>
       <c r="E656" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com</t>
+          <t>libschiropractic.com</t>
         </is>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>Mansour, Albert</t>
-        </is>
-      </c>
-      <c r="B657" s="3" t="inlineStr">
-        <is>
-          <t>mansourchiropractic.com</t>
-        </is>
-      </c>
+          <t>Lincoln, David</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr"/>
       <c r="C657" s="3" t="inlineStr">
         <is>
-          <t>mansourchiropractic.com/about-us/</t>
+          <t>uschirodirectory.com/directory/ca/healthy-families-chiroprac</t>
         </is>
       </c>
       <c r="D657" t="inlineStr"/>
       <c r="E657" s="3" t="inlineStr">
         <is>
-          <t>mansourchiropractic.com</t>
+          <t>uschirodirectory.com</t>
         </is>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>Marinaro, Ronald</t>
-        </is>
-      </c>
-      <c r="B658" t="inlineStr"/>
+          <t>Mansour, Albert</t>
+        </is>
+      </c>
+      <c r="B658" s="3" t="inlineStr">
+        <is>
+          <t>mansourchiropractic.com</t>
+        </is>
+      </c>
       <c r="C658" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com/directory/ca/loranger-family-wellness-c</t>
+          <t>mansourchiropractic.com/about-us/</t>
         </is>
       </c>
       <c r="D658" t="inlineStr"/>
       <c r="E658" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com</t>
+          <t>mansourchiropractic.com</t>
         </is>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>Marsh, Paul</t>
-        </is>
-      </c>
-      <c r="B659" s="3" t="inlineStr">
-        <is>
-          <t>drmarshonline.com</t>
-        </is>
-      </c>
-      <c r="C659" t="inlineStr"/>
+          <t>Marinaro, Ronald</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr"/>
+      <c r="C659" s="3" t="inlineStr">
+        <is>
+          <t>uschirodirectory.com/directory/ca/loranger-family-wellness-c</t>
+        </is>
+      </c>
       <c r="D659" t="inlineStr"/>
       <c r="E659" s="3" t="inlineStr">
         <is>
-          <t>drmarshonline.com</t>
+          <t>uschirodirectory.com</t>
         </is>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>McCarty, L Dwight</t>
+          <t>Marna, Bisaccia John and</t>
         </is>
       </c>
       <c r="B660" t="inlineStr"/>
       <c r="C660" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com/directory/ca/dr-mccarty-doctor-of-chiro</t>
+          <t>willistonchiropractic.com/about/</t>
         </is>
       </c>
       <c r="D660" t="inlineStr"/>
       <c r="E660" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com</t>
+          <t>willistonchiropractic.com</t>
         </is>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>Mellinger, Richard</t>
-        </is>
-      </c>
-      <c r="B661" t="inlineStr"/>
-      <c r="C661" s="3" t="inlineStr">
-        <is>
-          <t>uschirodirectory.com/directory/ca/mellinger-chiropractic-can</t>
-        </is>
-      </c>
+          <t>Marsh, Paul</t>
+        </is>
+      </c>
+      <c r="B661" s="3" t="inlineStr">
+        <is>
+          <t>drmarshonline.com</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr"/>
       <c r="D661" t="inlineStr"/>
       <c r="E661" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com</t>
+          <t>drmarshonline.com</t>
         </is>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>Melvin, Rod</t>
-        </is>
-      </c>
-      <c r="B662" s="3" t="inlineStr">
-        <is>
-          <t>southontariochiro.com</t>
-        </is>
-      </c>
-      <c r="C662" t="inlineStr"/>
+          <t>McCarty, L Dwight</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr"/>
+      <c r="C662" s="3" t="inlineStr">
+        <is>
+          <t>uschirodirectory.com/directory/ca/dr-mccarty-doctor-of-chiro</t>
+        </is>
+      </c>
       <c r="D662" t="inlineStr"/>
       <c r="E662" s="3" t="inlineStr">
         <is>
-          <t>southontariochiro.com</t>
+          <t>uschirodirectory.com</t>
         </is>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>Miller, Jason</t>
-        </is>
-      </c>
-      <c r="B663" s="3" t="inlineStr">
-        <is>
-          <t>posture-works.com</t>
-        </is>
-      </c>
-      <c r="C663" t="inlineStr"/>
+          <t>Mellinger, Richard</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr"/>
+      <c r="C663" s="3" t="inlineStr">
+        <is>
+          <t>uschirodirectory.com/directory/ca/mellinger-chiropractic-can</t>
+        </is>
+      </c>
       <c r="D663" t="inlineStr"/>
       <c r="E663" s="3" t="inlineStr">
         <is>
-          <t>posture-works.com</t>
+          <t>uschirodirectory.com</t>
         </is>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>Moreau, Bill</t>
-        </is>
-      </c>
-      <c r="B664" t="inlineStr"/>
+          <t>Melvin, Rod</t>
+        </is>
+      </c>
+      <c r="B664" s="3" t="inlineStr">
+        <is>
+          <t>southontariochiro.com</t>
+        </is>
+      </c>
       <c r="C664" t="inlineStr"/>
       <c r="D664" t="inlineStr"/>
-      <c r="E664" t="inlineStr"/>
+      <c r="E664" s="3" t="inlineStr">
+        <is>
+          <t>southontariochiro.com</t>
+        </is>
+      </c>
     </row>
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>MUAC, David Salse</t>
-        </is>
-      </c>
-      <c r="B665" t="inlineStr"/>
-      <c r="C665" s="3" t="inlineStr">
-        <is>
-          <t>uschirodirectory.com/directory/ca/salse-chiropractic-center-</t>
-        </is>
-      </c>
+          <t>Miller, Jason</t>
+        </is>
+      </c>
+      <c r="B665" s="3" t="inlineStr">
+        <is>
+          <t>posture-works.com</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr"/>
       <c r="D665" t="inlineStr"/>
       <c r="E665" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com</t>
+          <t>posture-works.com</t>
         </is>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>Mueller, Ken</t>
-        </is>
-      </c>
-      <c r="B666" s="3" t="inlineStr">
-        <is>
-          <t>drkenmueller.com</t>
-        </is>
-      </c>
-      <c r="C666" s="3" t="inlineStr">
-        <is>
-          <t>drkenmueller.com/about/</t>
-        </is>
-      </c>
+          <t>Moreau, Bill</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr"/>
+      <c r="C666" t="inlineStr"/>
       <c r="D666" t="inlineStr"/>
-      <c r="E666" s="3" t="inlineStr">
-        <is>
-          <t>drkenmueller.com</t>
-        </is>
-      </c>
+      <c r="E666" t="inlineStr"/>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>Ngan, Jason</t>
-        </is>
-      </c>
-      <c r="B667" s="3" t="inlineStr">
-        <is>
-          <t>nganchiropractic.com</t>
-        </is>
-      </c>
+          <t>MUAC, David Salse</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr"/>
       <c r="C667" s="3" t="inlineStr">
         <is>
-          <t>nganchiropractic.com/about-us</t>
+          <t>uschirodirectory.com/directory/ca/salse-chiropractic-center-</t>
         </is>
       </c>
       <c r="D667" t="inlineStr"/>
       <c r="E667" s="3" t="inlineStr">
         <is>
-          <t>nganchiropractic.com</t>
+          <t>uschirodirectory.com</t>
         </is>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>Nguyen, The</t>
+          <t>Mueller, Ken</t>
         </is>
       </c>
       <c r="B668" s="3" t="inlineStr">
         <is>
-          <t>nguyenchiro.com</t>
+          <t>drkenmueller.com</t>
         </is>
       </c>
       <c r="C668" s="3" t="inlineStr">
         <is>
-          <t>nguyenchiro.com/meet-our-team/</t>
+          <t>drkenmueller.com/about/</t>
         </is>
       </c>
       <c r="D668" t="inlineStr"/>
       <c r="E668" s="3" t="inlineStr">
         <is>
-          <t>nguyenchiro.com</t>
+          <t>drkenmueller.com</t>
         </is>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>Nia, Amin</t>
+          <t>Ngan, Jason</t>
         </is>
       </c>
       <c r="B669" s="3" t="inlineStr">
         <is>
-          <t>spectrummedical.org</t>
+          <t>nganchiropractic.com</t>
         </is>
       </c>
       <c r="C669" s="3" t="inlineStr">
         <is>
-          <t>spectrummedical.org/amin-nia-d-c</t>
+          <t>nganchiropractic.com/about-us</t>
         </is>
       </c>
       <c r="D669" t="inlineStr"/>
       <c r="E669" s="3" t="inlineStr">
         <is>
-          <t>spectrummedical.org</t>
+          <t>nganchiropractic.com</t>
         </is>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>Nikroo, Al</t>
+          <t>Nguyen, The</t>
         </is>
       </c>
       <c r="B670" s="3" t="inlineStr">
         <is>
-          <t>elitesportsdc.com</t>
+          <t>nguyenchiro.com</t>
         </is>
       </c>
       <c r="C670" s="3" t="inlineStr">
         <is>
-          <t>elitesportsdc.com/dr-al-nikroo-chiropractic-doctor-woodland-</t>
+          <t>nguyenchiro.com/meet-our-team/</t>
         </is>
       </c>
       <c r="D670" t="inlineStr"/>
       <c r="E670" s="3" t="inlineStr">
         <is>
-          <t>elitesportsdc.com</t>
+          <t>nguyenchiro.com</t>
         </is>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>Parlett, Chase</t>
+          <t>Nia, Amin</t>
         </is>
       </c>
       <c r="B671" s="3" t="inlineStr">
         <is>
-          <t>golifesource.com</t>
+          <t>spectrummedical.org</t>
         </is>
       </c>
       <c r="C671" s="3" t="inlineStr">
         <is>
-          <t>golifesource.com/dr-chase-parlett/</t>
+          <t>spectrummedical.org/amin-nia-d-c</t>
         </is>
       </c>
       <c r="D671" t="inlineStr"/>
       <c r="E671" s="3" t="inlineStr">
         <is>
-          <t>golifesource.com</t>
+          <t>spectrummedical.org</t>
         </is>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>Pham, Hang</t>
-        </is>
-      </c>
-      <c r="B672" t="inlineStr"/>
+          <t>Nikroo, Al</t>
+        </is>
+      </c>
+      <c r="B672" s="3" t="inlineStr">
+        <is>
+          <t>elitesportsdc.com</t>
+        </is>
+      </c>
       <c r="C672" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com/directory/ca/prime-health-center-anahei</t>
+          <t>elitesportsdc.com/dr-al-nikroo-chiropractic-doctor-woodland-</t>
         </is>
       </c>
       <c r="D672" t="inlineStr"/>
       <c r="E672" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com</t>
+          <t>elitesportsdc.com</t>
         </is>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>Poller, Wayne</t>
+          <t>Parlett, Chase</t>
         </is>
       </c>
       <c r="B673" s="3" t="inlineStr">
         <is>
-          <t>drpoller.com</t>
+          <t>golifesource.com</t>
         </is>
       </c>
       <c r="C673" s="3" t="inlineStr">
         <is>
-          <t>drpoller.com/us/ · drpoller.com/wp-content/uploads/2025/02/cv-on-letterhead.pdf</t>
+          <t>golifesource.com/dr-chase-parlett/</t>
         </is>
       </c>
       <c r="D673" t="inlineStr"/>
       <c r="E673" s="3" t="inlineStr">
         <is>
-          <t>drpoller.com</t>
+          <t>golifesource.com</t>
         </is>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>Putman, Michael</t>
-        </is>
-      </c>
-      <c r="B674" s="3" t="inlineStr">
-        <is>
-          <t>twincreekshealth.com</t>
-        </is>
-      </c>
-      <c r="C674" t="inlineStr"/>
+          <t>Pham, Hang</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr"/>
+      <c r="C674" s="3" t="inlineStr">
+        <is>
+          <t>uschirodirectory.com/directory/ca/prime-health-center-anahei</t>
+        </is>
+      </c>
       <c r="D674" t="inlineStr"/>
       <c r="E674" s="3" t="inlineStr">
         <is>
-          <t>twincreekshealth.com</t>
+          <t>uschirodirectory.com</t>
         </is>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>QME, Ali Mostafavi</t>
-        </is>
-      </c>
-      <c r="B675" t="inlineStr"/>
+          <t>Poller, Wayne</t>
+        </is>
+      </c>
+      <c r="B675" s="3" t="inlineStr">
+        <is>
+          <t>drpoller.com</t>
+        </is>
+      </c>
       <c r="C675" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com/directory/ca/chiropractic-and-spine-cen</t>
+          <t>drpoller.com/us/</t>
         </is>
       </c>
       <c r="D675" t="inlineStr"/>
       <c r="E675" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com</t>
+          <t>drpoller.com</t>
         </is>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>QME, Amin Nia</t>
-        </is>
-      </c>
-      <c r="B676" t="inlineStr"/>
-      <c r="C676" s="3" t="inlineStr">
-        <is>
-          <t>uschirodirectory.com/directory/ca/spectrum-medical-group-inc</t>
-        </is>
-      </c>
+          <t>Putman, Michael</t>
+        </is>
+      </c>
+      <c r="B676" s="3" t="inlineStr">
+        <is>
+          <t>twincreekshealth.com</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr"/>
       <c r="D676" t="inlineStr"/>
       <c r="E676" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com</t>
+          <t>twincreekshealth.com</t>
         </is>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>QME, Daniel Muldavin</t>
+          <t>QME, Ali Mostafavi</t>
         </is>
       </c>
       <c r="B677" t="inlineStr"/>
       <c r="C677" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com/directory/ca/muldavin-chiropractic-elk-</t>
+          <t>uschirodirectory.com/directory/ca/chiropractic-and-spine-cen</t>
         </is>
       </c>
       <c r="D677" t="inlineStr"/>
@@ -14417,13 +14475,13 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>QME, David Conner</t>
+          <t>QME, Amin Nia</t>
         </is>
       </c>
       <c r="B678" t="inlineStr"/>
       <c r="C678" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com/directory/ca/conner-chiropractic-care-c</t>
+          <t>uschirodirectory.com/directory/ca/spectrum-medical-group-inc</t>
         </is>
       </c>
       <c r="D678" t="inlineStr"/>
@@ -14436,13 +14494,13 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>QME, Douglas DeSalvo</t>
+          <t>QME, Daniel Muldavin</t>
         </is>
       </c>
       <c r="B679" t="inlineStr"/>
       <c r="C679" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com/directory/ca/desalvo-chiropractic-injur</t>
+          <t>uschirodirectory.com/directory/ca/muldavin-chiropractic-elk-</t>
         </is>
       </c>
       <c r="D679" t="inlineStr"/>
@@ -14455,13 +14513,13 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>QME, Jonathan Widenbaum</t>
+          <t>QME, David Conner</t>
         </is>
       </c>
       <c r="B680" t="inlineStr"/>
       <c r="C680" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com/directory/ca/widenbaum-chiropractic-all</t>
+          <t>uschirodirectory.com/directory/ca/conner-chiropractic-care-c</t>
         </is>
       </c>
       <c r="D680" t="inlineStr"/>
@@ -14474,13 +14532,13 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>QME, Sayel Fakhoury</t>
+          <t>QME, Douglas DeSalvo</t>
         </is>
       </c>
       <c r="B681" t="inlineStr"/>
       <c r="C681" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com/directory/ca/gentle-touch-chiropractic-</t>
+          <t>uschirodirectory.com/directory/ca/desalvo-chiropractic-injur</t>
         </is>
       </c>
       <c r="D681" t="inlineStr"/>
@@ -14493,13 +14551,13 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>QME, Wendy Chow</t>
+          <t>QME, Jonathan Widenbaum</t>
         </is>
       </c>
       <c r="B682" t="inlineStr"/>
       <c r="C682" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com/directory/ca/chow-chiropractic-el-monte</t>
+          <t>uschirodirectory.com/directory/ca/widenbaum-chiropractic-all</t>
         </is>
       </c>
       <c r="D682" t="inlineStr"/>
@@ -14512,13 +14570,13 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>QME, William Thomas</t>
+          <t>QME, Sayel Fakhoury</t>
         </is>
       </c>
       <c r="B683" t="inlineStr"/>
       <c r="C683" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com/directory/ca/dr-thomas-chiropractic-mas</t>
+          <t>uschirodirectory.com/directory/ca/gentle-touch-chiropractic-</t>
         </is>
       </c>
       <c r="D683" t="inlineStr"/>
@@ -14531,250 +14589,250 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>Razipour, Mitra</t>
-        </is>
-      </c>
-      <c r="B684" s="3" t="inlineStr">
-        <is>
-          <t>doctormitra.com</t>
-        </is>
-      </c>
+          <t>QME, Wendy Chow</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr"/>
       <c r="C684" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com/directory/ca/dr-mitra-razipour-chiropra</t>
+          <t>uschirodirectory.com/directory/ca/chow-chiropractic-el-monte</t>
         </is>
       </c>
       <c r="D684" t="inlineStr"/>
       <c r="E684" s="3" t="inlineStr">
         <is>
-          <t>doctormitra.com</t>
+          <t>uschirodirectory.com</t>
         </is>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>Reiley, James</t>
-        </is>
-      </c>
-      <c r="B685" s="3" t="inlineStr">
-        <is>
-          <t>familyandsportschiropractic.com</t>
-        </is>
-      </c>
+          <t>QME, William Thomas</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr"/>
       <c r="C685" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com/directory/ca/family-and-sports-chiropra</t>
+          <t>uschirodirectory.com/directory/ca/dr-thomas-chiropractic-mas</t>
         </is>
       </c>
       <c r="D685" t="inlineStr"/>
       <c r="E685" s="3" t="inlineStr">
         <is>
-          <t>familyandsportschiropractic.com</t>
+          <t>uschirodirectory.com</t>
         </is>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>Rein, Randy</t>
+          <t>Razipour, Mitra</t>
         </is>
       </c>
       <c r="B686" s="3" t="inlineStr">
         <is>
-          <t>technic.com</t>
+          <t>doctormitra.com</t>
         </is>
       </c>
       <c r="C686" s="3" t="inlineStr">
         <is>
-          <t>technic.com/about/news-events/news/dr-xavier-buch-appointed-</t>
+          <t>uschirodirectory.com/directory/ca/dr-mitra-razipour-chiropra</t>
         </is>
       </c>
       <c r="D686" t="inlineStr"/>
       <c r="E686" s="3" t="inlineStr">
         <is>
-          <t>technic.com</t>
+          <t>doctormitra.com</t>
         </is>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>Reinboldt, Daniel</t>
+          <t>Reiley, James</t>
         </is>
       </c>
       <c r="B687" s="3" t="inlineStr">
         <is>
-          <t>greenvillespineandjoint.com</t>
+          <t>familyandsportschiropractic.com</t>
         </is>
       </c>
       <c r="C687" s="3" t="inlineStr">
         <is>
-          <t>greenvillespineandjoint.com/us/ · greenvillespineandjoint.com/wp-content/uploads/2022/07/2015-</t>
+          <t>uschirodirectory.com/directory/ca/family-and-sports-chiropra</t>
         </is>
       </c>
       <c r="D687" t="inlineStr"/>
       <c r="E687" s="3" t="inlineStr">
         <is>
-          <t>greenvillespineandjoint.com</t>
+          <t>familyandsportschiropractic.com</t>
         </is>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>Rice, Derek</t>
+          <t>Rein, Randy</t>
         </is>
       </c>
       <c r="B688" s="3" t="inlineStr">
         <is>
-          <t>rcwsandiego.com</t>
+          <t>technic.com</t>
         </is>
       </c>
       <c r="C688" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com/directory/ca/rice-chiropractic-and-well</t>
+          <t>technic.com/about/news-events/news/dr-xavier-buch-appointed-</t>
         </is>
       </c>
       <c r="D688" t="inlineStr"/>
       <c r="E688" s="3" t="inlineStr">
         <is>
-          <t>rcwsandiego.com</t>
+          <t>technic.com</t>
         </is>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>Richter, Marielle</t>
-        </is>
-      </c>
-      <c r="B689" t="inlineStr"/>
+          <t>Reinboldt, Daniel</t>
+        </is>
+      </c>
+      <c r="B689" s="3" t="inlineStr">
+        <is>
+          <t>greenvillespineandjoint.com</t>
+        </is>
+      </c>
       <c r="C689" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com/directory/ca/advance-upper-cervical-chi</t>
+          <t>greenvillespineandjoint.com/us/</t>
         </is>
       </c>
       <c r="D689" t="inlineStr"/>
       <c r="E689" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com</t>
+          <t>greenvillespineandjoint.com</t>
         </is>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>Rozenberg, Brigitte</t>
+          <t>Rice, Derek</t>
         </is>
       </c>
       <c r="B690" s="3" t="inlineStr">
         <is>
-          <t>spinatomycenters.com</t>
+          <t>rcwsandiego.com</t>
         </is>
       </c>
       <c r="C690" s="3" t="inlineStr">
         <is>
-          <t>spinatomycenters.com/about/meet-the-doctor/</t>
+          <t>uschirodirectory.com/directory/ca/rice-chiropractic-and-well</t>
         </is>
       </c>
       <c r="D690" t="inlineStr"/>
       <c r="E690" s="3" t="inlineStr">
         <is>
-          <t>spinatomycenters.com</t>
+          <t>rcwsandiego.com</t>
         </is>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>Rundle, Sean</t>
-        </is>
-      </c>
-      <c r="B691" s="3" t="inlineStr">
-        <is>
-          <t>premierchiropracticoc.com</t>
-        </is>
-      </c>
+          <t>Richter, Marielle</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr"/>
       <c r="C691" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com/directory/ca/rundle-chiropractic-laguna</t>
+          <t>uschirodirectory.com/directory/ca/advance-upper-cervical-chi</t>
         </is>
       </c>
       <c r="D691" t="inlineStr"/>
       <c r="E691" s="3" t="inlineStr">
         <is>
-          <t>premierchiropracticoc.com</t>
+          <t>uschirodirectory.com</t>
         </is>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>Salse, David</t>
+          <t>Rozenberg, Brigitte</t>
         </is>
       </c>
       <c r="B692" s="3" t="inlineStr">
         <is>
-          <t>salsechiropractic.com</t>
-        </is>
-      </c>
-      <c r="C692" t="inlineStr"/>
+          <t>spinatomycenters.com</t>
+        </is>
+      </c>
+      <c r="C692" s="3" t="inlineStr">
+        <is>
+          <t>spinatomycenters.com/about/meet-the-doctor/</t>
+        </is>
+      </c>
       <c r="D692" t="inlineStr"/>
       <c r="E692" s="3" t="inlineStr">
         <is>
-          <t>salsechiropractic.com</t>
+          <t>spinatomycenters.com</t>
         </is>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>SARAT, DAVID DE SALVO</t>
-        </is>
-      </c>
-      <c r="B693" t="inlineStr"/>
+          <t>Rundle, Sean</t>
+        </is>
+      </c>
+      <c r="B693" s="3" t="inlineStr">
+        <is>
+          <t>premierchiropracticoc.com</t>
+        </is>
+      </c>
       <c r="C693" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com/directory/ca/saratoga-ave-back-and-neck</t>
+          <t>uschirodirectory.com/directory/ca/rundle-chiropractic-laguna</t>
         </is>
       </c>
       <c r="D693" t="inlineStr"/>
       <c r="E693" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com</t>
+          <t>premierchiropracticoc.com</t>
         </is>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>Shallow, Jordan</t>
+          <t>Salse, David</t>
         </is>
       </c>
       <c r="B694" s="3" t="inlineStr">
         <is>
-          <t>themuscledoc.com</t>
+          <t>salsechiropractic.com</t>
         </is>
       </c>
       <c r="C694" t="inlineStr"/>
       <c r="D694" t="inlineStr"/>
       <c r="E694" s="3" t="inlineStr">
         <is>
-          <t>themuscledoc.com</t>
+          <t>salsechiropractic.com</t>
         </is>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>Shani, Shay</t>
+          <t>SARAT, DAVID DE SALVO</t>
         </is>
       </c>
       <c r="B695" t="inlineStr"/>
       <c r="C695" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com/directory/ca/clear-purpose-chiropractic</t>
+          <t>uschirodirectory.com/directory/ca/saratoga-ave-back-and-neck</t>
         </is>
       </c>
       <c r="D695" t="inlineStr"/>
@@ -14787,135 +14845,131 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>Sheridan, Shamus</t>
+          <t>Shallow, Jordan</t>
         </is>
       </c>
       <c r="B696" s="3" t="inlineStr">
         <is>
-          <t>sheridanchiro.net</t>
+          <t>themuscledoc.com</t>
         </is>
       </c>
       <c r="C696" t="inlineStr"/>
       <c r="D696" t="inlineStr"/>
       <c r="E696" s="3" t="inlineStr">
         <is>
-          <t>sheridanchiro.net</t>
+          <t>themuscledoc.com</t>
         </is>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>Silverman, Steven</t>
-        </is>
-      </c>
-      <c r="B697" s="3" t="inlineStr">
-        <is>
-          <t>ssilvermanchiropractic.com</t>
-        </is>
-      </c>
-      <c r="C697" t="inlineStr"/>
+          <t>Shani, Shay</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr"/>
+      <c r="C697" s="3" t="inlineStr">
+        <is>
+          <t>uschirodirectory.com/directory/ca/clear-purpose-chiropractic</t>
+        </is>
+      </c>
       <c r="D697" t="inlineStr"/>
       <c r="E697" s="3" t="inlineStr">
         <is>
-          <t>ssilvermanchiropractic.com</t>
+          <t>uschirodirectory.com</t>
         </is>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>Smith, Christine</t>
+          <t>Sheridan, Shamus</t>
         </is>
       </c>
       <c r="B698" s="3" t="inlineStr">
         <is>
-          <t>southpaschiro.com</t>
-        </is>
-      </c>
-      <c r="C698" s="3" t="inlineStr">
-        <is>
-          <t>southpaschiro.com/aboutus · uschirodirectory.com/directory/ca/plano-injury-rehab-chiropr</t>
-        </is>
-      </c>
+          <t>sheridanchiro.net</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr"/>
       <c r="D698" t="inlineStr"/>
       <c r="E698" s="3" t="inlineStr">
         <is>
-          <t>southpaschiro.com</t>
+          <t>sheridanchiro.net</t>
         </is>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>Smith, Shain</t>
+          <t>Silverman, Steven</t>
         </is>
       </c>
       <c r="B699" s="3" t="inlineStr">
         <is>
-          <t>luxiamchiropractic.com</t>
+          <t>ssilvermanchiropractic.com</t>
         </is>
       </c>
       <c r="C699" t="inlineStr"/>
       <c r="D699" t="inlineStr"/>
       <c r="E699" s="3" t="inlineStr">
         <is>
-          <t>luxiamchiropractic.com</t>
+          <t>ssilvermanchiropractic.com</t>
         </is>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>Stackwood, Terrance</t>
-        </is>
-      </c>
-      <c r="B700" t="inlineStr"/>
+          <t>Smith, Christine</t>
+        </is>
+      </c>
+      <c r="B700" s="3" t="inlineStr">
+        <is>
+          <t>southpaschiro.com</t>
+        </is>
+      </c>
       <c r="C700" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com/directory/ca/universal-chiropractic-san</t>
+          <t>southpaschiro.com/aboutus · uschirodirectory.com/directory/ca/plano-injury-rehab-chiropr</t>
         </is>
       </c>
       <c r="D700" t="inlineStr"/>
       <c r="E700" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com</t>
+          <t>southpaschiro.com</t>
         </is>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>Steffins, Daniel</t>
+          <t>Smith, Shain</t>
         </is>
       </c>
       <c r="B701" s="3" t="inlineStr">
         <is>
-          <t>chiropracticencinitas.com</t>
-        </is>
-      </c>
-      <c r="C701" s="3" t="inlineStr">
-        <is>
-          <t>chiropracticencinitas.com/encinitas-chiropractor/</t>
-        </is>
-      </c>
+          <t>luxiamchiropractic.com</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr"/>
       <c r="D701" t="inlineStr"/>
       <c r="E701" s="3" t="inlineStr">
         <is>
-          <t>chiropracticencinitas.com</t>
+          <t>luxiamchiropractic.com</t>
         </is>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>Szafranski, Joe</t>
+          <t>Stackwood, Terrance</t>
         </is>
       </c>
       <c r="B702" t="inlineStr"/>
       <c r="C702" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com/directory/ca/summit-chiropractic-massag</t>
+          <t>uschirodirectory.com/directory/ca/universal-chiropractic-san</t>
         </is>
       </c>
       <c r="D702" t="inlineStr"/>
@@ -14928,97 +14982,101 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>Teitelbaum, Jan</t>
+          <t>Steffins, Daniel</t>
         </is>
       </c>
       <c r="B703" s="3" t="inlineStr">
         <is>
-          <t>realchiropractic.com</t>
+          <t>chiropracticencinitas.com</t>
         </is>
       </c>
       <c r="C703" s="3" t="inlineStr">
         <is>
-          <t>realchiropractic.com/meet-dr-jan-teitelbaum/ · uschirodirectory.com/directory/ca/mission-chiropractic-missi</t>
+          <t>chiropracticencinitas.com/encinitas-chiropractor/</t>
         </is>
       </c>
       <c r="D703" t="inlineStr"/>
       <c r="E703" s="3" t="inlineStr">
         <is>
-          <t>realchiropractic.com</t>
+          <t>chiropracticencinitas.com</t>
         </is>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>Thomas, William</t>
-        </is>
-      </c>
-      <c r="B704" s="3" t="inlineStr">
-        <is>
-          <t>drtchiro.com</t>
-        </is>
-      </c>
+          <t>Szafranski, Joe</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr"/>
       <c r="C704" s="3" t="inlineStr">
         <is>
-          <t>drtchiro.com/Documents/Whiplash · drtchiro.com/CV%20-%20DrT.htm</t>
+          <t>uschirodirectory.com/directory/ca/summit-chiropractic-massag</t>
         </is>
       </c>
       <c r="D704" t="inlineStr"/>
       <c r="E704" s="3" t="inlineStr">
         <is>
-          <t>drtchiro.com</t>
+          <t>uschirodirectory.com</t>
         </is>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>Toth-Tevel, Tas</t>
-        </is>
-      </c>
-      <c r="B705" t="inlineStr"/>
+          <t>Teitelbaum, Jan</t>
+        </is>
+      </c>
+      <c r="B705" s="3" t="inlineStr">
+        <is>
+          <t>realchiropractic.com</t>
+        </is>
+      </c>
       <c r="C705" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com/directory/ca/tevel-chiropractic-thousnd</t>
+          <t>realchiropractic.com/meet-dr-jan-teitelbaum/ · uschirodirectory.com/directory/ca/mission-chiropractic-missi</t>
         </is>
       </c>
       <c r="D705" t="inlineStr"/>
       <c r="E705" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com</t>
+          <t>realchiropractic.com</t>
         </is>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>Vernon, Ronald</t>
-        </is>
-      </c>
-      <c r="B706" t="inlineStr"/>
+          <t>Thomas, William</t>
+        </is>
+      </c>
+      <c r="B706" s="3" t="inlineStr">
+        <is>
+          <t>drtchiro.com</t>
+        </is>
+      </c>
       <c r="C706" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com/directory/ca/nonsurgical-pain-relief-ce</t>
+          <t>drtchiro.com/Documents/Whiplash</t>
         </is>
       </c>
       <c r="D706" t="inlineStr"/>
       <c r="E706" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com</t>
+          <t>drtchiro.com</t>
         </is>
       </c>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>Wang, Timothy</t>
+          <t>Toth-Tevel, Tas</t>
         </is>
       </c>
       <c r="B707" t="inlineStr"/>
       <c r="C707" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com/directory/ca/add-life-chiropractic-menl · uschirodirectory.com/directory/ca/pain-relief-chiropractic-c</t>
+          <t>uschirodirectory.com/directory/ca/tevel-chiropractic-thousnd</t>
         </is>
       </c>
       <c r="D707" t="inlineStr"/>
@@ -15031,741 +15089,798 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>Warren, Austin</t>
-        </is>
-      </c>
-      <c r="B708" s="3" t="inlineStr">
-        <is>
-          <t>coastphysicalmedicine.com</t>
-        </is>
-      </c>
-      <c r="C708" t="inlineStr"/>
+          <t>Vernon, Ronald</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr"/>
+      <c r="C708" s="3" t="inlineStr">
+        <is>
+          <t>uschirodirectory.com/directory/ca/nonsurgical-pain-relief-ce</t>
+        </is>
+      </c>
       <c r="D708" t="inlineStr"/>
       <c r="E708" s="3" t="inlineStr">
         <is>
-          <t>coastphysicalmedicine.com</t>
+          <t>uschirodirectory.com</t>
         </is>
       </c>
     </row>
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>Warren, John</t>
-        </is>
-      </c>
-      <c r="B709" s="3" t="inlineStr">
-        <is>
-          <t>coastphysicalmedicine.com</t>
-        </is>
-      </c>
+          <t>Wang, Timothy</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr"/>
       <c r="C709" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com/directory/ca/physical-medicine-clinic-o</t>
+          <t>uschirodirectory.com/directory/ca/add-life-chiropractic-menl · uschirodirectory.com/directory/ca/pain-relief-chiropractic-c</t>
         </is>
       </c>
       <c r="D709" t="inlineStr"/>
       <c r="E709" s="3" t="inlineStr">
         <is>
-          <t>coastphysicalmedicine.com</t>
+          <t>uschirodirectory.com</t>
         </is>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>Weed, Douglas</t>
-        </is>
-      </c>
-      <c r="B710" t="inlineStr"/>
-      <c r="C710" s="3" t="inlineStr">
-        <is>
-          <t>uschirodirectory.com/directory/ca/richard-r-chaney-dc-fairfi</t>
-        </is>
-      </c>
+          <t>Warren, Austin</t>
+        </is>
+      </c>
+      <c r="B710" s="3" t="inlineStr">
+        <is>
+          <t>coastphysicalmedicine.com</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr"/>
       <c r="D710" t="inlineStr"/>
       <c r="E710" s="3" t="inlineStr">
         <is>
-          <t>uschirodirectory.com</t>
+          <t>coastphysicalmedicine.com</t>
         </is>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>Whalen, Wayne</t>
+          <t>Warren, John</t>
         </is>
       </c>
       <c r="B711" s="3" t="inlineStr">
         <is>
-          <t>drwhalen.com</t>
+          <t>coastphysicalmedicine.com</t>
         </is>
       </c>
       <c r="C711" s="3" t="inlineStr">
         <is>
-          <t>drwhalen.com/meet-the-doctors/ · drwhalen.com/meet-the-doctors/curriculum-vitae/</t>
+          <t>uschirodirectory.com/directory/ca/physical-medicine-clinic-o</t>
         </is>
       </c>
       <c r="D711" t="inlineStr"/>
       <c r="E711" s="3" t="inlineStr">
         <is>
-          <t>drwhalen.com</t>
+          <t>coastphysicalmedicine.com</t>
         </is>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>Williamson, John</t>
-        </is>
-      </c>
-      <c r="B712" s="3" t="inlineStr">
-        <is>
-          <t>williamsonchiropractic.co.uk</t>
-        </is>
-      </c>
+          <t>Weed, Douglas</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr"/>
       <c r="C712" s="3" t="inlineStr">
         <is>
-          <t>williamsonchiropractic.co.uk/jill-williamson</t>
+          <t>uschirodirectory.com/directory/ca/richard-r-chaney-dc-fairfi</t>
         </is>
       </c>
       <c r="D712" t="inlineStr"/>
       <c r="E712" s="3" t="inlineStr">
         <is>
-          <t>williamsonchiropractic.co.uk</t>
+          <t>uschirodirectory.com</t>
         </is>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>Witness, Roger Clifford Expert</t>
-        </is>
-      </c>
-      <c r="B713" t="inlineStr"/>
-      <c r="C713" t="inlineStr"/>
+          <t>Whalen, Wayne</t>
+        </is>
+      </c>
+      <c r="B713" s="3" t="inlineStr">
+        <is>
+          <t>drwhalen.com</t>
+        </is>
+      </c>
+      <c r="C713" s="3" t="inlineStr">
+        <is>
+          <t>drwhalen.com/meet-the-doctors/</t>
+        </is>
+      </c>
       <c r="D713" t="inlineStr"/>
-      <c r="E713" t="inlineStr"/>
+      <c r="E713" s="3" t="inlineStr">
+        <is>
+          <t>drwhalen.com</t>
+        </is>
+      </c>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>Zollner, Charles</t>
+          <t>Williamson, John</t>
         </is>
       </c>
       <c r="B714" s="3" t="inlineStr">
         <is>
-          <t>drzollner.com</t>
+          <t>williamsonchiropractic.co.uk</t>
         </is>
       </c>
       <c r="C714" s="3" t="inlineStr">
         <is>
-          <t>drzollner.com/about-dr-zollner/ · uschirodirectory.com/directory/ca/ohio-spine-and-injury-cent</t>
+          <t>williamsonchiropractic.co.uk/jill-williamson</t>
         </is>
       </c>
       <c r="D714" t="inlineStr"/>
       <c r="E714" s="3" t="inlineStr">
         <is>
-          <t>drzollner.com</t>
+          <t>williamsonchiropractic.co.uk</t>
         </is>
       </c>
     </row>
     <row r="715">
-      <c r="A715" s="4" t="inlineStr">
-        <is>
-          <t>Clinics, schools and other organizations</t>
-        </is>
-      </c>
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>Witness, Roger Clifford Expert</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr"/>
+      <c r="C715" t="inlineStr"/>
+      <c r="D715" t="inlineStr"/>
+      <c r="E715" t="inlineStr"/>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>A New Chiropractic</t>
-        </is>
-      </c>
-      <c r="B716" t="inlineStr"/>
-      <c r="C716" t="inlineStr"/>
-      <c r="D716" s="3" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="E716" t="inlineStr"/>
+          <t>Zollner, Charles</t>
+        </is>
+      </c>
+      <c r="B716" s="3" t="inlineStr">
+        <is>
+          <t>drzollner.com</t>
+        </is>
+      </c>
+      <c r="C716" s="3" t="inlineStr">
+        <is>
+          <t>drzollner.com/about-dr-zollner/ · uschirodirectory.com/directory/ca/ohio-spine-and-injury-cent</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr"/>
+      <c r="E716" s="3" t="inlineStr">
+        <is>
+          <t>drzollner.com</t>
+        </is>
+      </c>
     </row>
     <row r="717">
-      <c r="A717" t="inlineStr">
-        <is>
-          <t>Baek'S Chiropractic Health Center, Inc</t>
-        </is>
-      </c>
-      <c r="B717" s="3" t="inlineStr">
-        <is>
-          <t>baekschiropractic.com</t>
-        </is>
-      </c>
-      <c r="C717" t="inlineStr"/>
-      <c r="D717" t="inlineStr"/>
-      <c r="E717" s="3" t="inlineStr">
-        <is>
-          <t>baekschiropractic.com</t>
+      <c r="A717" s="4" t="inlineStr">
+        <is>
+          <t>Clinics, schools and other organizations</t>
         </is>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>Baeks Chiropractic Health Center</t>
-        </is>
-      </c>
-      <c r="B718" s="3" t="inlineStr">
-        <is>
-          <t>baekschiropractic.com</t>
-        </is>
-      </c>
+          <t>A New Chiropractic</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr"/>
       <c r="C718" t="inlineStr"/>
-      <c r="D718" t="inlineStr"/>
-      <c r="E718" s="3" t="inlineStr">
-        <is>
-          <t>baekschiropractic.com</t>
-        </is>
-      </c>
+      <c r="D718" s="3" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E718" t="inlineStr"/>
     </row>
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>Brennan Chiropractic Inc</t>
+          <t>Baek'S Chiropractic Health Center, Inc</t>
         </is>
       </c>
       <c r="B719" s="3" t="inlineStr">
         <is>
-          <t>peaksportschiro.janeapp.com</t>
+          <t>baekschiropractic.com</t>
         </is>
       </c>
       <c r="C719" t="inlineStr"/>
       <c r="D719" t="inlineStr"/>
       <c r="E719" s="3" t="inlineStr">
         <is>
-          <t>peaksportschiro.janeapp.com</t>
+          <t>baekschiropractic.com</t>
         </is>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>Bridgwater Chiropractic Clinic (practitioner not named</t>
+          <t>Baeks Chiropractic Health Center</t>
         </is>
       </c>
       <c r="B720" s="3" t="inlineStr">
         <is>
-          <t>bridgwaterchiropracticclinic.com</t>
+          <t>baekschiropractic.com</t>
         </is>
       </c>
       <c r="C720" t="inlineStr"/>
       <c r="D720" t="inlineStr"/>
       <c r="E720" s="3" t="inlineStr">
         <is>
-          <t>bridgwaterchiropracticclinic.com</t>
+          <t>baekschiropractic.com</t>
         </is>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>Cool Chiropractic, Sacramento</t>
+          <t>Brennan Chiropractic Inc</t>
         </is>
       </c>
       <c r="B721" s="3" t="inlineStr">
         <is>
-          <t>coolchiropracticsac.com</t>
-        </is>
-      </c>
-      <c r="C721" s="3" t="inlineStr">
-        <is>
-          <t>coolchiropracticsac.com/meet-the-team</t>
-        </is>
-      </c>
+          <t>peaksportschiro.janeapp.com</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr"/>
       <c r="D721" t="inlineStr"/>
       <c r="E721" s="3" t="inlineStr">
         <is>
-          <t>coolchiropracticsac.com</t>
+          <t>peaksportschiro.janeapp.com</t>
         </is>
       </c>
     </row>
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>Dr. Julie O'Shaughnessy - Restorative Care Chiropractic</t>
+          <t>Bridgwater Chiropractic Clinic (practitioner not named</t>
         </is>
       </c>
       <c r="B722" s="3" t="inlineStr">
         <is>
-          <t>restorativecarechiropractic.com</t>
-        </is>
-      </c>
-      <c r="C722" s="3" t="inlineStr">
-        <is>
-          <t>restorativecarechiropractic.janeapp.com/</t>
-        </is>
-      </c>
+          <t>bridgwaterchiropracticclinic.com</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr"/>
       <c r="D722" t="inlineStr"/>
       <c r="E722" s="3" t="inlineStr">
         <is>
-          <t>restorativecarechiropractic.com</t>
+          <t>bridgwaterchiropracticclinic.com</t>
         </is>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>Eiler Chiropractic, Omaha - NMR page</t>
-        </is>
-      </c>
-      <c r="B723" t="inlineStr"/>
+          <t>Cool Chiropractic, Sacramento</t>
+        </is>
+      </c>
+      <c r="B723" s="3" t="inlineStr">
+        <is>
+          <t>coolchiropracticsac.com</t>
+        </is>
+      </c>
       <c r="C723" s="3" t="inlineStr">
         <is>
-          <t>eilerchiro.com/neuromuscular-reeducation/</t>
+          <t>coolchiropracticsac.com/meet-the-team</t>
         </is>
       </c>
       <c r="D723" t="inlineStr"/>
       <c r="E723" s="3" t="inlineStr">
         <is>
-          <t>eilerchiro.com</t>
+          <t>coolchiropracticsac.com</t>
         </is>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>Elite Spinal &amp; Sports Care, Inc.</t>
+          <t>Dr. Julie O'Shaughnessy - Restorative Care Chiropractic</t>
         </is>
       </c>
       <c r="B724" s="3" t="inlineStr">
         <is>
-          <t>elitespinalcare.com</t>
+          <t>restorativecarechiropractic.com</t>
         </is>
       </c>
       <c r="C724" s="3" t="inlineStr">
         <is>
-          <t>elitespinalcare.com/staff/justin-lau/</t>
+          <t>restorativecarechiropractic.janeapp.com/</t>
         </is>
       </c>
       <c r="D724" t="inlineStr"/>
       <c r="E724" s="3" t="inlineStr">
         <is>
-          <t>elitespinalcare.com</t>
+          <t>restorativecarechiropractic.com</t>
         </is>
       </c>
     </row>
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>Hayes Sports Chiropractic Inc</t>
-        </is>
-      </c>
-      <c r="B725" s="3" t="inlineStr">
-        <is>
-          <t>hayessportschiropractic.com</t>
-        </is>
-      </c>
+          <t>Eiler Chiropractic, Omaha - NMR page</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr"/>
       <c r="C725" s="3" t="inlineStr">
         <is>
-          <t>hayessportschiropractic.com/about/ · hayessportschiropractic.com/about/dr-fred-hayes/</t>
+          <t>eilerchiro.com/neuromuscular-reeducation/</t>
         </is>
       </c>
       <c r="D725" t="inlineStr"/>
       <c r="E725" s="3" t="inlineStr">
         <is>
-          <t>hayessportschiropractic.com</t>
+          <t>eilerchiro.com</t>
         </is>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>Inner-Action Sports Rehab Chiropractic - ART page</t>
-        </is>
-      </c>
-      <c r="B726" t="inlineStr"/>
+          <t>Elite Spinal &amp; Sports Care, Inc.</t>
+        </is>
+      </c>
+      <c r="B726" s="3" t="inlineStr">
+        <is>
+          <t>elitespinalcare.com</t>
+        </is>
+      </c>
       <c r="C726" s="3" t="inlineStr">
         <is>
-          <t>inner-actionchiro.com/services-at-inner-action-sports-rehab-</t>
+          <t>elitespinalcare.com/staff/justin-lau/</t>
         </is>
       </c>
       <c r="D726" t="inlineStr"/>
       <c r="E726" s="3" t="inlineStr">
         <is>
-          <t>inner-actionchiro.com</t>
+          <t>elitespinalcare.com</t>
         </is>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>Inspired Physical Therapy</t>
+          <t>Hayes Sports Chiropractic Inc</t>
         </is>
       </c>
       <c r="B727" s="3" t="inlineStr">
         <is>
-          <t>inspiredtherapy.com</t>
+          <t>hayessportschiropractic.com</t>
         </is>
       </c>
       <c r="C727" s="3" t="inlineStr">
         <is>
-          <t>inspiredtherapy.com/our-services/neuromuscular-re-education</t>
+          <t>hayessportschiropractic.com/about/ · hayessportschiropractic.com/about/dr-fred-hayes/</t>
         </is>
       </c>
       <c r="D727" t="inlineStr"/>
       <c r="E727" s="3" t="inlineStr">
         <is>
-          <t>inspiredtherapy.com</t>
+          <t>hayessportschiropractic.com</t>
         </is>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>Kenneth M. Toy A Professional Chiropractic Corporation</t>
-        </is>
-      </c>
-      <c r="B728" s="3" t="inlineStr">
-        <is>
-          <t>devandannychiropractic.janeapp.com</t>
-        </is>
-      </c>
-      <c r="C728" t="inlineStr"/>
+          <t>Injury and Spinecare Chiropractic, La Crescenta</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr"/>
+      <c r="C728" s="3" t="inlineStr">
+        <is>
+          <t>injuryandspinecare.com/about</t>
+        </is>
+      </c>
       <c r="D728" t="inlineStr"/>
       <c r="E728" s="3" t="inlineStr">
         <is>
-          <t>devandannychiropractic.janeapp.com</t>
+          <t>injuryandspinecare.com</t>
         </is>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>Kings Chiropractic</t>
-        </is>
-      </c>
-      <c r="B729" s="3" t="inlineStr">
-        <is>
-          <t>kingschiropractic.com</t>
-        </is>
-      </c>
-      <c r="C729" t="inlineStr"/>
+          <t>Inner-Action Sports Rehab Chiropractic - ART page</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr"/>
+      <c r="C729" s="3" t="inlineStr">
+        <is>
+          <t>inner-actionchiro.com/services-at-inner-action-sports-rehab-</t>
+        </is>
+      </c>
       <c r="D729" t="inlineStr"/>
       <c r="E729" s="3" t="inlineStr">
         <is>
-          <t>kingschiropractic.com</t>
+          <t>inner-actionchiro.com</t>
         </is>
       </c>
     </row>
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>Kraus Chiropractic Inc.</t>
+          <t>Inspired Physical Therapy</t>
         </is>
       </c>
       <c r="B730" s="3" t="inlineStr">
         <is>
-          <t>krauschiropractic.com</t>
-        </is>
-      </c>
-      <c r="C730" t="inlineStr"/>
+          <t>inspiredtherapy.com</t>
+        </is>
+      </c>
+      <c r="C730" s="3" t="inlineStr">
+        <is>
+          <t>inspiredtherapy.com/our-services/neuromuscular-re-education</t>
+        </is>
+      </c>
       <c r="D730" t="inlineStr"/>
       <c r="E730" s="3" t="inlineStr">
         <is>
-          <t>krauschiropractic.com</t>
+          <t>inspiredtherapy.com</t>
         </is>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>Magale Chiropractic Inc., A Prof. Corp.</t>
+          <t>Kenneth M. Toy A Professional Chiropractic Corporation</t>
         </is>
       </c>
       <c r="B731" s="3" t="inlineStr">
         <is>
-          <t>activelifesac.com</t>
-        </is>
-      </c>
-      <c r="C731" s="3" t="inlineStr">
-        <is>
-          <t>activelifesac.com/about · activelifesac.com/meet-the-doctor · activelifesac.com/staff</t>
-        </is>
-      </c>
+          <t>devandannychiropractic.janeapp.com</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr"/>
       <c r="D731" t="inlineStr"/>
       <c r="E731" s="3" t="inlineStr">
         <is>
-          <t>activelifesac.com</t>
+          <t>devandannychiropractic.janeapp.com</t>
         </is>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>Maio (first name not captured</t>
+          <t>Kings Chiropractic</t>
         </is>
       </c>
       <c r="B732" s="3" t="inlineStr">
         <is>
-          <t>northeastcollege.edu</t>
+          <t>kingschiropractic.com</t>
         </is>
       </c>
       <c r="C732" t="inlineStr"/>
       <c r="D732" t="inlineStr"/>
       <c r="E732" s="3" t="inlineStr">
         <is>
-          <t>northeastcollege.edu</t>
+          <t>kingschiropractic.com</t>
         </is>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>Maio, Dr - Northeast College bio PDF</t>
-        </is>
-      </c>
-      <c r="B733" t="inlineStr"/>
-      <c r="C733" s="3" t="inlineStr">
-        <is>
-          <t>northeastcollege.edu/pdfs/who-is-nycc/maio.pdf</t>
-        </is>
-      </c>
+          <t>Kraus Chiropractic Inc.</t>
+        </is>
+      </c>
+      <c r="B733" s="3" t="inlineStr">
+        <is>
+          <t>krauschiropractic.com</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr"/>
       <c r="D733" t="inlineStr"/>
       <c r="E733" s="3" t="inlineStr">
         <is>
-          <t>northeastcollege.edu</t>
+          <t>krauschiropractic.com</t>
         </is>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>Natural Health Chiropractic PC</t>
-        </is>
-      </c>
-      <c r="B734" t="inlineStr"/>
+          <t>Magale Chiropractic Inc., A Prof. Corp.</t>
+        </is>
+      </c>
+      <c r="B734" s="3" t="inlineStr">
+        <is>
+          <t>activelifesac.com</t>
+        </is>
+      </c>
       <c r="C734" s="3" t="inlineStr">
         <is>
-          <t>naturalhealthchiropracticpc.com/</t>
+          <t>activelifesac.com/about · activelifesac.com/meet-the-doctor · activelifesac.com/staff</t>
         </is>
       </c>
       <c r="D734" t="inlineStr"/>
       <c r="E734" s="3" t="inlineStr">
         <is>
-          <t>naturalhealthchiropracticpc.com</t>
+          <t>activelifesac.com</t>
         </is>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>P2 Sports Care</t>
+          <t>Maio (first name not captured</t>
         </is>
       </c>
       <c r="B735" s="3" t="inlineStr">
         <is>
-          <t>p2sportscare.com</t>
-        </is>
-      </c>
-      <c r="C735" s="3" t="inlineStr">
-        <is>
-          <t>p2sportscare.com/team</t>
-        </is>
-      </c>
+          <t>northeastcollege.edu</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr"/>
       <c r="D735" t="inlineStr"/>
       <c r="E735" s="3" t="inlineStr">
         <is>
-          <t>p2sportscare.com</t>
+          <t>northeastcollege.edu</t>
         </is>
       </c>
     </row>
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>Palmer College of Chiropractic Continuing Education</t>
-        </is>
-      </c>
-      <c r="B736" s="3" t="inlineStr">
-        <is>
-          <t>palmer.edu</t>
-        </is>
-      </c>
+          <t>Maio, Dr - Northeast College bio PDF</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr"/>
       <c r="C736" s="3" t="inlineStr">
         <is>
-          <t>palmer.edu/continuing-education/</t>
+          <t>northeastcollege.edu/pdfs/who-is-nycc/maio.pdf</t>
         </is>
       </c>
       <c r="D736" t="inlineStr"/>
       <c r="E736" s="3" t="inlineStr">
         <is>
-          <t>palmer.edu</t>
+          <t>northeastcollege.edu</t>
         </is>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>Pathways to Health (David Marquis, DC</t>
+          <t>Natural Health Chiropractic PC</t>
         </is>
       </c>
       <c r="B737" t="inlineStr"/>
       <c r="C737" s="3" t="inlineStr">
         <is>
-          <t>bestprosintown.com/ca/pismo-beach/pathways-to-health-marquis</t>
+          <t>naturalhealthchiropracticpc.com/</t>
         </is>
       </c>
       <c r="D737" t="inlineStr"/>
       <c r="E737" s="3" t="inlineStr">
         <is>
-          <t>bestprosintown.com</t>
+          <t>naturalhealthchiropracticpc.com</t>
         </is>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>Pathways to Health (Marquis, David</t>
+          <t>P2 Sports Care</t>
         </is>
       </c>
       <c r="B738" s="3" t="inlineStr">
         <is>
-          <t>pathwaystohealth.net</t>
+          <t>p2sportscare.com</t>
         </is>
       </c>
       <c r="C738" s="3" t="inlineStr">
         <is>
-          <t>pathwaystohealth.net/nmr</t>
+          <t>p2sportscare.com/team</t>
         </is>
       </c>
       <c r="D738" t="inlineStr"/>
       <c r="E738" s="3" t="inlineStr">
         <is>
-          <t>pathwaystohealth.net</t>
+          <t>p2sportscare.com</t>
         </is>
       </c>
     </row>
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>Pure Family Chiropractic, Brookfield WI - techniques</t>
-        </is>
-      </c>
-      <c r="B739" t="inlineStr"/>
+          <t>Palmer College of Chiropractic Continuing Education</t>
+        </is>
+      </c>
+      <c r="B739" s="3" t="inlineStr">
+        <is>
+          <t>palmer.edu</t>
+        </is>
+      </c>
       <c r="C739" s="3" t="inlineStr">
         <is>
-          <t>purefamilychiro.com/techniques-and-therapies/</t>
+          <t>palmer.edu/continuing-education/</t>
         </is>
       </c>
       <c r="D739" t="inlineStr"/>
       <c r="E739" s="3" t="inlineStr">
         <is>
-          <t>purefamilychiro.com</t>
+          <t>palmer.edu</t>
         </is>
       </c>
     </row>
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>Roberto Rivera Chiropractic P.C</t>
-        </is>
-      </c>
-      <c r="B740" s="3" t="inlineStr">
-        <is>
-          <t>movementinstitution.janeapp.com</t>
-        </is>
-      </c>
-      <c r="C740" t="inlineStr"/>
+          <t>Pathways to Health (David Marquis, DC</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr"/>
+      <c r="C740" s="3" t="inlineStr">
+        <is>
+          <t>bestprosintown.com/ca/pismo-beach/pathways-to-health-marquis</t>
+        </is>
+      </c>
       <c r="D740" t="inlineStr"/>
       <c r="E740" s="3" t="inlineStr">
         <is>
-          <t>movementinstitution.janeapp.com</t>
+          <t>bestprosintown.com</t>
         </is>
       </c>
     </row>
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>Rockenmacher Chiropractic</t>
+          <t>Pathways to Health (Marquis, David</t>
         </is>
       </c>
       <c r="B741" s="3" t="inlineStr">
         <is>
-          <t>rockenmacherchiropractic.com</t>
+          <t>pathwaystohealth.net</t>
         </is>
       </c>
       <c r="C741" s="3" t="inlineStr">
         <is>
-          <t>rockenmacherchiropractic.com/about-us.html · rockenmacherchiropractic.com/meet-the-chiropractor.html · rockenmacherchiropractic.com/about-us/meet-our-team.html</t>
+          <t>pathwaystohealth.net/nmr</t>
         </is>
       </c>
       <c r="D741" t="inlineStr"/>
       <c r="E741" s="3" t="inlineStr">
         <is>
-          <t>rockenmacherchiropractic.com</t>
+          <t>pathwaystohealth.net</t>
         </is>
       </c>
     </row>
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>Roy Page</t>
-        </is>
-      </c>
-      <c r="B742" s="3" t="inlineStr">
-        <is>
-          <t>lasportsandspine.janeapp.com</t>
-        </is>
-      </c>
-      <c r="C742" t="inlineStr"/>
+          <t>Pure Family Chiropractic, Brookfield WI - techniques</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr"/>
+      <c r="C742" s="3" t="inlineStr">
+        <is>
+          <t>purefamilychiro.com/techniques-and-therapies/</t>
+        </is>
+      </c>
       <c r="D742" t="inlineStr"/>
       <c r="E742" s="3" t="inlineStr">
         <is>
-          <t>lasportsandspine.janeapp.com</t>
+          <t>purefamilychiro.com</t>
         </is>
       </c>
     </row>
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>Sacramento Chiropractic</t>
+          <t>Roberto Rivera Chiropractic P.C</t>
         </is>
       </c>
       <c r="B743" s="3" t="inlineStr">
         <is>
-          <t>sacramentochiropractic.com</t>
-        </is>
-      </c>
-      <c r="C743" s="3" t="inlineStr">
-        <is>
-          <t>sacramentochiropractic.com/us/ · sacramentochiropractic.com/team/</t>
-        </is>
-      </c>
+          <t>movementinstitution.janeapp.com</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr"/>
       <c r="D743" t="inlineStr"/>
       <c r="E743" s="3" t="inlineStr">
         <is>
-          <t>sacramentochiropractic.com</t>
+          <t>movementinstitution.janeapp.com</t>
         </is>
       </c>
     </row>
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>Sam C Ho, A Professional Chiropractic Corporation</t>
+          <t>Rockenmacher Chiropractic</t>
         </is>
       </c>
       <c r="B744" s="3" t="inlineStr">
         <is>
-          <t>mychiroplus.com</t>
+          <t>rockenmacherchiropractic.com</t>
         </is>
       </c>
       <c r="C744" s="3" t="inlineStr">
         <is>
-          <t>mychiroplus.com/about-us</t>
+          <t>rockenmacherchiropractic.com/about-us.html · rockenmacherchiropractic.com/meet-the-chiropractor.html · rockenmacherchiropractic.com/about-us/meet-our-team.html</t>
         </is>
       </c>
       <c r="D744" t="inlineStr"/>
       <c r="E744" s="3" t="inlineStr">
+        <is>
+          <t>rockenmacherchiropractic.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>Roy Page</t>
+        </is>
+      </c>
+      <c r="B745" s="3" t="inlineStr">
+        <is>
+          <t>lasportsandspine.janeapp.com</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr"/>
+      <c r="D745" t="inlineStr"/>
+      <c r="E745" s="3" t="inlineStr">
+        <is>
+          <t>lasportsandspine.janeapp.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>Sacramento Chiropractic</t>
+        </is>
+      </c>
+      <c r="B746" s="3" t="inlineStr">
+        <is>
+          <t>sacramentochiropractic.com</t>
+        </is>
+      </c>
+      <c r="C746" s="3" t="inlineStr">
+        <is>
+          <t>sacramentochiropractic.com/us/ · sacramentochiropractic.com/team/</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr"/>
+      <c r="E746" s="3" t="inlineStr">
+        <is>
+          <t>sacramentochiropractic.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>Sam C Ho, A Professional Chiropractic Corporation</t>
+        </is>
+      </c>
+      <c r="B747" s="3" t="inlineStr">
+        <is>
+          <t>mychiroplus.com</t>
+        </is>
+      </c>
+      <c r="C747" s="3" t="inlineStr">
+        <is>
+          <t>mychiroplus.com/about-us</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr"/>
+      <c r="E747" s="3" t="inlineStr">
         <is>
           <t>mychiroplus.com</t>
         </is>
@@ -17133,18 +17248,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E609" r:id="rId1358"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C610" r:id="rId1359"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E610" r:id="rId1360"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B611" r:id="rId1361"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C611" r:id="rId1362"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E611" r:id="rId1363"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B612" r:id="rId1364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C611" r:id="rId1361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E611" r:id="rId1362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B612" r:id="rId1363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C612" r:id="rId1364"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E612" r:id="rId1365"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B613" r:id="rId1366"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E613" r:id="rId1367"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C614" r:id="rId1368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B614" r:id="rId1368"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E614" r:id="rId1369"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B615" r:id="rId1370"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C615" r:id="rId1371"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E615" r:id="rId1372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C615" r:id="rId1370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E615" r:id="rId1371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B616" r:id="rId1372"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C616" r:id="rId1373"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E616" r:id="rId1374"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C617" r:id="rId1375"/>
@@ -17153,31 +17268,31 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E618" r:id="rId1378"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C619" r:id="rId1379"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E619" r:id="rId1380"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B620" r:id="rId1381"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C620" r:id="rId1382"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E620" r:id="rId1383"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B621" r:id="rId1384"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C621" r:id="rId1385"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E621" r:id="rId1386"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B622" r:id="rId1387"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C622" r:id="rId1388"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E622" r:id="rId1389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C620" r:id="rId1381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E620" r:id="rId1382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B621" r:id="rId1383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C621" r:id="rId1384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E621" r:id="rId1385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B622" r:id="rId1386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C622" r:id="rId1387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E622" r:id="rId1388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B623" r:id="rId1389"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C623" r:id="rId1390"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E623" r:id="rId1391"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B624" r:id="rId1392"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C624" r:id="rId1393"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E624" r:id="rId1394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C624" r:id="rId1392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E624" r:id="rId1393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B625" r:id="rId1394"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C625" r:id="rId1395"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E625" r:id="rId1396"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B626" r:id="rId1397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C626" r:id="rId1397"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E626" r:id="rId1398"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C627" r:id="rId1399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B627" r:id="rId1399"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E627" r:id="rId1400"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B628" r:id="rId1401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C628" r:id="rId1401"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E628" r:id="rId1402"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B629" r:id="rId1403"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C629" r:id="rId1404"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E629" r:id="rId1405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E629" r:id="rId1404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B630" r:id="rId1405"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C630" r:id="rId1406"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E630" r:id="rId1407"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C631" r:id="rId1408"/>
@@ -17186,23 +17301,23 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E632" r:id="rId1411"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C633" r:id="rId1412"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E633" r:id="rId1413"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B634" r:id="rId1414"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C634" r:id="rId1415"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E634" r:id="rId1416"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B635" r:id="rId1417"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C635" r:id="rId1418"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E635" r:id="rId1419"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B636" r:id="rId1420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C634" r:id="rId1414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E634" r:id="rId1415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B635" r:id="rId1416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C635" r:id="rId1417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E635" r:id="rId1418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B636" r:id="rId1419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C636" r:id="rId1420"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E636" r:id="rId1421"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B637" r:id="rId1422"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C637" r:id="rId1423"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E637" r:id="rId1424"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B638" r:id="rId1425"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C638" r:id="rId1426"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E638" r:id="rId1427"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B639" r:id="rId1428"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C639" r:id="rId1429"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E639" r:id="rId1430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E637" r:id="rId1423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B638" r:id="rId1424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C638" r:id="rId1425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E638" r:id="rId1426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B639" r:id="rId1427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C639" r:id="rId1428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E639" r:id="rId1429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B640" r:id="rId1430"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C640" r:id="rId1431"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E640" r:id="rId1432"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C641" r:id="rId1433"/>
@@ -17213,80 +17328,80 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E643" r:id="rId1438"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C644" r:id="rId1439"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E644" r:id="rId1440"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B645" r:id="rId1441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C645" r:id="rId1441"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E645" r:id="rId1442"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C646" r:id="rId1443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B646" r:id="rId1443"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E646" r:id="rId1444"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B647" r:id="rId1445"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C647" r:id="rId1446"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E647" r:id="rId1447"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B648" r:id="rId1448"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C648" r:id="rId1449"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E648" r:id="rId1450"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B649" r:id="rId1451"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C649" r:id="rId1452"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E649" r:id="rId1453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C647" r:id="rId1445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E647" r:id="rId1446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B648" r:id="rId1447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C648" r:id="rId1448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E648" r:id="rId1449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B649" r:id="rId1450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C649" r:id="rId1451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E649" r:id="rId1452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B650" r:id="rId1453"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C650" r:id="rId1454"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E650" r:id="rId1455"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B651" r:id="rId1456"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C651" r:id="rId1457"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E651" r:id="rId1458"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B652" r:id="rId1459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C651" r:id="rId1456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E651" r:id="rId1457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B652" r:id="rId1458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C652" r:id="rId1459"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E652" r:id="rId1460"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B653" r:id="rId1461"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C653" r:id="rId1462"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E653" r:id="rId1463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E653" r:id="rId1462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B654" r:id="rId1463"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C654" r:id="rId1464"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E654" r:id="rId1465"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B655" r:id="rId1466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C655" r:id="rId1466"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E655" r:id="rId1467"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C656" r:id="rId1468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B656" r:id="rId1468"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E656" r:id="rId1469"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B657" r:id="rId1470"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C657" r:id="rId1471"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E657" r:id="rId1472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C657" r:id="rId1470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E657" r:id="rId1471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B658" r:id="rId1472"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C658" r:id="rId1473"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E658" r:id="rId1474"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B659" r:id="rId1475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C659" r:id="rId1475"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E659" r:id="rId1476"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C660" r:id="rId1477"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E660" r:id="rId1478"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C661" r:id="rId1479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B661" r:id="rId1479"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E661" r:id="rId1480"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B662" r:id="rId1481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C662" r:id="rId1481"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E662" r:id="rId1482"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B663" r:id="rId1483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C663" r:id="rId1483"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E663" r:id="rId1484"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C665" r:id="rId1485"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E665" r:id="rId1486"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B666" r:id="rId1487"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C666" r:id="rId1488"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E666" r:id="rId1489"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B667" r:id="rId1490"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C667" r:id="rId1491"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E667" r:id="rId1492"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B668" r:id="rId1493"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C668" r:id="rId1494"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E668" r:id="rId1495"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B669" r:id="rId1496"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C669" r:id="rId1497"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E669" r:id="rId1498"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B670" r:id="rId1499"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C670" r:id="rId1500"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E670" r:id="rId1501"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B671" r:id="rId1502"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C671" r:id="rId1503"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E671" r:id="rId1504"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C672" r:id="rId1505"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E672" r:id="rId1506"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B673" r:id="rId1507"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C673" r:id="rId1508"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E673" r:id="rId1509"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B674" r:id="rId1510"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E674" r:id="rId1511"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B664" r:id="rId1485"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E664" r:id="rId1486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B665" r:id="rId1487"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E665" r:id="rId1488"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C667" r:id="rId1489"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E667" r:id="rId1490"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B668" r:id="rId1491"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C668" r:id="rId1492"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E668" r:id="rId1493"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B669" r:id="rId1494"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C669" r:id="rId1495"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E669" r:id="rId1496"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B670" r:id="rId1497"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C670" r:id="rId1498"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E670" r:id="rId1499"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B671" r:id="rId1500"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C671" r:id="rId1501"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E671" r:id="rId1502"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B672" r:id="rId1503"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C672" r:id="rId1504"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E672" r:id="rId1505"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B673" r:id="rId1506"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C673" r:id="rId1507"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E673" r:id="rId1508"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C674" r:id="rId1509"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E674" r:id="rId1510"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B675" r:id="rId1511"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C675" r:id="rId1512"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E675" r:id="rId1513"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C676" r:id="rId1514"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B676" r:id="rId1514"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E676" r:id="rId1515"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C677" r:id="rId1516"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E677" r:id="rId1517"/>
@@ -17302,31 +17417,31 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E682" r:id="rId1527"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C683" r:id="rId1528"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E683" r:id="rId1529"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B684" r:id="rId1530"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C684" r:id="rId1531"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E684" r:id="rId1532"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B685" r:id="rId1533"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C685" r:id="rId1534"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E685" r:id="rId1535"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B686" r:id="rId1536"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C686" r:id="rId1537"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E686" r:id="rId1538"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B687" r:id="rId1539"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C687" r:id="rId1540"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E687" r:id="rId1541"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B688" r:id="rId1542"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C688" r:id="rId1543"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E688" r:id="rId1544"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C689" r:id="rId1545"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E689" r:id="rId1546"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B690" r:id="rId1547"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C690" r:id="rId1548"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E690" r:id="rId1549"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B691" r:id="rId1550"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C691" r:id="rId1551"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E691" r:id="rId1552"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B692" r:id="rId1553"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E692" r:id="rId1554"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C684" r:id="rId1530"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E684" r:id="rId1531"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C685" r:id="rId1532"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E685" r:id="rId1533"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B686" r:id="rId1534"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C686" r:id="rId1535"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E686" r:id="rId1536"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B687" r:id="rId1537"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C687" r:id="rId1538"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E687" r:id="rId1539"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B688" r:id="rId1540"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C688" r:id="rId1541"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E688" r:id="rId1542"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B689" r:id="rId1543"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C689" r:id="rId1544"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E689" r:id="rId1545"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B690" r:id="rId1546"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C690" r:id="rId1547"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E690" r:id="rId1548"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C691" r:id="rId1549"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E691" r:id="rId1550"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B692" r:id="rId1551"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C692" r:id="rId1552"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E692" r:id="rId1553"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B693" r:id="rId1554"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C693" r:id="rId1555"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E693" r:id="rId1556"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B694" r:id="rId1557"/>
@@ -17335,117 +17450,123 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E695" r:id="rId1560"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B696" r:id="rId1561"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E696" r:id="rId1562"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B697" r:id="rId1563"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C697" r:id="rId1563"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E697" r:id="rId1564"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B698" r:id="rId1565"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C698" r:id="rId1566"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E698" r:id="rId1567"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B699" r:id="rId1568"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E699" r:id="rId1569"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E698" r:id="rId1566"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B699" r:id="rId1567"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E699" r:id="rId1568"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B700" r:id="rId1569"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C700" r:id="rId1570"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E700" r:id="rId1571"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B701" r:id="rId1572"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C701" r:id="rId1573"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E701" r:id="rId1574"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C702" r:id="rId1575"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E702" r:id="rId1576"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B703" r:id="rId1577"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C703" r:id="rId1578"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E703" r:id="rId1579"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B704" r:id="rId1580"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C704" r:id="rId1581"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E704" r:id="rId1582"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C705" r:id="rId1583"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E705" r:id="rId1584"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E701" r:id="rId1573"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C702" r:id="rId1574"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E702" r:id="rId1575"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B703" r:id="rId1576"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C703" r:id="rId1577"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E703" r:id="rId1578"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C704" r:id="rId1579"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E704" r:id="rId1580"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B705" r:id="rId1581"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C705" r:id="rId1582"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E705" r:id="rId1583"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B706" r:id="rId1584"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C706" r:id="rId1585"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E706" r:id="rId1586"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C707" r:id="rId1587"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E707" r:id="rId1588"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B708" r:id="rId1589"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C708" r:id="rId1589"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E708" r:id="rId1590"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B709" r:id="rId1591"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C709" r:id="rId1592"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E709" r:id="rId1593"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C710" r:id="rId1594"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E710" r:id="rId1595"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B711" r:id="rId1596"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C711" r:id="rId1597"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E711" r:id="rId1598"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B712" r:id="rId1599"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C712" r:id="rId1600"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E712" r:id="rId1601"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B714" r:id="rId1602"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C714" r:id="rId1603"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E714" r:id="rId1604"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D716" r:id="rId1605"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B717" r:id="rId1606"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E717" r:id="rId1607"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B718" r:id="rId1608"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E718" r:id="rId1609"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C709" r:id="rId1591"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E709" r:id="rId1592"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B710" r:id="rId1593"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E710" r:id="rId1594"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B711" r:id="rId1595"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C711" r:id="rId1596"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E711" r:id="rId1597"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C712" r:id="rId1598"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E712" r:id="rId1599"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B713" r:id="rId1600"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C713" r:id="rId1601"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E713" r:id="rId1602"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B714" r:id="rId1603"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C714" r:id="rId1604"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E714" r:id="rId1605"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B716" r:id="rId1606"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C716" r:id="rId1607"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E716" r:id="rId1608"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D718" r:id="rId1609"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B719" r:id="rId1610"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E719" r:id="rId1611"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B720" r:id="rId1612"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E720" r:id="rId1613"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B721" r:id="rId1614"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C721" r:id="rId1615"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E721" r:id="rId1616"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B722" r:id="rId1617"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C722" r:id="rId1618"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E722" r:id="rId1619"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C723" r:id="rId1620"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E723" r:id="rId1621"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B724" r:id="rId1622"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C724" r:id="rId1623"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E724" r:id="rId1624"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B725" r:id="rId1625"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C725" r:id="rId1626"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E725" r:id="rId1627"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C726" r:id="rId1628"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E726" r:id="rId1629"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B727" r:id="rId1630"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C727" r:id="rId1631"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E727" r:id="rId1632"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B728" r:id="rId1633"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E728" r:id="rId1634"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B729" r:id="rId1635"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E729" r:id="rId1636"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B730" r:id="rId1637"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E721" r:id="rId1615"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B722" r:id="rId1616"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E722" r:id="rId1617"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B723" r:id="rId1618"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C723" r:id="rId1619"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E723" r:id="rId1620"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B724" r:id="rId1621"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C724" r:id="rId1622"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E724" r:id="rId1623"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C725" r:id="rId1624"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E725" r:id="rId1625"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B726" r:id="rId1626"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C726" r:id="rId1627"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E726" r:id="rId1628"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B727" r:id="rId1629"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C727" r:id="rId1630"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E727" r:id="rId1631"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C728" r:id="rId1632"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E728" r:id="rId1633"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C729" r:id="rId1634"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E729" r:id="rId1635"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B730" r:id="rId1636"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C730" r:id="rId1637"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E730" r:id="rId1638"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B731" r:id="rId1639"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C731" r:id="rId1640"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E731" r:id="rId1641"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B732" r:id="rId1642"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E732" r:id="rId1643"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C733" r:id="rId1644"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E733" r:id="rId1645"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E731" r:id="rId1640"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B732" r:id="rId1641"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E732" r:id="rId1642"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B733" r:id="rId1643"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E733" r:id="rId1644"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B734" r:id="rId1645"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C734" r:id="rId1646"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E734" r:id="rId1647"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B735" r:id="rId1648"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C735" r:id="rId1649"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E735" r:id="rId1650"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B736" r:id="rId1651"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C736" r:id="rId1652"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E736" r:id="rId1653"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C737" r:id="rId1654"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E737" r:id="rId1655"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B738" r:id="rId1656"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C738" r:id="rId1657"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E738" r:id="rId1658"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C739" r:id="rId1659"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E739" r:id="rId1660"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B740" r:id="rId1661"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E740" r:id="rId1662"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B741" r:id="rId1663"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C741" r:id="rId1664"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E741" r:id="rId1665"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B742" r:id="rId1666"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E742" r:id="rId1667"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B743" r:id="rId1668"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C743" r:id="rId1669"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E743" r:id="rId1670"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B744" r:id="rId1671"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C744" r:id="rId1672"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E744" r:id="rId1673"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E735" r:id="rId1649"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C736" r:id="rId1650"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E736" r:id="rId1651"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C737" r:id="rId1652"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E737" r:id="rId1653"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B738" r:id="rId1654"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C738" r:id="rId1655"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E738" r:id="rId1656"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B739" r:id="rId1657"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C739" r:id="rId1658"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E739" r:id="rId1659"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C740" r:id="rId1660"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E740" r:id="rId1661"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B741" r:id="rId1662"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C741" r:id="rId1663"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E741" r:id="rId1664"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C742" r:id="rId1665"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E742" r:id="rId1666"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B743" r:id="rId1667"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E743" r:id="rId1668"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B744" r:id="rId1669"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C744" r:id="rId1670"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E744" r:id="rId1671"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B745" r:id="rId1672"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E745" r:id="rId1673"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B746" r:id="rId1674"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C746" r:id="rId1675"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E746" r:id="rId1676"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B747" r:id="rId1677"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C747" r:id="rId1678"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E747" r:id="rId1679"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/downloads/doctors.xlsx
+++ b/downloads/doctors.xlsx
@@ -8,10 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Index" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Websites that post a CV" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Every chiropractor" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="US Chiro Directory CVs" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sports chiros, NPI registry" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Every chiropractor" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sports chiros, NPI registry" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -38,12 +36,12 @@
       <color rgb="00FFFFFF"/>
     </font>
     <font>
+      <b val="1"/>
+      <color rgb="001C458C"/>
+    </font>
+    <font>
       <color rgb="001C458C"/>
       <u val="single"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="001C458C"/>
     </font>
   </fonts>
   <fills count="4">
@@ -80,8 +78,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -447,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -488,58 +486,28 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Websites that post a CV</t>
+          <t>Every chiropractor</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11</v>
+        <v>740</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Websites that post a CV (11)</t>
+          <t>Every chiropractor and NMR practitioner, by list</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Every chiropractor</t>
+          <t>Sports chiros, NPI registry</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>740</v>
+        <v>558</v>
       </c>
       <c r="C6" t="inlineStr">
-        <is>
-          <t>Every chiropractor and NMR practitioner, by list</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>US Chiro Directory CVs</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>68</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>California chiropractors with a CV on US Chiro Directory (68)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Sports chiros, NPI registry</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>558</v>
-      </c>
-      <c r="C8" t="inlineStr">
         <is>
           <t>California chiropractors registered as sports physicians (NPI registry, 558)</t>
         </is>
@@ -549,403 +517,12 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="49" customWidth="1" min="1" max="1"/>
-    <col width="51" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="48" customWidth="1" min="5" max="5"/>
-    <col width="72" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Doctor</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Practice</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>About or team page</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>CV</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>Other pages</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>How the site shows it</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Betz, Joseph W, DC</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Modern Chiropractic Center</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>modernchiropracticcenter.com</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>open the CV</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Bio page with a "Link to Curriculum Vitae" button that opens the full CV (PDF, September 2026). The set-up to copy.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Moreau, William (Bill), DC, DACBSP</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>NeuroSport Spine and Concussion</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>neurosportspineandconcussion.com</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>open the CV</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>CV (PDF) · CV (PDF) · dconline.org · ncmic.com</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Team page with a CV summary and drop-downs; a Curriculum Vitae page with highlights and a "Download Full Curriculum Vitae (PDF)" button; instructor and speaker bios elsewhere.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Fish, Gene, DC</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Genesis Chiropractic</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>genesischiroclinic.com</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>open the CV</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>About page with a "See Dr. Fish's CV" button (PDF).</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Injury and Spinecare Chiropractic, La Crescenta</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Injury and Spinecare Chiropractic</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>injuryandspinecare.com</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>open the CV</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>About page with "Click to view CV"; the CV is a page on US Chiro Directory.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Casazza, Lance, DC</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Sacramento Chiropractic</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>sacramentochiropractic.com</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>no separate CV</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>sacramentochiropractic.com</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Team page with a full bio for each doctor (education, experience, certifications, books); no separate CV.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Cool Chiropractic (Sacramento)</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Cool Chiropractic</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>coolchiropracticsac.com</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>no separate CV</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Team page with a full bio for each doctor; no separate CV.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>P2 Sports Care</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>P2 Sports Care</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>p2sportscare.com</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>no separate CV</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Team page with a full bio for each doctor; no separate CV.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Sorrentino, Anne, DC</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Dr. Anne Sorrentino</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>drannesorrentino.com</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>no separate CV</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Short bio with credentials after the name; no CV.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Young, Tom, DC</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Countryside Chiropractic</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>countryside-chiropractic.com</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>no separate CV</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Short bio with credentials after the name; no CV.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Horrigan, Joseph, DC</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Southern California University of Health Sciences</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>scuhs.edu</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>no separate CV</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Faculty bio page; no CV.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Bisaccia, John and Marna, DC (NMR certified)</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Williston Chiropractic &amp; Sportsmedicine</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>willistonchiropractic.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>no separate CV</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>About page with each doctor's bio and NMR certification; no CV.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId17"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -17572,1269 +17149,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C69"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="63" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Doctor</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Practice and city</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>CV</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Ray Arensdorf, DC</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Arensdorf Chiropractic Santa Maria</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Kurt Armstrong, DC</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Armstrong Chiropractic Sacramento</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Dennis Barker, DC</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Tice Valley Chiropractic Walnut Creek</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Steven Bretow, DC</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Westside Family Chiropractic Berkeley</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Dale Charrette, DC</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Charrette Chiropractic Health Systems Visalia</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Wendy Chow, DC QME</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Chow Chiropractic EL Monte</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>David Conner, DC QME</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Conner Chiropractic Care Corp Vacaville</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Jeff Coyle, DC FASBE</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Jeff Coyle And Advanced Health Center Campbell</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Robert Davison, DC</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Back IN Action Chiropractic Center Berkeley</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Douglas DeSalvo, DC QME</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Desalvo Chiropractic Injury Center Novato</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Robert Dickman, DC</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Dickman Chiropractic Corporation EL Dorado Hills</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Binh Huu Do, DC</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Binh Huu DO D C San Jose</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Stacey Duckett, DC ACN</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Stacey Duckett Chiropractic Antioch</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Sayel Fakhoury, DC, QME</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Gentle Touch Chiropractic Tarzana</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Leonard Faye, DC FRCCS</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Faye Faye Chiropractic Los Angeles</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Pierre Fey, DC</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Fey Chiropractic Westlake Village</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Howard Friedman, DC</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Friedman Family Chiropractic Burbank</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Steve Funk, DC</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>DR Funk Chiropractic Roseville</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Daniel Garcia, DC</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Garcia Chiropractic Costa Mesa</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Tom Gibson, DC</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>DR Tom Gibson D C Cameron Park</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Robert Hecht, DC</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Advanced Health Solutions Irvine</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Jose Hernandez, DC</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Hernandez Chiropractic San Marcos</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Aaron Hinde, DC BA</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Hinde Chiropractic Wellness Center Scotts Valley</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Greg Jones, DC</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Turlock Family Chiropractic Turlock</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Rick Junnila, DC FPSC</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Lifestyle Health Fitness Oakely</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Rick Junnila, DC DAAPM</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Spine Sportcare Associates Lafayette</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>T. Jimmy Kazandjian, DC LA</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Sol Wellness Center Burbank</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Marc Lewis, DC</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Gabriel Hannawi San Diego</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>David Lincoln, DC DACNB</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Healthy Families Chiropractic Santa Rosa</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Albert Mansour, DC IDE</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Mansour Chiropractic Inc Chino Hills</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Ronald Marinaro, DC</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Loranger Family Wellness Center PC Studio City</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>L. Dwight McCarty, DC</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>DR Mccarty Doctor Of Chiropractic Wellness Coach Garden Grove</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Richard Mellinger, DC</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Mellinger Chiropractic Canoga Park</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Rod Melvin, DC DAAML</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>South Ontario Chiropractic Ontario</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Ali Mostafavi, DC QME</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Chiropractic And Spine Center Tustin</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Bradley Mouroux, DC CPAK</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Mouroux Chiropractic San Jose</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Daniel Muldavin, DC QME</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Muldavin Chiropractic Elk Grove</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Amin Nia, DC QME</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Spectrum Medical Group Inc Los Angeles</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Hang Pham, DC</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Prime Health Center Anaheim</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Michael Putman, DC CFMP</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Twin Creeks Health Roseville</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Mitra Razipour, DC</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>DR Mitra Razipour Chiropractor Woodland Hills</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>James Reiley, DC</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Family And Sports Chiropractic Aliso Viejo</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Derek Rice, DC</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Rice Chiropractic And Wellness San Diego</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Marielle Richter, DC</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Advance Upper Cervical Chiropractic Bridgeport</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Sean Rundle, DC</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Rundle Chiropractic Laguna Hills</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>David Salse, DC MUAC</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Salse Chiropractic Center Monrovia</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>DAVID DE SALVO, DC SARAT</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Saratoga Ave Back And Neck Center San Jose</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Shay Shani, DC</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Clear Purpose Chiropractic Westlake Village</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Christine Smith, DC</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Plano Injury Rehab Chiropractic South Pasadena</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Terrance Stackwood, DC</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Universal Chiropractic San Francisco</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Daniel Steffins, DC FPSC</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Spinal Health Center Of West Monroe Encinitas</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Anthony Subia, DC</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Injury And Spinecare Chiropractic LA Crescenta</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Joe Szafranski, DC</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Summit Chiropractic Massage EL Cajon</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Jan Teitelbaum, DC</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Mission Chiropractic Mission Viejo</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>William Thomas, DC QME</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>DR Thomas Chiropractic Massage Therapy LA Mirada</t>
-        </is>
-      </c>
-      <c r="C56" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>D. Joe Tobias, DC</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>D Joe Tobias D C Laguna Hills</t>
-        </is>
-      </c>
-      <c r="C57" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>D. Joe Tobias, DC</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Placentia Linda Chiropractic Centre Placentia</t>
-        </is>
-      </c>
-      <c r="C58" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Tas Toth-Tevel, DC</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Tevel Chiropractic Thousnd Oaks</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Ronald Vernon, DC</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Nonsurgical Pain Relief Center Pleasanton</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Timothy Wang, DC</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Add Life Chiropractic Menlo Park</t>
-        </is>
-      </c>
-      <c r="C61" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Timothy Wang, DC</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Pain Relief Chiropractic Center Fresno</t>
-        </is>
-      </c>
-      <c r="C62" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>John Warren, DC</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Physical Medicine Clinic Of Granite City Fountain Valley</t>
-        </is>
-      </c>
-      <c r="C63" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Douglas Weed, DC</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Richard R Chaney DC Fairfield</t>
-        </is>
-      </c>
-      <c r="C64" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Marc Weiss, DC DAAML</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Weiss Chiropractic Inc Torrance</t>
-        </is>
-      </c>
-      <c r="C65" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Jonathan Widenbaum, DC QME</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Widenbaum Chiropractic Allergy Relief Center Dublin</t>
-        </is>
-      </c>
-      <c r="C66" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>KIRK WRIGHT, DC RN HARMO</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Harmonic Life Chiropractic Center San Pedro</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>WON YOO, DC DAAML</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>DR Won S Yoo D C Oakland</t>
-        </is>
-      </c>
-      <c r="C68" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Charles Zollner, DC CCEP</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Ohio Spine And Injury Centers San Rafael</t>
-        </is>
-      </c>
-      <c r="C69" s="3" t="inlineStr">
-        <is>
-          <t>CV page</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C44" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C45" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C46" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C47" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C48" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C49" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C52" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C53" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C54" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C56" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C58" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C59" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C60" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C61" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C62" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C63" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C64" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C65" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C66" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C67" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C68" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C69" r:id="rId68"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/downloads/doctors.xlsx
+++ b/downloads/doctors.xlsx
@@ -706,9 +706,9 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Bigelow, Brian T</t>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Bigelow, Brian T mentions NMR</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -760,9 +760,9 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Bisaccia, John Jalso in: Other chiropractors (CV and website review)</t>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Bisaccia, John J mentions NMRalso in: Other chiropractors (CV and website review)</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -783,9 +783,9 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Bisaccia, Marna Malso in: Other chiropractors (CV and website review)</t>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Bisaccia, Marna M mentions NMRalso in: Other chiropractors (CV and website review)</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -829,9 +829,9 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Cayer, Jeremy</t>
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Cayer, Jeremy mentions NMR</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -1051,9 +1051,9 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Duckett, Staceyalso in: Other chiropractors (CV and website review)</t>
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Duckett, Stacey mentions NMRalso in: Other chiropractors (CV and website review)</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1300,9 +1300,9 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Hallam, David</t>
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Hallam, David mentions NMR</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -1415,9 +1415,9 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Johnson, Jeffrey</t>
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Johnson, Jeffrey mentions NMR</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -1837,9 +1837,9 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Miller, Diane</t>
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>Miller, Diane mentions NMR</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -1921,9 +1921,9 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Mott, Lisa</t>
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>Mott, Lisa mentions NMR</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -2012,9 +2012,9 @@
       <c r="E67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Poane, Robert</t>
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>Poane, Robert mentions NMR</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -2345,9 +2345,9 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Townshend, Judith</t>
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>Townshend, Judith mentions NMR</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -2647,9 +2647,9 @@
       <c r="E96" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Zollinger-Muench, Nicole</t>
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>Zollinger-Muench, Nicole mentions NMR</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -15493,1671 +15493,1683 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B34" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B36" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B37" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B38" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B41" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B42" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C44" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B45" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B47" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C47" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C48" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B49" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B50" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B51" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B52" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D52" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B53" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D53" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C54" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B55" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C56" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D56" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D57" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B58" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C58" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D58" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C59" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D60" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B61" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C61" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D61" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B62" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C62" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B63" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C63" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B64" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B65" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D65" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D67" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B68" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C68" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D68" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D69" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C70" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D70" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B71" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C72" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B73" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D73" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B74" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C74" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D74" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B75" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C75" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D75" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B76" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C76" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B77" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C77" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D77" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B79" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D79" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B80" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C80" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B81" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C81" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D81" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C82" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B83" r:id="rId224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C83" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D83" r:id="rId226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B84" r:id="rId228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C84" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D84" r:id="rId230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B86" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C86" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C87" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B88" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C88" r:id="rId238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C89" r:id="rId240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D89" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C90" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D90" r:id="rId244"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B91" r:id="rId246"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C91" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId248"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B92" r:id="rId249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C92" r:id="rId250"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B93" r:id="rId252"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C93" r:id="rId253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId254"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C94" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D94" r:id="rId256"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B95" r:id="rId258"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D95" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId260"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B97" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C97" r:id="rId262"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B98" r:id="rId264"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C98" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId266"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D100" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D101" r:id="rId268"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D102" r:id="rId269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B103" r:id="rId270"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D103" r:id="rId271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId272"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D104" r:id="rId273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D106" r:id="rId274"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D107" r:id="rId275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D108" r:id="rId276"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D109" r:id="rId277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D110" r:id="rId278"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C111" r:id="rId279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId280"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D112" r:id="rId281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D113" r:id="rId282"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B114" r:id="rId283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId284"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D115" r:id="rId285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D116" r:id="rId286"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D117" r:id="rId287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D118" r:id="rId288"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D119" r:id="rId289"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B120" r:id="rId290"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId291"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D121" r:id="rId292"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D122" r:id="rId293"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D123" r:id="rId294"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D124" r:id="rId295"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D125" r:id="rId296"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D126" r:id="rId297"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D127" r:id="rId298"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D128" r:id="rId299"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D129" r:id="rId300"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B130" r:id="rId301"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C130" r:id="rId302"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D130" r:id="rId303"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E130" r:id="rId304"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B131" r:id="rId305"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E131" r:id="rId306"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D132" r:id="rId307"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D133" r:id="rId308"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D134" r:id="rId309"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D135" r:id="rId310"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C136" r:id="rId311"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D136" r:id="rId312"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E136" r:id="rId313"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D137" r:id="rId314"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D138" r:id="rId315"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D139" r:id="rId316"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B140" r:id="rId317"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E140" r:id="rId318"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D141" r:id="rId319"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D142" r:id="rId320"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D143" r:id="rId321"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B144" r:id="rId322"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C144" r:id="rId323"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E144" r:id="rId324"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D145" r:id="rId325"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D146" r:id="rId326"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D147" r:id="rId327"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C148" r:id="rId328"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E148" r:id="rId329"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B149" r:id="rId330"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D149" r:id="rId331"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E149" r:id="rId332"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D150" r:id="rId333"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D151" r:id="rId334"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D152" r:id="rId335"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D153" r:id="rId336"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D154" r:id="rId337"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D155" r:id="rId338"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D156" r:id="rId339"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D157" r:id="rId340"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D158" r:id="rId341"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D159" r:id="rId342"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B160" r:id="rId343"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E160" r:id="rId344"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D161" r:id="rId345"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D162" r:id="rId346"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D163" r:id="rId347"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D164" r:id="rId348"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D165" r:id="rId349"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D166" r:id="rId350"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D167" r:id="rId351"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D168" r:id="rId352"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D169" r:id="rId353"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D170" r:id="rId354"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D171" r:id="rId355"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D172" r:id="rId356"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D173" r:id="rId357"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C174" r:id="rId358"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E174" r:id="rId359"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D175" r:id="rId360"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D176" r:id="rId361"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D177" r:id="rId362"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D178" r:id="rId363"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D179" r:id="rId364"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D180" r:id="rId365"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D181" r:id="rId366"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D182" r:id="rId367"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D183" r:id="rId368"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D184" r:id="rId369"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B185" r:id="rId370"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E185" r:id="rId371"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C186" r:id="rId372"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E186" r:id="rId373"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D187" r:id="rId374"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D188" r:id="rId375"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D189" r:id="rId376"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B190" r:id="rId377"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C190" r:id="rId378"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D190" r:id="rId379"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E190" r:id="rId380"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B191" r:id="rId381"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D191" r:id="rId382"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E191" r:id="rId383"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D192" r:id="rId384"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D193" r:id="rId385"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B194" r:id="rId386"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E194" r:id="rId387"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D195" r:id="rId388"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C196" r:id="rId389"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E196" r:id="rId390"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D197" r:id="rId391"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D198" r:id="rId392"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D199" r:id="rId393"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D200" r:id="rId394"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D201" r:id="rId395"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D202" r:id="rId396"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D203" r:id="rId397"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B204" r:id="rId398"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E204" r:id="rId399"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D205" r:id="rId400"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D206" r:id="rId401"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D207" r:id="rId402"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D208" r:id="rId403"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B209" r:id="rId404"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E209" r:id="rId405"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B210" r:id="rId406"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E210" r:id="rId407"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D211" r:id="rId408"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D212" r:id="rId409"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D213" r:id="rId410"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D214" r:id="rId411"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D215" r:id="rId412"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D216" r:id="rId413"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D217" r:id="rId414"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D218" r:id="rId415"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C219" r:id="rId416"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D219" r:id="rId417"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E219" r:id="rId418"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D220" r:id="rId419"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D221" r:id="rId420"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D222" r:id="rId421"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D223" r:id="rId422"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D224" r:id="rId423"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D225" r:id="rId424"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D226" r:id="rId425"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D227" r:id="rId426"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D228" r:id="rId427"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B229" r:id="rId428"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D229" r:id="rId429"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E229" r:id="rId430"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B230" r:id="rId431"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D230" r:id="rId432"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E230" r:id="rId433"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D231" r:id="rId434"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D232" r:id="rId435"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B233" r:id="rId436"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D233" r:id="rId437"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E233" r:id="rId438"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B234" r:id="rId439"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E234" r:id="rId440"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D235" r:id="rId441"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B236" r:id="rId442"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E236" r:id="rId443"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D237" r:id="rId444"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B238" r:id="rId445"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D238" r:id="rId446"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E238" r:id="rId447"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D239" r:id="rId448"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D240" r:id="rId449"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D241" r:id="rId450"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D242" r:id="rId451"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D243" r:id="rId452"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D244" r:id="rId453"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D245" r:id="rId454"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B246" r:id="rId455"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E246" r:id="rId456"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C247" r:id="rId457"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D247" r:id="rId458"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E247" r:id="rId459"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D248" r:id="rId460"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D249" r:id="rId461"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D250" r:id="rId462"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D251" r:id="rId463"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B252" r:id="rId464"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D252" r:id="rId465"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E252" r:id="rId466"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D253" r:id="rId467"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D254" r:id="rId468"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D255" r:id="rId469"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B256" r:id="rId470"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D256" r:id="rId471"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E256" r:id="rId472"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D257" r:id="rId473"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D258" r:id="rId474"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D259" r:id="rId475"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D260" r:id="rId476"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D261" r:id="rId477"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D262" r:id="rId478"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D263" r:id="rId479"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B264" r:id="rId480"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E264" r:id="rId481"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D265" r:id="rId482"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D266" r:id="rId483"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D267" r:id="rId484"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D268" r:id="rId485"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D269" r:id="rId486"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D270" r:id="rId487"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D271" r:id="rId488"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D272" r:id="rId489"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D273" r:id="rId490"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D274" r:id="rId491"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D275" r:id="rId492"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D276" r:id="rId493"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D277" r:id="rId494"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D278" r:id="rId495"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D279" r:id="rId496"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D280" r:id="rId497"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B281" r:id="rId498"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E281" r:id="rId499"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B282" r:id="rId500"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C282" r:id="rId501"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D282" r:id="rId502"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E282" r:id="rId503"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D283" r:id="rId504"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D284" r:id="rId505"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D286" r:id="rId506"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D287" r:id="rId507"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D288" r:id="rId508"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D289" r:id="rId509"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B290" r:id="rId510"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C290" r:id="rId511"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D290" r:id="rId512"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E290" r:id="rId513"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B292" r:id="rId514"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E292" r:id="rId515"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B293" r:id="rId516"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C293" r:id="rId517"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E293" r:id="rId518"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B294" r:id="rId519"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C294" r:id="rId520"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E294" r:id="rId521"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B295" r:id="rId522"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E295" r:id="rId523"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B296" r:id="rId524"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C296" r:id="rId525"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E296" r:id="rId526"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B297" r:id="rId527"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C297" r:id="rId528"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E297" r:id="rId529"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B298" r:id="rId530"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C298" r:id="rId531"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E298" r:id="rId532"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B299" r:id="rId533"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C299" r:id="rId534"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E299" r:id="rId535"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B300" r:id="rId536"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E300" r:id="rId537"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B301" r:id="rId538"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C301" r:id="rId539"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E301" r:id="rId540"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B302" r:id="rId541"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C302" r:id="rId542"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E302" r:id="rId543"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B303" r:id="rId544"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E303" r:id="rId545"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B304" r:id="rId546"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C304" r:id="rId547"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E304" r:id="rId548"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B305" r:id="rId549"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C305" r:id="rId550"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E305" r:id="rId551"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B306" r:id="rId552"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E306" r:id="rId553"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B307" r:id="rId554"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C307" r:id="rId555"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E307" r:id="rId556"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B308" r:id="rId557"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C308" r:id="rId558"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E308" r:id="rId559"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B309" r:id="rId560"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C309" r:id="rId561"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E309" r:id="rId562"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B310" r:id="rId563"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C310" r:id="rId564"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E310" r:id="rId565"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B311" r:id="rId566"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C311" r:id="rId567"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E311" r:id="rId568"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B312" r:id="rId569"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C312" r:id="rId570"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E312" r:id="rId571"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B313" r:id="rId572"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E313" r:id="rId573"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B314" r:id="rId574"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C314" r:id="rId575"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E314" r:id="rId576"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B315" r:id="rId577"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C315" r:id="rId578"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E315" r:id="rId579"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B316" r:id="rId580"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C316" r:id="rId581"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E316" r:id="rId582"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B317" r:id="rId583"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C317" r:id="rId584"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E317" r:id="rId585"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B318" r:id="rId586"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E318" r:id="rId587"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B319" r:id="rId588"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C319" r:id="rId589"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E319" r:id="rId590"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B320" r:id="rId591"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C320" r:id="rId592"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E320" r:id="rId593"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C322" r:id="rId594"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E322" r:id="rId595"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B323" r:id="rId596"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C323" r:id="rId597"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E323" r:id="rId598"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B324" r:id="rId599"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C324" r:id="rId600"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E324" r:id="rId601"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B325" r:id="rId602"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C325" r:id="rId603"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E325" r:id="rId604"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B326" r:id="rId605"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C326" r:id="rId606"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E326" r:id="rId607"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C327" r:id="rId608"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E327" r:id="rId609"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B328" r:id="rId610"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C328" r:id="rId611"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E328" r:id="rId612"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B329" r:id="rId613"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C329" r:id="rId614"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E329" r:id="rId615"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B330" r:id="rId616"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C330" r:id="rId617"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E330" r:id="rId618"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B331" r:id="rId619"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C331" r:id="rId620"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E331" r:id="rId621"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C332" r:id="rId622"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E332" r:id="rId623"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B333" r:id="rId624"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C333" r:id="rId625"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E333" r:id="rId626"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B334" r:id="rId627"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C334" r:id="rId628"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E334" r:id="rId629"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B335" r:id="rId630"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C335" r:id="rId631"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E335" r:id="rId632"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B336" r:id="rId633"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C336" r:id="rId634"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E336" r:id="rId635"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B337" r:id="rId636"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C337" r:id="rId637"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E337" r:id="rId638"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B338" r:id="rId639"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C338" r:id="rId640"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E338" r:id="rId641"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C339" r:id="rId642"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E339" r:id="rId643"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B340" r:id="rId644"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C340" r:id="rId645"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E340" r:id="rId646"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B341" r:id="rId647"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C341" r:id="rId648"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E341" r:id="rId649"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B342" r:id="rId650"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C342" r:id="rId651"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E342" r:id="rId652"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B343" r:id="rId653"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C343" r:id="rId654"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E343" r:id="rId655"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B344" r:id="rId656"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C344" r:id="rId657"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E344" r:id="rId658"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B345" r:id="rId659"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C345" r:id="rId660"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E345" r:id="rId661"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B346" r:id="rId662"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C346" r:id="rId663"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E346" r:id="rId664"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B347" r:id="rId665"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C347" r:id="rId666"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E347" r:id="rId667"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B348" r:id="rId668"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C348" r:id="rId669"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E348" r:id="rId670"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B349" r:id="rId671"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C349" r:id="rId672"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E349" r:id="rId673"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B350" r:id="rId674"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C350" r:id="rId675"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E350" r:id="rId676"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B351" r:id="rId677"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C351" r:id="rId678"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E351" r:id="rId679"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B352" r:id="rId680"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C352" r:id="rId681"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E352" r:id="rId682"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B353" r:id="rId683"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C353" r:id="rId684"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E353" r:id="rId685"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B354" r:id="rId686"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C354" r:id="rId687"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E354" r:id="rId688"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B355" r:id="rId689"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C355" r:id="rId690"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E355" r:id="rId691"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B356" r:id="rId692"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C356" r:id="rId693"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E356" r:id="rId694"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B357" r:id="rId695"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C357" r:id="rId696"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E357" r:id="rId697"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B358" r:id="rId698"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E358" r:id="rId699"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B359" r:id="rId700"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C359" r:id="rId701"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E359" r:id="rId702"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B360" r:id="rId703"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C360" r:id="rId704"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E360" r:id="rId705"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B361" r:id="rId706"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C361" r:id="rId707"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E361" r:id="rId708"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B362" r:id="rId709"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C362" r:id="rId710"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E362" r:id="rId711"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B363" r:id="rId712"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C363" r:id="rId713"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E363" r:id="rId714"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B364" r:id="rId715"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C364" r:id="rId716"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E364" r:id="rId717"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B365" r:id="rId718"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E365" r:id="rId719"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C366" r:id="rId720"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E366" r:id="rId721"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B367" r:id="rId722"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C367" r:id="rId723"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E367" r:id="rId724"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B368" r:id="rId725"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E368" r:id="rId726"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B369" r:id="rId727"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E369" r:id="rId728"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B370" r:id="rId729"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C370" r:id="rId730"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E370" r:id="rId731"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B371" r:id="rId732"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E371" r:id="rId733"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B372" r:id="rId734"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C372" r:id="rId735"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E372" r:id="rId736"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B373" r:id="rId737"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C373" r:id="rId738"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E373" r:id="rId739"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B374" r:id="rId740"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C374" r:id="rId741"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E374" r:id="rId742"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B375" r:id="rId743"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C375" r:id="rId744"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E375" r:id="rId745"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B376" r:id="rId746"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C376" r:id="rId747"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E376" r:id="rId748"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B377" r:id="rId749"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C377" r:id="rId750"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E377" r:id="rId751"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B378" r:id="rId752"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E378" r:id="rId753"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B379" r:id="rId754"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C379" r:id="rId755"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E379" r:id="rId756"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B380" r:id="rId757"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C380" r:id="rId758"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E380" r:id="rId759"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B381" r:id="rId760"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C381" r:id="rId761"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E381" r:id="rId762"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B382" r:id="rId763"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C382" r:id="rId764"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E382" r:id="rId765"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B383" r:id="rId766"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C383" r:id="rId767"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E383" r:id="rId768"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B384" r:id="rId769"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C384" r:id="rId770"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E384" r:id="rId771"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B385" r:id="rId772"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C385" r:id="rId773"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E385" r:id="rId774"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B386" r:id="rId775"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C386" r:id="rId776"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E386" r:id="rId777"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B387" r:id="rId778"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C387" r:id="rId779"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E387" r:id="rId780"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B388" r:id="rId781"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C388" r:id="rId782"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E388" r:id="rId783"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B389" r:id="rId784"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E389" r:id="rId785"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B390" r:id="rId786"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C390" r:id="rId787"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E390" r:id="rId788"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B391" r:id="rId789"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C391" r:id="rId790"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E391" r:id="rId791"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B392" r:id="rId792"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C392" r:id="rId793"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E392" r:id="rId794"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B393" r:id="rId795"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C393" r:id="rId796"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E393" r:id="rId797"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B394" r:id="rId798"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C394" r:id="rId799"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E394" r:id="rId800"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B395" r:id="rId801"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E395" r:id="rId802"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B396" r:id="rId803"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C396" r:id="rId804"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E396" r:id="rId805"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B397" r:id="rId806"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C397" r:id="rId807"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E397" r:id="rId808"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B398" r:id="rId809"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E398" r:id="rId810"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B399" r:id="rId811"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C399" r:id="rId812"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E399" r:id="rId813"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B400" r:id="rId814"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C400" r:id="rId815"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E400" r:id="rId816"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B401" r:id="rId817"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C401" r:id="rId818"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E401" r:id="rId819"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B402" r:id="rId820"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C402" r:id="rId821"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E402" r:id="rId822"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B403" r:id="rId823"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C403" r:id="rId824"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E403" r:id="rId825"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B404" r:id="rId826"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C404" r:id="rId827"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E404" r:id="rId828"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B405" r:id="rId829"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C405" r:id="rId830"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E405" r:id="rId831"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B406" r:id="rId832"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C406" r:id="rId833"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E406" r:id="rId834"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B407" r:id="rId835"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C407" r:id="rId836"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E407" r:id="rId837"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B408" r:id="rId838"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C408" r:id="rId839"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E408" r:id="rId840"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B409" r:id="rId841"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C409" r:id="rId842"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E409" r:id="rId843"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B410" r:id="rId844"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C410" r:id="rId845"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E410" r:id="rId846"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B411" r:id="rId847"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C411" r:id="rId848"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E411" r:id="rId849"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B412" r:id="rId850"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C412" r:id="rId851"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E412" r:id="rId852"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B413" r:id="rId853"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C413" r:id="rId854"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E413" r:id="rId855"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B414" r:id="rId856"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C414" r:id="rId857"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E414" r:id="rId858"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B415" r:id="rId859"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E415" r:id="rId860"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B416" r:id="rId861"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C416" r:id="rId862"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E416" r:id="rId863"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B417" r:id="rId864"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C417" r:id="rId865"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E417" r:id="rId866"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B418" r:id="rId867"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C418" r:id="rId868"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E418" r:id="rId869"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B419" r:id="rId870"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C419" r:id="rId871"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E419" r:id="rId872"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B420" r:id="rId873"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C420" r:id="rId874"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E420" r:id="rId875"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B421" r:id="rId876"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C421" r:id="rId877"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E421" r:id="rId878"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B422" r:id="rId879"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C422" r:id="rId880"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E422" r:id="rId881"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B423" r:id="rId882"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E423" r:id="rId883"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B424" r:id="rId884"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E424" r:id="rId885"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B425" r:id="rId886"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C425" r:id="rId887"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E425" r:id="rId888"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B426" r:id="rId889"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C426" r:id="rId890"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E426" r:id="rId891"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B427" r:id="rId892"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C427" r:id="rId893"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E427" r:id="rId894"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B428" r:id="rId895"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C428" r:id="rId896"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E428" r:id="rId897"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B429" r:id="rId898"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E429" r:id="rId899"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B430" r:id="rId900"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C430" r:id="rId901"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E430" r:id="rId902"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B431" r:id="rId903"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C431" r:id="rId904"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E431" r:id="rId905"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B432" r:id="rId906"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C432" r:id="rId907"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E432" r:id="rId908"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B433" r:id="rId909"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E433" r:id="rId910"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B434" r:id="rId911"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E434" r:id="rId912"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B435" r:id="rId913"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C435" r:id="rId914"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E435" r:id="rId915"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B436" r:id="rId916"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C436" r:id="rId917"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E436" r:id="rId918"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B437" r:id="rId919"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C437" r:id="rId920"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E437" r:id="rId921"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B438" r:id="rId922"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E438" r:id="rId923"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B439" r:id="rId924"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C439" r:id="rId925"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E439" r:id="rId926"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B440" r:id="rId927"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C440" r:id="rId928"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E440" r:id="rId929"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B441" r:id="rId930"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E441" r:id="rId931"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B442" r:id="rId932"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C442" r:id="rId933"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E442" r:id="rId934"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B443" r:id="rId935"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C443" r:id="rId936"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E443" r:id="rId937"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B444" r:id="rId938"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C444" r:id="rId939"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E444" r:id="rId940"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B445" r:id="rId941"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C445" r:id="rId942"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E445" r:id="rId943"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B446" r:id="rId944"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C446" r:id="rId945"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E446" r:id="rId946"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B447" r:id="rId947"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C447" r:id="rId948"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E447" r:id="rId949"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B448" r:id="rId950"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C448" r:id="rId951"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E448" r:id="rId952"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B449" r:id="rId953"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C449" r:id="rId954"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E449" r:id="rId955"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B450" r:id="rId956"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C450" r:id="rId957"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E450" r:id="rId958"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B451" r:id="rId959"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C451" r:id="rId960"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E451" r:id="rId961"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B452" r:id="rId962"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C452" r:id="rId963"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E452" r:id="rId964"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B453" r:id="rId965"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C453" r:id="rId966"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E453" r:id="rId967"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B454" r:id="rId968"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C454" r:id="rId969"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E454" r:id="rId970"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B455" r:id="rId971"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E455" r:id="rId972"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B456" r:id="rId973"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E456" r:id="rId974"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B457" r:id="rId975"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C457" r:id="rId976"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E457" r:id="rId977"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B458" r:id="rId978"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C458" r:id="rId979"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E458" r:id="rId980"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B459" r:id="rId981"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C459" r:id="rId982"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E459" r:id="rId983"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B460" r:id="rId984"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C460" r:id="rId985"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E460" r:id="rId986"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B461" r:id="rId987"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C461" r:id="rId988"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E461" r:id="rId989"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B462" r:id="rId990"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C462" r:id="rId991"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E462" r:id="rId992"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B463" r:id="rId993"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E463" r:id="rId994"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B464" r:id="rId995"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C464" r:id="rId996"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E464" r:id="rId997"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B465" r:id="rId998"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C465" r:id="rId999"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E465" r:id="rId1000"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B466" r:id="rId1001"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C466" r:id="rId1002"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E466" r:id="rId1003"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B467" r:id="rId1004"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C467" r:id="rId1005"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E467" r:id="rId1006"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C468" r:id="rId1007"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E468" r:id="rId1008"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B469" r:id="rId1009"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C469" r:id="rId1010"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E469" r:id="rId1011"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B470" r:id="rId1012"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C470" r:id="rId1013"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E470" r:id="rId1014"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B471" r:id="rId1015"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C471" r:id="rId1016"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E471" r:id="rId1017"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B472" r:id="rId1018"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C472" r:id="rId1019"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E472" r:id="rId1020"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B473" r:id="rId1021"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C473" r:id="rId1022"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E473" r:id="rId1023"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B474" r:id="rId1024"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C474" r:id="rId1025"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E474" r:id="rId1026"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B475" r:id="rId1027"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E475" r:id="rId1028"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B476" r:id="rId1029"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E476" r:id="rId1030"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B477" r:id="rId1031"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C477" r:id="rId1032"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E477" r:id="rId1033"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B478" r:id="rId1034"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E478" r:id="rId1035"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B479" r:id="rId1036"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E479" r:id="rId1037"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B480" r:id="rId1038"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C480" r:id="rId1039"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E480" r:id="rId1040"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B481" r:id="rId1041"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E481" r:id="rId1042"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B482" r:id="rId1043"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C482" r:id="rId1044"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E482" r:id="rId1045"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B483" r:id="rId1046"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C483" r:id="rId1047"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E483" r:id="rId1048"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C484" r:id="rId1049"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E484" r:id="rId1050"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B485" r:id="rId1051"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C485" r:id="rId1052"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E485" r:id="rId1053"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B486" r:id="rId1054"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C486" r:id="rId1055"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E486" r:id="rId1056"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B487" r:id="rId1057"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C487" r:id="rId1058"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E487" r:id="rId1059"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C488" r:id="rId1060"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E488" r:id="rId1061"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B489" r:id="rId1062"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C489" r:id="rId1063"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E489" r:id="rId1064"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B490" r:id="rId1065"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C490" r:id="rId1066"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E490" r:id="rId1067"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B491" r:id="rId1068"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C491" r:id="rId1069"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E491" r:id="rId1070"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B492" r:id="rId1071"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C492" r:id="rId1072"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E492" r:id="rId1073"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B493" r:id="rId1074"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C493" r:id="rId1075"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E493" r:id="rId1076"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B494" r:id="rId1077"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C494" r:id="rId1078"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E494" r:id="rId1079"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B495" r:id="rId1080"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C495" r:id="rId1081"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E495" r:id="rId1082"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B496" r:id="rId1083"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C496" r:id="rId1084"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E496" r:id="rId1085"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B497" r:id="rId1086"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C497" r:id="rId1087"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E497" r:id="rId1088"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B498" r:id="rId1089"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C498" r:id="rId1090"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E498" r:id="rId1091"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B499" r:id="rId1092"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C499" r:id="rId1093"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E499" r:id="rId1094"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B500" r:id="rId1095"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C500" r:id="rId1096"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E500" r:id="rId1097"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B501" r:id="rId1098"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C501" r:id="rId1099"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E501" r:id="rId1100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B502" r:id="rId1101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E502" r:id="rId1102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B503" r:id="rId1103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C503" r:id="rId1104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E503" r:id="rId1105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B504" r:id="rId1106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C504" r:id="rId1107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E504" r:id="rId1108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B505" r:id="rId1109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C505" r:id="rId1110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E505" r:id="rId1111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B506" r:id="rId1112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C506" r:id="rId1113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E506" r:id="rId1114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B507" r:id="rId1115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E507" r:id="rId1116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B508" r:id="rId1117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C508" r:id="rId1118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E508" r:id="rId1119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B509" r:id="rId1120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C509" r:id="rId1121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E509" r:id="rId1122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B510" r:id="rId1123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C510" r:id="rId1124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E510" r:id="rId1125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B511" r:id="rId1126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C511" r:id="rId1127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E511" r:id="rId1128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B512" r:id="rId1129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C512" r:id="rId1130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E512" r:id="rId1131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B513" r:id="rId1132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C513" r:id="rId1133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E513" r:id="rId1134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B514" r:id="rId1135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C514" r:id="rId1136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E514" r:id="rId1137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B515" r:id="rId1138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C515" r:id="rId1139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E515" r:id="rId1140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B516" r:id="rId1141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C516" r:id="rId1142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E516" r:id="rId1143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C517" r:id="rId1144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E517" r:id="rId1145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B518" r:id="rId1146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C518" r:id="rId1147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E518" r:id="rId1148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B519" r:id="rId1149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C519" r:id="rId1150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E519" r:id="rId1151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B520" r:id="rId1152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C520" r:id="rId1153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E520" r:id="rId1154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B521" r:id="rId1155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E521" r:id="rId1156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B522" r:id="rId1157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C522" r:id="rId1158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E522" r:id="rId1159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B523" r:id="rId1160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C523" r:id="rId1161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E523" r:id="rId1162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B524" r:id="rId1163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E524" r:id="rId1164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B525" r:id="rId1165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C525" r:id="rId1166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E525" r:id="rId1167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B526" r:id="rId1168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C526" r:id="rId1169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E526" r:id="rId1170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C527" r:id="rId1171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E527" r:id="rId1172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B528" r:id="rId1173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C528" r:id="rId1174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E528" r:id="rId1175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B529" r:id="rId1176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C529" r:id="rId1177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E529" r:id="rId1178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B530" r:id="rId1179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E530" r:id="rId1180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B531" r:id="rId1181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C531" r:id="rId1182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E531" r:id="rId1183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B532" r:id="rId1184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C532" r:id="rId1185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E532" r:id="rId1186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B533" r:id="rId1187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C533" r:id="rId1188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E533" r:id="rId1189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B534" r:id="rId1190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C534" r:id="rId1191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E534" r:id="rId1192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B535" r:id="rId1193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C535" r:id="rId1194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E535" r:id="rId1195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B536" r:id="rId1196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C536" r:id="rId1197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E536" r:id="rId1198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B537" r:id="rId1199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C537" r:id="rId1200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E537" r:id="rId1201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C538" r:id="rId1202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E538" r:id="rId1203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B539" r:id="rId1204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E539" r:id="rId1205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B540" r:id="rId1206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C540" r:id="rId1207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E540" r:id="rId1208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B541" r:id="rId1209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C541" r:id="rId1210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E541" r:id="rId1211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B542" r:id="rId1212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C542" r:id="rId1213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E542" r:id="rId1214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B543" r:id="rId1215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C543" r:id="rId1216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E543" r:id="rId1217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B545" r:id="rId1218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E545" r:id="rId1219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B546" r:id="rId1220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C546" r:id="rId1221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E546" r:id="rId1222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B547" r:id="rId1223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C547" r:id="rId1224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E547" r:id="rId1225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B548" r:id="rId1226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C548" r:id="rId1227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E548" r:id="rId1228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B549" r:id="rId1229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C549" r:id="rId1230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E549" r:id="rId1231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B551" r:id="rId1232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E551" r:id="rId1233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B552" r:id="rId1234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E552" r:id="rId1235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B553" r:id="rId1236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C553" r:id="rId1237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E553" r:id="rId1238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B555" r:id="rId1239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C555" r:id="rId1240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E555" r:id="rId1241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B556" r:id="rId1242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C556" r:id="rId1243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E556" r:id="rId1244"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B558" r:id="rId1245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C558" r:id="rId1246"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E558" r:id="rId1247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B560" r:id="rId1248"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C560" r:id="rId1249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E560" r:id="rId1250"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B563" r:id="rId1251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C563" r:id="rId1252"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E563" r:id="rId1253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B564" r:id="rId1254"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E564" r:id="rId1255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B565" r:id="rId1256"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E565" r:id="rId1257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B566" r:id="rId1258"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C566" r:id="rId1259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E566" r:id="rId1260"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B567" r:id="rId1261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C567" r:id="rId1262"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E567" r:id="rId1263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B568" r:id="rId1264"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E568" r:id="rId1265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C569" r:id="rId1266"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E569" r:id="rId1267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B570" r:id="rId1268"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E570" r:id="rId1269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B571" r:id="rId1270"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C571" r:id="rId1271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E571" r:id="rId1272"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B573" r:id="rId1273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C573" r:id="rId1274"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E573" r:id="rId1275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C574" r:id="rId1276"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E574" r:id="rId1277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B575" r:id="rId1278"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C575" r:id="rId1279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E575" r:id="rId1280"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B576" r:id="rId1281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C576" r:id="rId1282"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E576" r:id="rId1283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B577" r:id="rId1284"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C577" r:id="rId1285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E577" r:id="rId1286"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B578" r:id="rId1287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C578" r:id="rId1288"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E578" r:id="rId1289"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B579" r:id="rId1290"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C579" r:id="rId1291"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E579" r:id="rId1292"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B580" r:id="rId1293"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C580" r:id="rId1294"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E580" r:id="rId1295"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B581" r:id="rId1296"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C581" r:id="rId1297"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E581" r:id="rId1298"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B583" r:id="rId1299"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E583" r:id="rId1300"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B584" r:id="rId1301"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C584" r:id="rId1302"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E584" r:id="rId1303"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B587" r:id="rId1304"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C587" r:id="rId1305"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E587" r:id="rId1306"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B590" r:id="rId1307"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C590" r:id="rId1308"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E590" r:id="rId1309"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B591" r:id="rId1310"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C591" r:id="rId1311"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E591" r:id="rId1312"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B592" r:id="rId1313"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C592" r:id="rId1314"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E592" r:id="rId1315"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B593" r:id="rId1316"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C593" r:id="rId1317"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E593" r:id="rId1318"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B595" r:id="rId1319"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C595" r:id="rId1320"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E595" r:id="rId1321"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B596" r:id="rId1322"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C596" r:id="rId1323"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E596" r:id="rId1324"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C599" r:id="rId1325"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E599" r:id="rId1326"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B600" r:id="rId1327"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C600" r:id="rId1328"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E600" r:id="rId1329"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C601" r:id="rId1330"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E601" r:id="rId1331"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B602" r:id="rId1332"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C602" r:id="rId1333"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E602" r:id="rId1334"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C603" r:id="rId1335"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E603" r:id="rId1336"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B604" r:id="rId1337"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C604" r:id="rId1338"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E604" r:id="rId1339"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B605" r:id="rId1340"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C605" r:id="rId1341"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E605" r:id="rId1342"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B606" r:id="rId1343"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C606" r:id="rId1344"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E606" r:id="rId1345"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B607" r:id="rId1346"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C607" r:id="rId1347"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E607" r:id="rId1348"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B608" r:id="rId1349"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C608" r:id="rId1350"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E608" r:id="rId1351"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B609" r:id="rId1352"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C609" r:id="rId1353"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E609" r:id="rId1354"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B610" r:id="rId1355"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E610" r:id="rId1356"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C611" r:id="rId1357"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E611" r:id="rId1358"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C612" r:id="rId1359"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E612" r:id="rId1360"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C613" r:id="rId1361"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E613" r:id="rId1362"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B614" r:id="rId1363"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C614" r:id="rId1364"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E614" r:id="rId1365"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B615" r:id="rId1366"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E615" r:id="rId1367"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B616" r:id="rId1368"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E616" r:id="rId1369"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C617" r:id="rId1370"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E617" r:id="rId1371"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B618" r:id="rId1372"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C618" r:id="rId1373"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E618" r:id="rId1374"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C619" r:id="rId1375"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E619" r:id="rId1376"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C620" r:id="rId1377"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E620" r:id="rId1378"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C621" r:id="rId1379"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E621" r:id="rId1380"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C622" r:id="rId1381"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E622" r:id="rId1382"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B623" r:id="rId1383"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C623" r:id="rId1384"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E623" r:id="rId1385"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B624" r:id="rId1386"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C624" r:id="rId1387"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E624" r:id="rId1388"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B625" r:id="rId1389"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C625" r:id="rId1390"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E625" r:id="rId1391"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C626" r:id="rId1392"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E626" r:id="rId1393"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B627" r:id="rId1394"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C627" r:id="rId1395"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E627" r:id="rId1396"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C628" r:id="rId1397"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E628" r:id="rId1398"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B629" r:id="rId1399"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E629" r:id="rId1400"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C630" r:id="rId1401"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E630" r:id="rId1402"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B631" r:id="rId1403"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E631" r:id="rId1404"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B632" r:id="rId1405"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C632" r:id="rId1406"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E632" r:id="rId1407"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C633" r:id="rId1408"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E633" r:id="rId1409"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C634" r:id="rId1410"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E634" r:id="rId1411"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C635" r:id="rId1412"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E635" r:id="rId1413"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C636" r:id="rId1414"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E636" r:id="rId1415"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B637" r:id="rId1416"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C637" r:id="rId1417"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E637" r:id="rId1418"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B638" r:id="rId1419"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C638" r:id="rId1420"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E638" r:id="rId1421"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B639" r:id="rId1422"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E639" r:id="rId1423"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B640" r:id="rId1424"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C640" r:id="rId1425"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E640" r:id="rId1426"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B641" r:id="rId1427"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C641" r:id="rId1428"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E641" r:id="rId1429"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B642" r:id="rId1430"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C642" r:id="rId1431"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E642" r:id="rId1432"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C643" r:id="rId1433"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E643" r:id="rId1434"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C644" r:id="rId1435"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E644" r:id="rId1436"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C645" r:id="rId1437"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E645" r:id="rId1438"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C646" r:id="rId1439"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E646" r:id="rId1440"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C647" r:id="rId1441"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E647" r:id="rId1442"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B648" r:id="rId1443"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E648" r:id="rId1444"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C649" r:id="rId1445"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E649" r:id="rId1446"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B650" r:id="rId1447"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C650" r:id="rId1448"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E650" r:id="rId1449"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B651" r:id="rId1450"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C651" r:id="rId1451"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E651" r:id="rId1452"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B652" r:id="rId1453"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C652" r:id="rId1454"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E652" r:id="rId1455"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C653" r:id="rId1456"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E653" r:id="rId1457"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B654" r:id="rId1458"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C654" r:id="rId1459"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E654" r:id="rId1460"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B655" r:id="rId1461"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E655" r:id="rId1462"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B656" r:id="rId1463"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C656" r:id="rId1464"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E656" r:id="rId1465"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C657" r:id="rId1466"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E657" r:id="rId1467"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B658" r:id="rId1468"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E658" r:id="rId1469"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C659" r:id="rId1470"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E659" r:id="rId1471"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B660" r:id="rId1472"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C660" r:id="rId1473"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E660" r:id="rId1474"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C661" r:id="rId1475"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E661" r:id="rId1476"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C662" r:id="rId1477"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E662" r:id="rId1478"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B663" r:id="rId1479"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E663" r:id="rId1480"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C664" r:id="rId1481"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E664" r:id="rId1482"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C665" r:id="rId1483"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E665" r:id="rId1484"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B666" r:id="rId1485"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E666" r:id="rId1486"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B667" r:id="rId1487"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E667" r:id="rId1488"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C669" r:id="rId1489"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E669" r:id="rId1490"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B670" r:id="rId1491"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C670" r:id="rId1492"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E670" r:id="rId1493"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B671" r:id="rId1494"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C671" r:id="rId1495"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E671" r:id="rId1496"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B672" r:id="rId1497"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C672" r:id="rId1498"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E672" r:id="rId1499"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B673" r:id="rId1500"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C673" r:id="rId1501"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E673" r:id="rId1502"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B674" r:id="rId1503"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C674" r:id="rId1504"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E674" r:id="rId1505"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B675" r:id="rId1506"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C675" r:id="rId1507"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E675" r:id="rId1508"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C676" r:id="rId1509"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E676" r:id="rId1510"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B677" r:id="rId1511"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C677" r:id="rId1512"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E677" r:id="rId1513"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B678" r:id="rId1514"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E678" r:id="rId1515"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C679" r:id="rId1516"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E679" r:id="rId1517"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C680" r:id="rId1518"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E680" r:id="rId1519"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C681" r:id="rId1520"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E681" r:id="rId1521"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C682" r:id="rId1522"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E682" r:id="rId1523"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C683" r:id="rId1524"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E683" r:id="rId1525"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C684" r:id="rId1526"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E684" r:id="rId1527"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C685" r:id="rId1528"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E685" r:id="rId1529"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C686" r:id="rId1530"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E686" r:id="rId1531"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C687" r:id="rId1532"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E687" r:id="rId1533"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B688" r:id="rId1534"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C688" r:id="rId1535"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E688" r:id="rId1536"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B689" r:id="rId1537"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C689" r:id="rId1538"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E689" r:id="rId1539"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B690" r:id="rId1540"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C690" r:id="rId1541"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E690" r:id="rId1542"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B691" r:id="rId1543"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C691" r:id="rId1544"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E691" r:id="rId1545"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B692" r:id="rId1546"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C692" r:id="rId1547"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E692" r:id="rId1548"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C693" r:id="rId1549"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E693" r:id="rId1550"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B694" r:id="rId1551"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C694" r:id="rId1552"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E694" r:id="rId1553"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B695" r:id="rId1554"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C695" r:id="rId1555"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E695" r:id="rId1556"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B696" r:id="rId1557"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E696" r:id="rId1558"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C697" r:id="rId1559"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E697" r:id="rId1560"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B698" r:id="rId1561"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E698" r:id="rId1562"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C699" r:id="rId1563"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E699" r:id="rId1564"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B700" r:id="rId1565"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E700" r:id="rId1566"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B701" r:id="rId1567"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E701" r:id="rId1568"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B702" r:id="rId1569"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C702" r:id="rId1570"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E702" r:id="rId1571"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B703" r:id="rId1572"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E703" r:id="rId1573"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C704" r:id="rId1574"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E704" r:id="rId1575"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B705" r:id="rId1576"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C705" r:id="rId1577"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E705" r:id="rId1578"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C706" r:id="rId1579"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E706" r:id="rId1580"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B707" r:id="rId1581"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C707" r:id="rId1582"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E707" r:id="rId1583"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B708" r:id="rId1584"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C708" r:id="rId1585"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E708" r:id="rId1586"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C709" r:id="rId1587"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E709" r:id="rId1588"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C710" r:id="rId1589"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E710" r:id="rId1590"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C711" r:id="rId1591"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E711" r:id="rId1592"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B712" r:id="rId1593"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E712" r:id="rId1594"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B713" r:id="rId1595"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C713" r:id="rId1596"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E713" r:id="rId1597"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C714" r:id="rId1598"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E714" r:id="rId1599"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B715" r:id="rId1600"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C715" r:id="rId1601"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E715" r:id="rId1602"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B716" r:id="rId1603"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C716" r:id="rId1604"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E716" r:id="rId1605"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B718" r:id="rId1606"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C718" r:id="rId1607"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E718" r:id="rId1608"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D720" r:id="rId1609"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B721" r:id="rId1610"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E721" r:id="rId1611"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B722" r:id="rId1612"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E722" r:id="rId1613"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B723" r:id="rId1614"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E723" r:id="rId1615"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B724" r:id="rId1616"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E724" r:id="rId1617"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B725" r:id="rId1618"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C725" r:id="rId1619"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E725" r:id="rId1620"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B726" r:id="rId1621"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C726" r:id="rId1622"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E726" r:id="rId1623"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C727" r:id="rId1624"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E727" r:id="rId1625"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B728" r:id="rId1626"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C728" r:id="rId1627"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E728" r:id="rId1628"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B729" r:id="rId1629"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C729" r:id="rId1630"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E729" r:id="rId1631"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C730" r:id="rId1632"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E730" r:id="rId1633"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C731" r:id="rId1634"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E731" r:id="rId1635"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B732" r:id="rId1636"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C732" r:id="rId1637"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E732" r:id="rId1638"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B733" r:id="rId1639"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E733" r:id="rId1640"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B734" r:id="rId1641"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E734" r:id="rId1642"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B735" r:id="rId1643"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E735" r:id="rId1644"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B736" r:id="rId1645"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C736" r:id="rId1646"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E736" r:id="rId1647"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B737" r:id="rId1648"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E737" r:id="rId1649"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C738" r:id="rId1650"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E738" r:id="rId1651"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C739" r:id="rId1652"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E739" r:id="rId1653"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B740" r:id="rId1654"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C740" r:id="rId1655"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E740" r:id="rId1656"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B741" r:id="rId1657"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C741" r:id="rId1658"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E741" r:id="rId1659"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C742" r:id="rId1660"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E742" r:id="rId1661"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B743" r:id="rId1662"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C743" r:id="rId1663"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E743" r:id="rId1664"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C744" r:id="rId1665"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E744" r:id="rId1666"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B745" r:id="rId1667"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E745" r:id="rId1668"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B746" r:id="rId1669"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C746" r:id="rId1670"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E746" r:id="rId1671"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B747" r:id="rId1672"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E747" r:id="rId1673"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B748" r:id="rId1674"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C748" r:id="rId1675"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E748" r:id="rId1676"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B749" r:id="rId1677"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C749" r:id="rId1678"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E749" r:id="rId1679"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B34" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B36" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B37" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B38" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A41" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B41" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B42" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C44" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B45" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B47" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C47" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C48" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B49" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B50" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B51" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B52" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D52" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B53" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D53" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C54" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B55" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C56" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D56" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D57" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B58" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C58" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D58" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A59" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C59" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D60" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B61" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C61" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D61" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B62" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C62" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A63" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B63" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C63" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B64" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B65" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D65" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D67" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A68" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B68" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C68" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D68" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D69" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C70" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D70" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B71" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C72" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B73" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D73" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B74" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C74" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D74" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B75" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C75" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D75" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B76" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C76" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B77" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C77" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D77" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B79" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D79" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B80" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C80" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B81" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C81" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D81" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C82" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A83" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B83" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C83" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D83" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B84" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C84" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D84" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B86" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C86" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C87" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B88" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C88" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C89" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D89" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C90" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D90" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B91" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C91" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B92" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C92" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B93" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C93" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C94" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D94" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B95" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D95" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A97" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B97" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C97" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B98" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C98" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D100" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D101" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D102" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B103" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D103" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D104" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D106" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D107" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D108" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D109" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D110" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C111" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D112" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D113" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B114" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D115" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D116" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D117" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D118" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D119" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B120" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D121" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D122" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D123" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D124" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D125" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D126" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D127" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D128" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D129" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B130" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C130" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D130" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E130" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B131" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E131" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D132" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D133" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D134" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D135" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C136" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D136" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E136" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D137" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D138" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D139" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B140" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E140" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D141" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D142" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D143" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B144" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C144" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E144" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D145" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D146" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D147" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C148" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E148" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B149" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D149" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E149" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D150" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D151" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D152" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D153" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D154" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D155" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D156" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D157" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D158" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D159" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B160" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E160" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D161" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D162" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D163" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D164" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D165" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D166" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D167" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D168" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D169" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D170" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D171" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D172" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D173" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C174" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E174" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D175" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D176" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D177" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D178" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D179" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D180" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D181" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D182" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D183" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D184" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B185" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E185" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C186" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E186" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D187" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D188" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D189" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B190" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C190" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D190" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E190" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B191" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D191" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E191" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D192" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D193" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B194" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E194" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D195" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C196" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E196" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D197" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D198" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D199" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D200" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D201" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D202" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D203" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B204" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E204" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D205" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D206" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D207" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D208" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B209" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E209" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B210" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E210" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D211" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D212" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D213" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D214" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D215" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D216" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D217" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D218" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C219" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D219" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E219" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D220" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D221" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D222" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D223" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D224" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D225" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D226" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D227" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D228" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B229" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D229" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E229" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B230" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D230" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E230" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D231" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D232" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B233" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D233" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E233" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B234" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E234" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D235" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B236" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E236" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D237" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B238" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D238" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E238" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D239" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D240" r:id="rId461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D241" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D242" r:id="rId463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D243" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D244" r:id="rId465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D245" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B246" r:id="rId467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E246" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C247" r:id="rId469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D247" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E247" r:id="rId471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D248" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D249" r:id="rId473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D250" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D251" r:id="rId475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B252" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D252" r:id="rId477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E252" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D253" r:id="rId479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D254" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D255" r:id="rId481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B256" r:id="rId482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D256" r:id="rId483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E256" r:id="rId484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D257" r:id="rId485"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D258" r:id="rId486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D259" r:id="rId487"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D260" r:id="rId488"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D261" r:id="rId489"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D262" r:id="rId490"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D263" r:id="rId491"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B264" r:id="rId492"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E264" r:id="rId493"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D265" r:id="rId494"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D266" r:id="rId495"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D267" r:id="rId496"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D268" r:id="rId497"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D269" r:id="rId498"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D270" r:id="rId499"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D271" r:id="rId500"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D272" r:id="rId501"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D273" r:id="rId502"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D274" r:id="rId503"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D275" r:id="rId504"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D276" r:id="rId505"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D277" r:id="rId506"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D278" r:id="rId507"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D279" r:id="rId508"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D280" r:id="rId509"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B281" r:id="rId510"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E281" r:id="rId511"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B282" r:id="rId512"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C282" r:id="rId513"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D282" r:id="rId514"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E282" r:id="rId515"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D283" r:id="rId516"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D284" r:id="rId517"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D286" r:id="rId518"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D287" r:id="rId519"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D288" r:id="rId520"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D289" r:id="rId521"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B290" r:id="rId522"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C290" r:id="rId523"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D290" r:id="rId524"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E290" r:id="rId525"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B292" r:id="rId526"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E292" r:id="rId527"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B293" r:id="rId528"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C293" r:id="rId529"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E293" r:id="rId530"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B294" r:id="rId531"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C294" r:id="rId532"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E294" r:id="rId533"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B295" r:id="rId534"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E295" r:id="rId535"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B296" r:id="rId536"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C296" r:id="rId537"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E296" r:id="rId538"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B297" r:id="rId539"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C297" r:id="rId540"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E297" r:id="rId541"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B298" r:id="rId542"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C298" r:id="rId543"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E298" r:id="rId544"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B299" r:id="rId545"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C299" r:id="rId546"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E299" r:id="rId547"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B300" r:id="rId548"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E300" r:id="rId549"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B301" r:id="rId550"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C301" r:id="rId551"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E301" r:id="rId552"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B302" r:id="rId553"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C302" r:id="rId554"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E302" r:id="rId555"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B303" r:id="rId556"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E303" r:id="rId557"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B304" r:id="rId558"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C304" r:id="rId559"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E304" r:id="rId560"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B305" r:id="rId561"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C305" r:id="rId562"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E305" r:id="rId563"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B306" r:id="rId564"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E306" r:id="rId565"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B307" r:id="rId566"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C307" r:id="rId567"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E307" r:id="rId568"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B308" r:id="rId569"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C308" r:id="rId570"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E308" r:id="rId571"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B309" r:id="rId572"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C309" r:id="rId573"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E309" r:id="rId574"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B310" r:id="rId575"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C310" r:id="rId576"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E310" r:id="rId577"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B311" r:id="rId578"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C311" r:id="rId579"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E311" r:id="rId580"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B312" r:id="rId581"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C312" r:id="rId582"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E312" r:id="rId583"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B313" r:id="rId584"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E313" r:id="rId585"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B314" r:id="rId586"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C314" r:id="rId587"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E314" r:id="rId588"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B315" r:id="rId589"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C315" r:id="rId590"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E315" r:id="rId591"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B316" r:id="rId592"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C316" r:id="rId593"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E316" r:id="rId594"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B317" r:id="rId595"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C317" r:id="rId596"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E317" r:id="rId597"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B318" r:id="rId598"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E318" r:id="rId599"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B319" r:id="rId600"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C319" r:id="rId601"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E319" r:id="rId602"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B320" r:id="rId603"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C320" r:id="rId604"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E320" r:id="rId605"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C322" r:id="rId606"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E322" r:id="rId607"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B323" r:id="rId608"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C323" r:id="rId609"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E323" r:id="rId610"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B324" r:id="rId611"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C324" r:id="rId612"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E324" r:id="rId613"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B325" r:id="rId614"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C325" r:id="rId615"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E325" r:id="rId616"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B326" r:id="rId617"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C326" r:id="rId618"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E326" r:id="rId619"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C327" r:id="rId620"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E327" r:id="rId621"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B328" r:id="rId622"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C328" r:id="rId623"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E328" r:id="rId624"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B329" r:id="rId625"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C329" r:id="rId626"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E329" r:id="rId627"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B330" r:id="rId628"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C330" r:id="rId629"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E330" r:id="rId630"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B331" r:id="rId631"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C331" r:id="rId632"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E331" r:id="rId633"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C332" r:id="rId634"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E332" r:id="rId635"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B333" r:id="rId636"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C333" r:id="rId637"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E333" r:id="rId638"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B334" r:id="rId639"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C334" r:id="rId640"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E334" r:id="rId641"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B335" r:id="rId642"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C335" r:id="rId643"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E335" r:id="rId644"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B336" r:id="rId645"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C336" r:id="rId646"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E336" r:id="rId647"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B337" r:id="rId648"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C337" r:id="rId649"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E337" r:id="rId650"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B338" r:id="rId651"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C338" r:id="rId652"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E338" r:id="rId653"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C339" r:id="rId654"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E339" r:id="rId655"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B340" r:id="rId656"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C340" r:id="rId657"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E340" r:id="rId658"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B341" r:id="rId659"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C341" r:id="rId660"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E341" r:id="rId661"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B342" r:id="rId662"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C342" r:id="rId663"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E342" r:id="rId664"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B343" r:id="rId665"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C343" r:id="rId666"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E343" r:id="rId667"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B344" r:id="rId668"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C344" r:id="rId669"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E344" r:id="rId670"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B345" r:id="rId671"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C345" r:id="rId672"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E345" r:id="rId673"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B346" r:id="rId674"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C346" r:id="rId675"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E346" r:id="rId676"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B347" r:id="rId677"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C347" r:id="rId678"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E347" r:id="rId679"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B348" r:id="rId680"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C348" r:id="rId681"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E348" r:id="rId682"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B349" r:id="rId683"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C349" r:id="rId684"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E349" r:id="rId685"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B350" r:id="rId686"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C350" r:id="rId687"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E350" r:id="rId688"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B351" r:id="rId689"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C351" r:id="rId690"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E351" r:id="rId691"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B352" r:id="rId692"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C352" r:id="rId693"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E352" r:id="rId694"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B353" r:id="rId695"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C353" r:id="rId696"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E353" r:id="rId697"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B354" r:id="rId698"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C354" r:id="rId699"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E354" r:id="rId700"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B355" r:id="rId701"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C355" r:id="rId702"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E355" r:id="rId703"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B356" r:id="rId704"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C356" r:id="rId705"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E356" r:id="rId706"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B357" r:id="rId707"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C357" r:id="rId708"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E357" r:id="rId709"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B358" r:id="rId710"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E358" r:id="rId711"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B359" r:id="rId712"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C359" r:id="rId713"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E359" r:id="rId714"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B360" r:id="rId715"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C360" r:id="rId716"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E360" r:id="rId717"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B361" r:id="rId718"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C361" r:id="rId719"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E361" r:id="rId720"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B362" r:id="rId721"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C362" r:id="rId722"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E362" r:id="rId723"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B363" r:id="rId724"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C363" r:id="rId725"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E363" r:id="rId726"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B364" r:id="rId727"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C364" r:id="rId728"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E364" r:id="rId729"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B365" r:id="rId730"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E365" r:id="rId731"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C366" r:id="rId732"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E366" r:id="rId733"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B367" r:id="rId734"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C367" r:id="rId735"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E367" r:id="rId736"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B368" r:id="rId737"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E368" r:id="rId738"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B369" r:id="rId739"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E369" r:id="rId740"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B370" r:id="rId741"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C370" r:id="rId742"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E370" r:id="rId743"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B371" r:id="rId744"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E371" r:id="rId745"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B372" r:id="rId746"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C372" r:id="rId747"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E372" r:id="rId748"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B373" r:id="rId749"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C373" r:id="rId750"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E373" r:id="rId751"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B374" r:id="rId752"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C374" r:id="rId753"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E374" r:id="rId754"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B375" r:id="rId755"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C375" r:id="rId756"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E375" r:id="rId757"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B376" r:id="rId758"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C376" r:id="rId759"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E376" r:id="rId760"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B377" r:id="rId761"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C377" r:id="rId762"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E377" r:id="rId763"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B378" r:id="rId764"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E378" r:id="rId765"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B379" r:id="rId766"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C379" r:id="rId767"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E379" r:id="rId768"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B380" r:id="rId769"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C380" r:id="rId770"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E380" r:id="rId771"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B381" r:id="rId772"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C381" r:id="rId773"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E381" r:id="rId774"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B382" r:id="rId775"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C382" r:id="rId776"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E382" r:id="rId777"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B383" r:id="rId778"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C383" r:id="rId779"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E383" r:id="rId780"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B384" r:id="rId781"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C384" r:id="rId782"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E384" r:id="rId783"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B385" r:id="rId784"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C385" r:id="rId785"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E385" r:id="rId786"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B386" r:id="rId787"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C386" r:id="rId788"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E386" r:id="rId789"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B387" r:id="rId790"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C387" r:id="rId791"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E387" r:id="rId792"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B388" r:id="rId793"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C388" r:id="rId794"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E388" r:id="rId795"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B389" r:id="rId796"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E389" r:id="rId797"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B390" r:id="rId798"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C390" r:id="rId799"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E390" r:id="rId800"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B391" r:id="rId801"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C391" r:id="rId802"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E391" r:id="rId803"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B392" r:id="rId804"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C392" r:id="rId805"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E392" r:id="rId806"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B393" r:id="rId807"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C393" r:id="rId808"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E393" r:id="rId809"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B394" r:id="rId810"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C394" r:id="rId811"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E394" r:id="rId812"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B395" r:id="rId813"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E395" r:id="rId814"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B396" r:id="rId815"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C396" r:id="rId816"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E396" r:id="rId817"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B397" r:id="rId818"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C397" r:id="rId819"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E397" r:id="rId820"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B398" r:id="rId821"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E398" r:id="rId822"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B399" r:id="rId823"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C399" r:id="rId824"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E399" r:id="rId825"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B400" r:id="rId826"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C400" r:id="rId827"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E400" r:id="rId828"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B401" r:id="rId829"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C401" r:id="rId830"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E401" r:id="rId831"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B402" r:id="rId832"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C402" r:id="rId833"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E402" r:id="rId834"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B403" r:id="rId835"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C403" r:id="rId836"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E403" r:id="rId837"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B404" r:id="rId838"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C404" r:id="rId839"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E404" r:id="rId840"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B405" r:id="rId841"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C405" r:id="rId842"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E405" r:id="rId843"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B406" r:id="rId844"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C406" r:id="rId845"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E406" r:id="rId846"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B407" r:id="rId847"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C407" r:id="rId848"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E407" r:id="rId849"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B408" r:id="rId850"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C408" r:id="rId851"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E408" r:id="rId852"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B409" r:id="rId853"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C409" r:id="rId854"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E409" r:id="rId855"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B410" r:id="rId856"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C410" r:id="rId857"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E410" r:id="rId858"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B411" r:id="rId859"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C411" r:id="rId860"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E411" r:id="rId861"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B412" r:id="rId862"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C412" r:id="rId863"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E412" r:id="rId864"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B413" r:id="rId865"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C413" r:id="rId866"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E413" r:id="rId867"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B414" r:id="rId868"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C414" r:id="rId869"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E414" r:id="rId870"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B415" r:id="rId871"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E415" r:id="rId872"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B416" r:id="rId873"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C416" r:id="rId874"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E416" r:id="rId875"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B417" r:id="rId876"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C417" r:id="rId877"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E417" r:id="rId878"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B418" r:id="rId879"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C418" r:id="rId880"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E418" r:id="rId881"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B419" r:id="rId882"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C419" r:id="rId883"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E419" r:id="rId884"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B420" r:id="rId885"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C420" r:id="rId886"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E420" r:id="rId887"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B421" r:id="rId888"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C421" r:id="rId889"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E421" r:id="rId890"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B422" r:id="rId891"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C422" r:id="rId892"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E422" r:id="rId893"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B423" r:id="rId894"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E423" r:id="rId895"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B424" r:id="rId896"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E424" r:id="rId897"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B425" r:id="rId898"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C425" r:id="rId899"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E425" r:id="rId900"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B426" r:id="rId901"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C426" r:id="rId902"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E426" r:id="rId903"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B427" r:id="rId904"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C427" r:id="rId905"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E427" r:id="rId906"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B428" r:id="rId907"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C428" r:id="rId908"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E428" r:id="rId909"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B429" r:id="rId910"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E429" r:id="rId911"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B430" r:id="rId912"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C430" r:id="rId913"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E430" r:id="rId914"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B431" r:id="rId915"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C431" r:id="rId916"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E431" r:id="rId917"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B432" r:id="rId918"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C432" r:id="rId919"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E432" r:id="rId920"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B433" r:id="rId921"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E433" r:id="rId922"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B434" r:id="rId923"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E434" r:id="rId924"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B435" r:id="rId925"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C435" r:id="rId926"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E435" r:id="rId927"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B436" r:id="rId928"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C436" r:id="rId929"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E436" r:id="rId930"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B437" r:id="rId931"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C437" r:id="rId932"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E437" r:id="rId933"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B438" r:id="rId934"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E438" r:id="rId935"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B439" r:id="rId936"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C439" r:id="rId937"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E439" r:id="rId938"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B440" r:id="rId939"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C440" r:id="rId940"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E440" r:id="rId941"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B441" r:id="rId942"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E441" r:id="rId943"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B442" r:id="rId944"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C442" r:id="rId945"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E442" r:id="rId946"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B443" r:id="rId947"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C443" r:id="rId948"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E443" r:id="rId949"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B444" r:id="rId950"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C444" r:id="rId951"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E444" r:id="rId952"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B445" r:id="rId953"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C445" r:id="rId954"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E445" r:id="rId955"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B446" r:id="rId956"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C446" r:id="rId957"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E446" r:id="rId958"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B447" r:id="rId959"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C447" r:id="rId960"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E447" r:id="rId961"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B448" r:id="rId962"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C448" r:id="rId963"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E448" r:id="rId964"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B449" r:id="rId965"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C449" r:id="rId966"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E449" r:id="rId967"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B450" r:id="rId968"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C450" r:id="rId969"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E450" r:id="rId970"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B451" r:id="rId971"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C451" r:id="rId972"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E451" r:id="rId973"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B452" r:id="rId974"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C452" r:id="rId975"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E452" r:id="rId976"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B453" r:id="rId977"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C453" r:id="rId978"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E453" r:id="rId979"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B454" r:id="rId980"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C454" r:id="rId981"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E454" r:id="rId982"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B455" r:id="rId983"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E455" r:id="rId984"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B456" r:id="rId985"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E456" r:id="rId986"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B457" r:id="rId987"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C457" r:id="rId988"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E457" r:id="rId989"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B458" r:id="rId990"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C458" r:id="rId991"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E458" r:id="rId992"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B459" r:id="rId993"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C459" r:id="rId994"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E459" r:id="rId995"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B460" r:id="rId996"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C460" r:id="rId997"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E460" r:id="rId998"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B461" r:id="rId999"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C461" r:id="rId1000"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E461" r:id="rId1001"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B462" r:id="rId1002"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C462" r:id="rId1003"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E462" r:id="rId1004"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B463" r:id="rId1005"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E463" r:id="rId1006"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B464" r:id="rId1007"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C464" r:id="rId1008"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E464" r:id="rId1009"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B465" r:id="rId1010"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C465" r:id="rId1011"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E465" r:id="rId1012"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B466" r:id="rId1013"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C466" r:id="rId1014"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E466" r:id="rId1015"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B467" r:id="rId1016"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C467" r:id="rId1017"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E467" r:id="rId1018"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C468" r:id="rId1019"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E468" r:id="rId1020"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B469" r:id="rId1021"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C469" r:id="rId1022"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E469" r:id="rId1023"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B470" r:id="rId1024"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C470" r:id="rId1025"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E470" r:id="rId1026"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B471" r:id="rId1027"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C471" r:id="rId1028"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E471" r:id="rId1029"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B472" r:id="rId1030"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C472" r:id="rId1031"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E472" r:id="rId1032"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B473" r:id="rId1033"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C473" r:id="rId1034"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E473" r:id="rId1035"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B474" r:id="rId1036"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C474" r:id="rId1037"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E474" r:id="rId1038"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B475" r:id="rId1039"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E475" r:id="rId1040"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B476" r:id="rId1041"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E476" r:id="rId1042"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B477" r:id="rId1043"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C477" r:id="rId1044"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E477" r:id="rId1045"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B478" r:id="rId1046"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E478" r:id="rId1047"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B479" r:id="rId1048"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E479" r:id="rId1049"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B480" r:id="rId1050"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C480" r:id="rId1051"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E480" r:id="rId1052"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B481" r:id="rId1053"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E481" r:id="rId1054"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B482" r:id="rId1055"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C482" r:id="rId1056"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E482" r:id="rId1057"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B483" r:id="rId1058"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C483" r:id="rId1059"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E483" r:id="rId1060"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C484" r:id="rId1061"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E484" r:id="rId1062"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B485" r:id="rId1063"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C485" r:id="rId1064"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E485" r:id="rId1065"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B486" r:id="rId1066"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C486" r:id="rId1067"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E486" r:id="rId1068"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B487" r:id="rId1069"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C487" r:id="rId1070"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E487" r:id="rId1071"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C488" r:id="rId1072"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E488" r:id="rId1073"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B489" r:id="rId1074"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C489" r:id="rId1075"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E489" r:id="rId1076"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B490" r:id="rId1077"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C490" r:id="rId1078"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E490" r:id="rId1079"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B491" r:id="rId1080"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C491" r:id="rId1081"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E491" r:id="rId1082"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B492" r:id="rId1083"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C492" r:id="rId1084"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E492" r:id="rId1085"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B493" r:id="rId1086"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C493" r:id="rId1087"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E493" r:id="rId1088"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B494" r:id="rId1089"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C494" r:id="rId1090"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E494" r:id="rId1091"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B495" r:id="rId1092"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C495" r:id="rId1093"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E495" r:id="rId1094"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B496" r:id="rId1095"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C496" r:id="rId1096"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E496" r:id="rId1097"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B497" r:id="rId1098"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C497" r:id="rId1099"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E497" r:id="rId1100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B498" r:id="rId1101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C498" r:id="rId1102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E498" r:id="rId1103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B499" r:id="rId1104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C499" r:id="rId1105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E499" r:id="rId1106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B500" r:id="rId1107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C500" r:id="rId1108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E500" r:id="rId1109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B501" r:id="rId1110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C501" r:id="rId1111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E501" r:id="rId1112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B502" r:id="rId1113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E502" r:id="rId1114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B503" r:id="rId1115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C503" r:id="rId1116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E503" r:id="rId1117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B504" r:id="rId1118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C504" r:id="rId1119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E504" r:id="rId1120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B505" r:id="rId1121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C505" r:id="rId1122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E505" r:id="rId1123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B506" r:id="rId1124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C506" r:id="rId1125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E506" r:id="rId1126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B507" r:id="rId1127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E507" r:id="rId1128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B508" r:id="rId1129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C508" r:id="rId1130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E508" r:id="rId1131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B509" r:id="rId1132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C509" r:id="rId1133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E509" r:id="rId1134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B510" r:id="rId1135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C510" r:id="rId1136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E510" r:id="rId1137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B511" r:id="rId1138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C511" r:id="rId1139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E511" r:id="rId1140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B512" r:id="rId1141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C512" r:id="rId1142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E512" r:id="rId1143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B513" r:id="rId1144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C513" r:id="rId1145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E513" r:id="rId1146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B514" r:id="rId1147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C514" r:id="rId1148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E514" r:id="rId1149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B515" r:id="rId1150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C515" r:id="rId1151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E515" r:id="rId1152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B516" r:id="rId1153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C516" r:id="rId1154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E516" r:id="rId1155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C517" r:id="rId1156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E517" r:id="rId1157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B518" r:id="rId1158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C518" r:id="rId1159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E518" r:id="rId1160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B519" r:id="rId1161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C519" r:id="rId1162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E519" r:id="rId1163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B520" r:id="rId1164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C520" r:id="rId1165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E520" r:id="rId1166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B521" r:id="rId1167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E521" r:id="rId1168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B522" r:id="rId1169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C522" r:id="rId1170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E522" r:id="rId1171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B523" r:id="rId1172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C523" r:id="rId1173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E523" r:id="rId1174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B524" r:id="rId1175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E524" r:id="rId1176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B525" r:id="rId1177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C525" r:id="rId1178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E525" r:id="rId1179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B526" r:id="rId1180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C526" r:id="rId1181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E526" r:id="rId1182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C527" r:id="rId1183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E527" r:id="rId1184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B528" r:id="rId1185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C528" r:id="rId1186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E528" r:id="rId1187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B529" r:id="rId1188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C529" r:id="rId1189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E529" r:id="rId1190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B530" r:id="rId1191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E530" r:id="rId1192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B531" r:id="rId1193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C531" r:id="rId1194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E531" r:id="rId1195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B532" r:id="rId1196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C532" r:id="rId1197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E532" r:id="rId1198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B533" r:id="rId1199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C533" r:id="rId1200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E533" r:id="rId1201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B534" r:id="rId1202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C534" r:id="rId1203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E534" r:id="rId1204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B535" r:id="rId1205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C535" r:id="rId1206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E535" r:id="rId1207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B536" r:id="rId1208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C536" r:id="rId1209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E536" r:id="rId1210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B537" r:id="rId1211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C537" r:id="rId1212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E537" r:id="rId1213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C538" r:id="rId1214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E538" r:id="rId1215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B539" r:id="rId1216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E539" r:id="rId1217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B540" r:id="rId1218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C540" r:id="rId1219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E540" r:id="rId1220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B541" r:id="rId1221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C541" r:id="rId1222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E541" r:id="rId1223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B542" r:id="rId1224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C542" r:id="rId1225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E542" r:id="rId1226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B543" r:id="rId1227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C543" r:id="rId1228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E543" r:id="rId1229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B545" r:id="rId1230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E545" r:id="rId1231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B546" r:id="rId1232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C546" r:id="rId1233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E546" r:id="rId1234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B547" r:id="rId1235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C547" r:id="rId1236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E547" r:id="rId1237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B548" r:id="rId1238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C548" r:id="rId1239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E548" r:id="rId1240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B549" r:id="rId1241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C549" r:id="rId1242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E549" r:id="rId1243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B551" r:id="rId1244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E551" r:id="rId1245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B552" r:id="rId1246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E552" r:id="rId1247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B553" r:id="rId1248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C553" r:id="rId1249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E553" r:id="rId1250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B555" r:id="rId1251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C555" r:id="rId1252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E555" r:id="rId1253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B556" r:id="rId1254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C556" r:id="rId1255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E556" r:id="rId1256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B558" r:id="rId1257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C558" r:id="rId1258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E558" r:id="rId1259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B560" r:id="rId1260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C560" r:id="rId1261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E560" r:id="rId1262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B563" r:id="rId1263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C563" r:id="rId1264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E563" r:id="rId1265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B564" r:id="rId1266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E564" r:id="rId1267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B565" r:id="rId1268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E565" r:id="rId1269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B566" r:id="rId1270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C566" r:id="rId1271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E566" r:id="rId1272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B567" r:id="rId1273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C567" r:id="rId1274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E567" r:id="rId1275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B568" r:id="rId1276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E568" r:id="rId1277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C569" r:id="rId1278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E569" r:id="rId1279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B570" r:id="rId1280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E570" r:id="rId1281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B571" r:id="rId1282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C571" r:id="rId1283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E571" r:id="rId1284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B573" r:id="rId1285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C573" r:id="rId1286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E573" r:id="rId1287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C574" r:id="rId1288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E574" r:id="rId1289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B575" r:id="rId1290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C575" r:id="rId1291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E575" r:id="rId1292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B576" r:id="rId1293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C576" r:id="rId1294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E576" r:id="rId1295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B577" r:id="rId1296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C577" r:id="rId1297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E577" r:id="rId1298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B578" r:id="rId1299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C578" r:id="rId1300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E578" r:id="rId1301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B579" r:id="rId1302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C579" r:id="rId1303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E579" r:id="rId1304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B580" r:id="rId1305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C580" r:id="rId1306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E580" r:id="rId1307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B581" r:id="rId1308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C581" r:id="rId1309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E581" r:id="rId1310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B583" r:id="rId1311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E583" r:id="rId1312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B584" r:id="rId1313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C584" r:id="rId1314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E584" r:id="rId1315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B587" r:id="rId1316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C587" r:id="rId1317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E587" r:id="rId1318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B590" r:id="rId1319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C590" r:id="rId1320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E590" r:id="rId1321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B591" r:id="rId1322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C591" r:id="rId1323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E591" r:id="rId1324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B592" r:id="rId1325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C592" r:id="rId1326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E592" r:id="rId1327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B593" r:id="rId1328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C593" r:id="rId1329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E593" r:id="rId1330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B595" r:id="rId1331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C595" r:id="rId1332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E595" r:id="rId1333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B596" r:id="rId1334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C596" r:id="rId1335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E596" r:id="rId1336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C599" r:id="rId1337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E599" r:id="rId1338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B600" r:id="rId1339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C600" r:id="rId1340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E600" r:id="rId1341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C601" r:id="rId1342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E601" r:id="rId1343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B602" r:id="rId1344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C602" r:id="rId1345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E602" r:id="rId1346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C603" r:id="rId1347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E603" r:id="rId1348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B604" r:id="rId1349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C604" r:id="rId1350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E604" r:id="rId1351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B605" r:id="rId1352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C605" r:id="rId1353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E605" r:id="rId1354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B606" r:id="rId1355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C606" r:id="rId1356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E606" r:id="rId1357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B607" r:id="rId1358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C607" r:id="rId1359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E607" r:id="rId1360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B608" r:id="rId1361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C608" r:id="rId1362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E608" r:id="rId1363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B609" r:id="rId1364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C609" r:id="rId1365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E609" r:id="rId1366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B610" r:id="rId1367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E610" r:id="rId1368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C611" r:id="rId1369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E611" r:id="rId1370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C612" r:id="rId1371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E612" r:id="rId1372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C613" r:id="rId1373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E613" r:id="rId1374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B614" r:id="rId1375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C614" r:id="rId1376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E614" r:id="rId1377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B615" r:id="rId1378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E615" r:id="rId1379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B616" r:id="rId1380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E616" r:id="rId1381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C617" r:id="rId1382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E617" r:id="rId1383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B618" r:id="rId1384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C618" r:id="rId1385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E618" r:id="rId1386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C619" r:id="rId1387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E619" r:id="rId1388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C620" r:id="rId1389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E620" r:id="rId1390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C621" r:id="rId1391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E621" r:id="rId1392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C622" r:id="rId1393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E622" r:id="rId1394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B623" r:id="rId1395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C623" r:id="rId1396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E623" r:id="rId1397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B624" r:id="rId1398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C624" r:id="rId1399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E624" r:id="rId1400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B625" r:id="rId1401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C625" r:id="rId1402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E625" r:id="rId1403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C626" r:id="rId1404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E626" r:id="rId1405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B627" r:id="rId1406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C627" r:id="rId1407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E627" r:id="rId1408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C628" r:id="rId1409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E628" r:id="rId1410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B629" r:id="rId1411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E629" r:id="rId1412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C630" r:id="rId1413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E630" r:id="rId1414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B631" r:id="rId1415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E631" r:id="rId1416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B632" r:id="rId1417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C632" r:id="rId1418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E632" r:id="rId1419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C633" r:id="rId1420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E633" r:id="rId1421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C634" r:id="rId1422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E634" r:id="rId1423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C635" r:id="rId1424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E635" r:id="rId1425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C636" r:id="rId1426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E636" r:id="rId1427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B637" r:id="rId1428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C637" r:id="rId1429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E637" r:id="rId1430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B638" r:id="rId1431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C638" r:id="rId1432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E638" r:id="rId1433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B639" r:id="rId1434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E639" r:id="rId1435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B640" r:id="rId1436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C640" r:id="rId1437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E640" r:id="rId1438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B641" r:id="rId1439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C641" r:id="rId1440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E641" r:id="rId1441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B642" r:id="rId1442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C642" r:id="rId1443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E642" r:id="rId1444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C643" r:id="rId1445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E643" r:id="rId1446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C644" r:id="rId1447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E644" r:id="rId1448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C645" r:id="rId1449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E645" r:id="rId1450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C646" r:id="rId1451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E646" r:id="rId1452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C647" r:id="rId1453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E647" r:id="rId1454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B648" r:id="rId1455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E648" r:id="rId1456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C649" r:id="rId1457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E649" r:id="rId1458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B650" r:id="rId1459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C650" r:id="rId1460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E650" r:id="rId1461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B651" r:id="rId1462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C651" r:id="rId1463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E651" r:id="rId1464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B652" r:id="rId1465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C652" r:id="rId1466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E652" r:id="rId1467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C653" r:id="rId1468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E653" r:id="rId1469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B654" r:id="rId1470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C654" r:id="rId1471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E654" r:id="rId1472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B655" r:id="rId1473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E655" r:id="rId1474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B656" r:id="rId1475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C656" r:id="rId1476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E656" r:id="rId1477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C657" r:id="rId1478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E657" r:id="rId1479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B658" r:id="rId1480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E658" r:id="rId1481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C659" r:id="rId1482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E659" r:id="rId1483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B660" r:id="rId1484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C660" r:id="rId1485"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E660" r:id="rId1486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C661" r:id="rId1487"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E661" r:id="rId1488"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C662" r:id="rId1489"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E662" r:id="rId1490"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B663" r:id="rId1491"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E663" r:id="rId1492"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C664" r:id="rId1493"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E664" r:id="rId1494"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C665" r:id="rId1495"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E665" r:id="rId1496"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B666" r:id="rId1497"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E666" r:id="rId1498"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B667" r:id="rId1499"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E667" r:id="rId1500"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C669" r:id="rId1501"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E669" r:id="rId1502"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B670" r:id="rId1503"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C670" r:id="rId1504"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E670" r:id="rId1505"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B671" r:id="rId1506"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C671" r:id="rId1507"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E671" r:id="rId1508"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B672" r:id="rId1509"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C672" r:id="rId1510"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E672" r:id="rId1511"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B673" r:id="rId1512"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C673" r:id="rId1513"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E673" r:id="rId1514"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B674" r:id="rId1515"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C674" r:id="rId1516"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E674" r:id="rId1517"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B675" r:id="rId1518"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C675" r:id="rId1519"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E675" r:id="rId1520"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C676" r:id="rId1521"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E676" r:id="rId1522"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B677" r:id="rId1523"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C677" r:id="rId1524"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E677" r:id="rId1525"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B678" r:id="rId1526"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E678" r:id="rId1527"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C679" r:id="rId1528"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E679" r:id="rId1529"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C680" r:id="rId1530"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E680" r:id="rId1531"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C681" r:id="rId1532"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E681" r:id="rId1533"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C682" r:id="rId1534"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E682" r:id="rId1535"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C683" r:id="rId1536"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E683" r:id="rId1537"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C684" r:id="rId1538"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E684" r:id="rId1539"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C685" r:id="rId1540"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E685" r:id="rId1541"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C686" r:id="rId1542"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E686" r:id="rId1543"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C687" r:id="rId1544"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E687" r:id="rId1545"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B688" r:id="rId1546"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C688" r:id="rId1547"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E688" r:id="rId1548"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B689" r:id="rId1549"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C689" r:id="rId1550"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E689" r:id="rId1551"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B690" r:id="rId1552"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C690" r:id="rId1553"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E690" r:id="rId1554"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B691" r:id="rId1555"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C691" r:id="rId1556"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E691" r:id="rId1557"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B692" r:id="rId1558"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C692" r:id="rId1559"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E692" r:id="rId1560"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C693" r:id="rId1561"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E693" r:id="rId1562"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B694" r:id="rId1563"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C694" r:id="rId1564"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E694" r:id="rId1565"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B695" r:id="rId1566"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C695" r:id="rId1567"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E695" r:id="rId1568"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B696" r:id="rId1569"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E696" r:id="rId1570"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C697" r:id="rId1571"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E697" r:id="rId1572"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B698" r:id="rId1573"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E698" r:id="rId1574"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C699" r:id="rId1575"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E699" r:id="rId1576"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B700" r:id="rId1577"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E700" r:id="rId1578"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B701" r:id="rId1579"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E701" r:id="rId1580"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B702" r:id="rId1581"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C702" r:id="rId1582"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E702" r:id="rId1583"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B703" r:id="rId1584"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E703" r:id="rId1585"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C704" r:id="rId1586"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E704" r:id="rId1587"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B705" r:id="rId1588"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C705" r:id="rId1589"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E705" r:id="rId1590"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C706" r:id="rId1591"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E706" r:id="rId1592"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B707" r:id="rId1593"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C707" r:id="rId1594"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E707" r:id="rId1595"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B708" r:id="rId1596"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C708" r:id="rId1597"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E708" r:id="rId1598"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C709" r:id="rId1599"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E709" r:id="rId1600"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C710" r:id="rId1601"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E710" r:id="rId1602"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C711" r:id="rId1603"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E711" r:id="rId1604"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B712" r:id="rId1605"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E712" r:id="rId1606"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B713" r:id="rId1607"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C713" r:id="rId1608"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E713" r:id="rId1609"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C714" r:id="rId1610"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E714" r:id="rId1611"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B715" r:id="rId1612"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C715" r:id="rId1613"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E715" r:id="rId1614"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B716" r:id="rId1615"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C716" r:id="rId1616"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E716" r:id="rId1617"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B718" r:id="rId1618"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C718" r:id="rId1619"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E718" r:id="rId1620"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D720" r:id="rId1621"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B721" r:id="rId1622"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E721" r:id="rId1623"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B722" r:id="rId1624"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E722" r:id="rId1625"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B723" r:id="rId1626"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E723" r:id="rId1627"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B724" r:id="rId1628"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E724" r:id="rId1629"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B725" r:id="rId1630"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C725" r:id="rId1631"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E725" r:id="rId1632"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B726" r:id="rId1633"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C726" r:id="rId1634"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E726" r:id="rId1635"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C727" r:id="rId1636"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E727" r:id="rId1637"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B728" r:id="rId1638"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C728" r:id="rId1639"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E728" r:id="rId1640"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B729" r:id="rId1641"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C729" r:id="rId1642"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E729" r:id="rId1643"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C730" r:id="rId1644"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E730" r:id="rId1645"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C731" r:id="rId1646"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E731" r:id="rId1647"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B732" r:id="rId1648"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C732" r:id="rId1649"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E732" r:id="rId1650"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B733" r:id="rId1651"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E733" r:id="rId1652"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B734" r:id="rId1653"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E734" r:id="rId1654"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B735" r:id="rId1655"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E735" r:id="rId1656"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B736" r:id="rId1657"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C736" r:id="rId1658"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E736" r:id="rId1659"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B737" r:id="rId1660"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E737" r:id="rId1661"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C738" r:id="rId1662"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E738" r:id="rId1663"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C739" r:id="rId1664"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E739" r:id="rId1665"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B740" r:id="rId1666"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C740" r:id="rId1667"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E740" r:id="rId1668"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B741" r:id="rId1669"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C741" r:id="rId1670"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E741" r:id="rId1671"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C742" r:id="rId1672"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E742" r:id="rId1673"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B743" r:id="rId1674"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C743" r:id="rId1675"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E743" r:id="rId1676"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C744" r:id="rId1677"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E744" r:id="rId1678"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B745" r:id="rId1679"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E745" r:id="rId1680"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B746" r:id="rId1681"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C746" r:id="rId1682"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E746" r:id="rId1683"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B747" r:id="rId1684"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E747" r:id="rId1685"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B748" r:id="rId1686"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C748" r:id="rId1687"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E748" r:id="rId1688"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B749" r:id="rId1689"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C749" r:id="rId1690"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E749" r:id="rId1691"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
